--- a/806-Ramseur-PnL.xlsx
+++ b/806-Ramseur-PnL.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="231">
   <si>
     <t xml:space="preserve">806 E Ramseur Mini Golf + Bar — P&amp;L model</t>
   </si>
@@ -43,7 +43,7 @@
     <t xml:space="preserve">3. Set gross margin per revenue line in Assumptions!B19:B23.</t>
   </si>
   <si>
-    <t xml:space="preserve">4. Staffing per daypart is on the Labor sheet; hours follow the days and daypart hours on Assumptions.</t>
+    <t xml:space="preserve">4. Hourly staff per day and daypart (summer and winter) are entered on the Labor sheet at one hourly wage; players and days come from Assumptions.</t>
   </si>
   <si>
     <t xml:space="preserve">5. Black text = formula, green = link from another sheet. Don't type over black cells.</t>
@@ -67,7 +67,7 @@
     <t xml:space="preserve">Assumptions — schedule, players and spend by period, gross margins, cost and finance inputs.</t>
   </si>
   <si>
-    <t xml:space="preserve">Labor — people on shift by daypart, hours, wages. Capex — one-time costs. Opex — fixed annual costs. Financing — loan and equity.</t>
+    <t xml:space="preserve">Labor — hourly staff by day and daypart vs. players, salaried management, annual total. Capex — one-time costs. Opex — fixed annual costs. Financing — loan and equity.</t>
   </si>
   <si>
     <t xml:space="preserve">Excludes depreciation, interest/principal split and income taxes. Planning estimates, not quotes.</t>
@@ -145,7 +145,7 @@
     <t xml:space="preserve">Operating costs</t>
   </si>
   <si>
-    <t xml:space="preserve">Hourly labor (by open hours)</t>
+    <t xml:space="preserve">Hourly labor</t>
   </si>
   <si>
     <t xml:space="preserve">Salaried labor</t>
@@ -418,115 +418,109 @@
     <t xml:space="preserve">Year 5 volume vs. stabilized</t>
   </si>
   <si>
-    <t xml:space="preserve">Labor — tied to the operating schedule on Assumptions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hourly role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wkday aft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wkday eve</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wkend aft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wkend eve</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hours / yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rate</t>
+    <t xml:space="preserve">GM or Assistant GM is always on premises (salaried, below). Enter hourly staff per day and daypart in columns G and J. Players come from the Assumptions period table.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hourly wage, all hourly staff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summer days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summer players / daypart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summer players / hr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summer hourly staff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Winter days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Winter players / daypart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Winter hourly staff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summer staff hrs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Winter staff hrs</t>
   </si>
   <si>
     <t xml:space="preserve">Annual wages</t>
   </si>
   <si>
-    <t xml:space="preserve">People on shift per daypart (same in summer and winter)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Course host / cashier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check-in, putters, course flow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bartender</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base wage above NC tipped minimum ($2.13); tips on top</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ice cream attendant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Afternoon-heavy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barback / porter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cleaning, restocking, glassware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Door / security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ID checks, closing on weekend nights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open / close crew</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B = staff, C = hours each per open day</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maintenance tech (part-time)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B = hours per week, off-hours</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hourly wages</t>
+    <t xml:space="preserve">Monday</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Closed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tuesday</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wednesday</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thursday</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Friday</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saturday</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunday</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annual labor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">General Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recommended band $65k-$75k + up to 10% bonus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assistant GM / Bar Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Durham bar manager postings ~$38k-$67k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GM performance bonus (target)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taxes + health benefits on salaries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salaried total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hourly staff wages</t>
   </si>
   <si>
     <t xml:space="preserve">Hourly payroll taxes</t>
   </si>
   <si>
-    <t xml:space="preserve">Hourly total, loaded</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salaried role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Annual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">General Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recommended band $65k-$75k + up to 10% bonus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assistant GM / Bar Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Durham bar manager postings ~$38k-$67k</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GM performance bonus (target)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salaried total, loaded</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total labor, loaded</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bartender rate is base wage above NC's $2.13 tipped minimum; tips not modeled. Friday counts as a weekday.</t>
+    <t xml:space="preserve">Hourly staff total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annual total labor</t>
   </si>
   <si>
     <t xml:space="preserve">Initial capex</t>
@@ -869,7 +863,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -978,7 +972,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="172" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1381,15 +1379,15 @@
       </c>
       <c r="B4" s="6" t="n">
         <f aca="false">SUM(Assumptions!$J$8:$J$11)</f>
-        <v>31740</v>
+        <v>21960</v>
       </c>
       <c r="C4" s="6" t="n">
         <f aca="false">SUM(Assumptions!$J$12:$J$15)</f>
-        <v>7410</v>
+        <v>4915</v>
       </c>
       <c r="D4" s="7" t="n">
         <f aca="false">B4+C4</f>
-        <v>39150</v>
+        <v>26875</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1420,15 +1418,15 @@
       </c>
       <c r="B8" s="8" t="n">
         <f aca="false">SUM(Assumptions!$J$8:$J$11)*Assumptions!$B$3</f>
-        <v>380880</v>
+        <v>263520</v>
       </c>
       <c r="C8" s="8" t="n">
         <f aca="false">SUM(Assumptions!$J$12:$J$15)*Assumptions!$B$3</f>
-        <v>88920</v>
+        <v>58980</v>
       </c>
       <c r="D8" s="9" t="n">
         <f aca="false">B8+C8</f>
-        <v>469800</v>
+        <v>322500</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1437,15 +1435,15 @@
       </c>
       <c r="B9" s="8" t="n">
         <f aca="false">SUMPRODUCT(Assumptions!$J$8:$J$11,Assumptions!$G$8:$G$11)</f>
-        <v>226000</v>
+        <v>158240</v>
       </c>
       <c r="C9" s="8" t="n">
         <f aca="false">SUMPRODUCT(Assumptions!$J$12:$J$15,Assumptions!$G$12:$G$15)</f>
-        <v>53610</v>
+        <v>35690</v>
       </c>
       <c r="D9" s="9" t="n">
         <f aca="false">B9+C9</f>
-        <v>279610</v>
+        <v>193930</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1454,15 +1452,15 @@
       </c>
       <c r="B10" s="8" t="n">
         <f aca="false">SUMPRODUCT(Assumptions!$J$8:$J$11,Assumptions!$H$8:$H$11)</f>
-        <v>73620</v>
+        <v>48120</v>
       </c>
       <c r="C10" s="8" t="n">
         <f aca="false">SUMPRODUCT(Assumptions!$J$12:$J$15,Assumptions!$H$12:$H$15)</f>
-        <v>10245</v>
+        <v>0</v>
       </c>
       <c r="D10" s="9" t="n">
         <f aca="false">B10+C10</f>
-        <v>83865</v>
+        <v>48120</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1471,15 +1469,15 @@
       </c>
       <c r="B11" s="8" t="n">
         <f aca="false">SUMPRODUCT(Assumptions!$J$8:$J$11,Assumptions!$I$8:$I$11)</f>
-        <v>326360</v>
+        <v>171200</v>
       </c>
       <c r="C11" s="8" t="n">
         <f aca="false">SUMPRODUCT(Assumptions!$J$12:$J$15,Assumptions!$I$12:$I$15)</f>
-        <v>81705</v>
+        <v>20600</v>
       </c>
       <c r="D11" s="9" t="n">
         <f aca="false">B11+C11</f>
-        <v>408065</v>
+        <v>191800</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1505,15 +1503,15 @@
       </c>
       <c r="B13" s="10" t="n">
         <f aca="false">SUM(B8:B12)</f>
-        <v>1066860</v>
+        <v>701080</v>
       </c>
       <c r="C13" s="10" t="n">
         <f aca="false">SUM(C8:C12)</f>
-        <v>264480</v>
+        <v>145270</v>
       </c>
       <c r="D13" s="10" t="n">
         <f aca="false">B13+C13</f>
-        <v>1331340</v>
+        <v>846350</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1527,15 +1525,15 @@
       </c>
       <c r="B16" s="9" t="n">
         <f aca="false">B8*Assumptions!$B$19</f>
-        <v>361836</v>
+        <v>250344</v>
       </c>
       <c r="C16" s="9" t="n">
         <f aca="false">C8*Assumptions!$B$19</f>
-        <v>84474</v>
+        <v>56031</v>
       </c>
       <c r="D16" s="9" t="n">
         <f aca="false">B16+C16</f>
-        <v>446310</v>
+        <v>306375</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1544,15 +1542,15 @@
       </c>
       <c r="B17" s="9" t="n">
         <f aca="false">B9*Assumptions!$B$20</f>
-        <v>33900</v>
+        <v>23736</v>
       </c>
       <c r="C17" s="9" t="n">
         <f aca="false">C9*Assumptions!$B$20</f>
-        <v>8041.5</v>
+        <v>5353.5</v>
       </c>
       <c r="D17" s="9" t="n">
         <f aca="false">B17+C17</f>
-        <v>41941.5</v>
+        <v>29089.5</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1561,15 +1559,15 @@
       </c>
       <c r="B18" s="9" t="n">
         <f aca="false">B10*Assumptions!$B$21</f>
-        <v>51534</v>
+        <v>33684</v>
       </c>
       <c r="C18" s="9" t="n">
         <f aca="false">C10*Assumptions!$B$21</f>
-        <v>7171.5</v>
+        <v>0</v>
       </c>
       <c r="D18" s="9" t="n">
         <f aca="false">B18+C18</f>
-        <v>58705.5</v>
+        <v>33684</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1578,15 +1576,15 @@
       </c>
       <c r="B19" s="9" t="n">
         <f aca="false">B11*Assumptions!$B$22</f>
-        <v>248033.6</v>
+        <v>130112</v>
       </c>
       <c r="C19" s="9" t="n">
         <f aca="false">C11*Assumptions!$B$22</f>
-        <v>62095.8</v>
+        <v>15656</v>
       </c>
       <c r="D19" s="9" t="n">
         <f aca="false">B19+C19</f>
-        <v>310129.4</v>
+        <v>145768</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1612,15 +1610,15 @@
       </c>
       <c r="B21" s="10" t="n">
         <f aca="false">SUM(B16:B20)</f>
-        <v>740303.6</v>
+        <v>482876</v>
       </c>
       <c r="C21" s="10" t="n">
         <f aca="false">SUM(C16:C20)</f>
-        <v>184282.8</v>
+        <v>99540.5</v>
       </c>
       <c r="D21" s="10" t="n">
         <f aca="false">B21+C21</f>
-        <v>924586.4</v>
+        <v>582416.5</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1629,15 +1627,15 @@
       </c>
       <c r="B22" s="11" t="n">
         <f aca="false">IF(B13=0,0,B21/B13)</f>
-        <v>0.693908854020209</v>
+        <v>0.688760198550807</v>
       </c>
       <c r="C22" s="11" t="n">
         <f aca="false">IF(C13=0,0,C21/C13)</f>
-        <v>0.696774047186933</v>
+        <v>0.685210298065671</v>
       </c>
       <c r="D22" s="11" t="n">
         <f aca="false">IF(D13=0,0,D21/D13)</f>
-        <v>0.694478044676792</v>
+        <v>0.688150883204348</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1650,16 +1648,16 @@
         <v>39</v>
       </c>
       <c r="B25" s="8" t="n">
-        <f aca="false">Labor!$H$14*B5/$D$5</f>
-        <v>171861.066666667</v>
+        <f aca="false">Labor!$K$20*Labor!$C$3*(1+Assumptions!$B$33)</f>
+        <v>100023</v>
       </c>
       <c r="C25" s="8" t="n">
-        <f aca="false">Labor!$H$14*C5/$D$5</f>
-        <v>85930.5333333334</v>
+        <f aca="false">Labor!$L$20*Labor!$C$3*(1+Assumptions!$B$33)</f>
+        <v>30574.5</v>
       </c>
       <c r="D25" s="9" t="n">
         <f aca="false">B25+C25</f>
-        <v>257791.6</v>
+        <v>130597.5</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1667,11 +1665,11 @@
         <v>40</v>
       </c>
       <c r="B26" s="8" t="n">
-        <f aca="false">Labor!$H$20*8/12</f>
+        <f aca="false">Labor!$M$28*8/12</f>
         <v>103293.333333333</v>
       </c>
       <c r="C26" s="8" t="n">
-        <f aca="false">Labor!$H$20*4/12</f>
+        <f aca="false">Labor!$M$28*4/12</f>
         <v>51646.6666666667</v>
       </c>
       <c r="D26" s="9" t="n">
@@ -1702,15 +1700,15 @@
       </c>
       <c r="B28" s="9" t="n">
         <f aca="false">(B13-B9)*Assumptions!$B$26</f>
-        <v>23123.65</v>
+        <v>14928.1</v>
       </c>
       <c r="C28" s="9" t="n">
         <f aca="false">(C13-C9)*Assumptions!$B$26</f>
-        <v>5798.925</v>
+        <v>3013.45</v>
       </c>
       <c r="D28" s="9" t="n">
         <f aca="false">B28+C28</f>
-        <v>28922.575</v>
+        <v>17941.55</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1719,15 +1717,15 @@
       </c>
       <c r="B29" s="9" t="n">
         <f aca="false">B13*Assumptions!$B$27</f>
-        <v>42674.4</v>
+        <v>28043.2</v>
       </c>
       <c r="C29" s="9" t="n">
         <f aca="false">C13*Assumptions!$B$27</f>
-        <v>10579.2</v>
+        <v>5810.8</v>
       </c>
       <c r="D29" s="9" t="n">
         <f aca="false">B29+C29</f>
-        <v>53253.6</v>
+        <v>33854</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1736,15 +1734,15 @@
       </c>
       <c r="B30" s="10" t="n">
         <f aca="false">SUM(B25:B29)</f>
-        <v>460014.716666667</v>
+        <v>365349.9</v>
       </c>
       <c r="C30" s="10" t="n">
         <f aca="false">SUM(C25:C29)</f>
-        <v>213486.458333333</v>
+        <v>150576.55</v>
       </c>
       <c r="D30" s="10" t="n">
         <f aca="false">B30+C30</f>
-        <v>673501.175</v>
+        <v>515926.45</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1753,15 +1751,15 @@
       </c>
       <c r="B32" s="12" t="n">
         <f aca="false">B21-B30</f>
-        <v>280288.883333333</v>
+        <v>117526.1</v>
       </c>
       <c r="C32" s="12" t="n">
         <f aca="false">C21-C30</f>
-        <v>-29203.6583333334</v>
+        <v>-51036.05</v>
       </c>
       <c r="D32" s="12" t="n">
         <f aca="false">B32+C32</f>
-        <v>251085.225</v>
+        <v>66490.05</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1770,15 +1768,15 @@
       </c>
       <c r="B33" s="11" t="n">
         <f aca="false">IF(B13=0,0,B32/B13)</f>
-        <v>0.26272320954327</v>
+        <v>0.167635790494665</v>
       </c>
       <c r="C33" s="11" t="n">
         <f aca="false">IF(C13=0,0,C32/C13)</f>
-        <v>-0.110419155827788</v>
+        <v>-0.351318579197357</v>
       </c>
       <c r="D33" s="11" t="n">
         <f aca="false">IF(D13=0,0,D32/D13)</f>
-        <v>0.188595869575015</v>
+        <v>0.078560938146157</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1804,15 +1802,15 @@
       </c>
       <c r="B35" s="10" t="n">
         <f aca="false">B32-B34</f>
-        <v>165576.542773657</v>
+        <v>2813.75944032341</v>
       </c>
       <c r="C35" s="10" t="n">
         <f aca="false">C32-C34</f>
-        <v>-86559.8286131717</v>
+        <v>-108392.220279838</v>
       </c>
       <c r="D35" s="10" t="n">
         <f aca="false">B35+C35</f>
-        <v>79016.714160485</v>
+        <v>-105578.460839515</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1825,8 +1823,8 @@
         <v>50</v>
       </c>
       <c r="D38" s="11" t="n">
-        <f aca="false">IF(D13=0,0,Labor!$H$22/D13)</f>
-        <v>0.310012168191446</v>
+        <f aca="false">IF(D13=0,0,Labor!$M$32/D13)</f>
+        <v>0.337375199385597</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1835,7 +1833,7 @@
       </c>
       <c r="D39" s="13" t="n">
         <f aca="false">IF(D4=0,0,D13/D4)</f>
-        <v>34.0061302681992</v>
+        <v>31.4920930232558</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1844,7 +1842,7 @@
       </c>
       <c r="D40" s="14" t="n">
         <f aca="false">IF(D34=0,0,D32/D34)</f>
-        <v>1.45921658631766</v>
+        <v>0.386416141312538</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1853,7 +1851,7 @@
       </c>
       <c r="D41" s="11" t="n">
         <f aca="false">IF(Financing!$B$6=0,0,D35/Financing!$B$6)</f>
-        <v>0.0929389721953481</v>
+        <v>-0.124180734932386</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1912,23 +1910,23 @@
       </c>
       <c r="B47" s="12" t="n">
         <f aca="false">$D$13*B46</f>
-        <v>998505</v>
+        <v>634762.5</v>
       </c>
       <c r="C47" s="12" t="n">
         <f aca="false">$D$13*C46</f>
-        <v>1198206</v>
+        <v>761715</v>
       </c>
       <c r="D47" s="12" t="n">
         <f aca="false">$D$13*D46</f>
-        <v>1331340</v>
+        <v>846350</v>
       </c>
       <c r="E47" s="12" t="n">
         <f aca="false">$D$13*E46</f>
-        <v>1371280.2</v>
+        <v>871740.5</v>
       </c>
       <c r="F47" s="12" t="n">
         <f aca="false">$D$13*F46</f>
-        <v>1411220.4</v>
+        <v>897131</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1937,23 +1935,23 @@
       </c>
       <c r="B48" s="9" t="n">
         <f aca="false">$D$21*B46</f>
-        <v>693439.8</v>
+        <v>436812.375</v>
       </c>
       <c r="C48" s="9" t="n">
         <f aca="false">$D$21*C46</f>
-        <v>832127.76</v>
+        <v>524174.85</v>
       </c>
       <c r="D48" s="9" t="n">
         <f aca="false">$D$21*D46</f>
-        <v>924586.4</v>
+        <v>582416.5</v>
       </c>
       <c r="E48" s="9" t="n">
         <f aca="false">$D$21*E46</f>
-        <v>952323.992</v>
+        <v>599888.995</v>
       </c>
       <c r="F48" s="9" t="n">
         <f aca="false">$D$21*F46</f>
-        <v>980061.584</v>
+        <v>617361.49</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1961,24 +1959,24 @@
         <v>62</v>
       </c>
       <c r="B49" s="8" t="n">
-        <f aca="false">Labor!$H$22*(1+Assumptions!$B$38)^0</f>
-        <v>412731.6</v>
+        <f aca="false">Labor!$M$32*(1+Assumptions!$B$38)^0</f>
+        <v>285537.5</v>
       </c>
       <c r="C49" s="8" t="n">
-        <f aca="false">Labor!$H$22*(1+Assumptions!$B$38)^1</f>
-        <v>425113.548</v>
+        <f aca="false">Labor!$M$32*(1+Assumptions!$B$38)^1</f>
+        <v>294103.625</v>
       </c>
       <c r="D49" s="8" t="n">
-        <f aca="false">Labor!$H$22*(1+Assumptions!$B$38)^2</f>
-        <v>437866.95444</v>
+        <f aca="false">Labor!$M$32*(1+Assumptions!$B$38)^2</f>
+        <v>302926.73375</v>
       </c>
       <c r="E49" s="8" t="n">
-        <f aca="false">Labor!$H$22*(1+Assumptions!$B$38)^3</f>
-        <v>451002.9630732</v>
+        <f aca="false">Labor!$M$32*(1+Assumptions!$B$38)^3</f>
+        <v>312014.5357625</v>
       </c>
       <c r="F49" s="8" t="n">
-        <f aca="false">Labor!$H$22*(1+Assumptions!$B$38)^4</f>
-        <v>464533.051965396</v>
+        <f aca="false">Labor!$M$32*(1+Assumptions!$B$38)^4</f>
+        <v>321374.971835375</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2012,23 +2010,23 @@
       </c>
       <c r="B51" s="9" t="n">
         <f aca="false">(SUM($D$28:$D$29))*B46</f>
-        <v>61632.13125</v>
+        <v>38846.6625</v>
       </c>
       <c r="C51" s="9" t="n">
         <f aca="false">(SUM($D$28:$D$29))*C46</f>
-        <v>73958.5575</v>
+        <v>46615.995</v>
       </c>
       <c r="D51" s="9" t="n">
         <f aca="false">(SUM($D$28:$D$29))*D46</f>
-        <v>82176.175</v>
+        <v>51795.55</v>
       </c>
       <c r="E51" s="9" t="n">
         <f aca="false">(SUM($D$28:$D$29))*E46</f>
-        <v>84641.46025</v>
+        <v>53349.4165</v>
       </c>
       <c r="F51" s="9" t="n">
         <f aca="false">(SUM($D$28:$D$29))*F46</f>
-        <v>87106.7455</v>
+        <v>54903.283</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2037,23 +2035,23 @@
       </c>
       <c r="B52" s="10" t="n">
         <f aca="false">B48-B49-B50-B51</f>
-        <v>40482.6687499999</v>
+        <v>-66165.1875</v>
       </c>
       <c r="C52" s="10" t="n">
         <f aca="false">C48-C49-C50-C51</f>
-        <v>149104.4525</v>
+        <v>-495.971999999958</v>
       </c>
       <c r="D52" s="10" t="n">
         <f aca="false">D48-D49-D50-D51</f>
-        <v>215073.5325</v>
+        <v>38224.47819</v>
       </c>
       <c r="E52" s="10" t="n">
         <f aca="false">E48-E49-E50-E51</f>
-        <v>221525.738475</v>
+        <v>39371.2125357</v>
       </c>
       <c r="F52" s="10" t="n">
         <f aca="false">F48-F49-F50-F51</f>
-        <v>227413.34142675</v>
+        <v>40074.7900567709</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2087,23 +2085,23 @@
       </c>
       <c r="B54" s="10" t="n">
         <f aca="false">B52-B53</f>
-        <v>-131585.842089515</v>
+        <v>-238233.698339515</v>
       </c>
       <c r="C54" s="10" t="n">
         <f aca="false">C52-C53</f>
-        <v>-22964.058339515</v>
+        <v>-172564.482839515</v>
       </c>
       <c r="D54" s="10" t="n">
         <f aca="false">D52-D53</f>
-        <v>43005.0216604851</v>
+        <v>-133844.032649515</v>
       </c>
       <c r="E54" s="10" t="n">
         <f aca="false">E52-E53</f>
-        <v>49457.2276354851</v>
+        <v>-132697.298303815</v>
       </c>
       <c r="F54" s="10" t="n">
         <f aca="false">F52-F53</f>
-        <v>55344.8305872349</v>
+        <v>-131993.720782744</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2112,23 +2110,23 @@
       </c>
       <c r="B55" s="9" t="n">
         <f aca="false">B54</f>
-        <v>-131585.842089515</v>
+        <v>-238233.698339515</v>
       </c>
       <c r="C55" s="9" t="n">
         <f aca="false">B55+C54</f>
-        <v>-154549.90042903</v>
+        <v>-410798.18117903</v>
       </c>
       <c r="D55" s="9" t="n">
         <f aca="false">C55+D54</f>
-        <v>-111544.878768545</v>
+        <v>-544642.213828545</v>
       </c>
       <c r="E55" s="9" t="n">
         <f aca="false">D55+E54</f>
-        <v>-62087.6511330598</v>
+        <v>-677339.512132359</v>
       </c>
       <c r="F55" s="9" t="n">
         <f aca="false">E55+F54</f>
-        <v>-6742.82054582483</v>
+        <v>-809333.232915103</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2137,23 +2135,23 @@
       </c>
       <c r="B56" s="9" t="n">
         <f aca="false">Financing!$B$6-B55</f>
-        <v>981785.842089515</v>
+        <v>1088433.69833952</v>
       </c>
       <c r="C56" s="9" t="n">
         <f aca="false">Financing!$B$6-C55</f>
-        <v>1004749.90042903</v>
+        <v>1260998.18117903</v>
       </c>
       <c r="D56" s="9" t="n">
         <f aca="false">Financing!$B$6-D55</f>
-        <v>961744.878768545</v>
+        <v>1394842.21382854</v>
       </c>
       <c r="E56" s="9" t="n">
         <f aca="false">Financing!$B$6-E55</f>
-        <v>912287.65113306</v>
+        <v>1527539.51213236</v>
       </c>
       <c r="F56" s="9" t="n">
         <f aca="false">Financing!$B$6-F55</f>
-        <v>856942.820545825</v>
+        <v>1659533.2329151</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2280,7 +2278,7 @@
         <v>5</v>
       </c>
       <c r="F8" s="19" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G8" s="20" t="n">
         <v>6</v>
@@ -2289,15 +2287,15 @@
         <v>4</v>
       </c>
       <c r="I8" s="20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J8" s="7" t="n">
         <f aca="false">D8*F8</f>
-        <v>4160</v>
+        <v>3120</v>
       </c>
       <c r="K8" s="9" t="n">
         <f aca="false">J8*(Assumptions!$B$3+G8+H8+I8)</f>
-        <v>104000</v>
+        <v>68640</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2317,7 +2315,7 @@
         <v>6</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G9" s="20" t="n">
         <v>8</v>
@@ -2326,15 +2324,15 @@
         <v>1</v>
       </c>
       <c r="I9" s="20" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="J9" s="7" t="n">
         <f aca="false">D9*F9</f>
-        <v>7280</v>
+        <v>6240</v>
       </c>
       <c r="K9" s="9" t="n">
         <f aca="false">J9*(Assumptions!$B$3+G9+H9+I9)</f>
-        <v>269360</v>
+        <v>162240</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2354,7 +2352,7 @@
         <v>5</v>
       </c>
       <c r="F10" s="19" t="n">
-        <v>140</v>
+        <v>80</v>
       </c>
       <c r="G10" s="20" t="n">
         <v>6</v>
@@ -2363,15 +2361,15 @@
         <v>4</v>
       </c>
       <c r="I10" s="20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J10" s="7" t="n">
         <f aca="false">D10*F10</f>
-        <v>9800</v>
+        <v>5600</v>
       </c>
       <c r="K10" s="9" t="n">
         <f aca="false">J10*(Assumptions!$B$3+G10+H10+I10)</f>
-        <v>245000</v>
+        <v>151200</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2391,7 +2389,7 @@
         <v>6</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="G11" s="20" t="n">
         <v>8</v>
@@ -2404,11 +2402,11 @@
       </c>
       <c r="J11" s="7" t="n">
         <f aca="false">D11*F11</f>
-        <v>10500</v>
+        <v>7000</v>
       </c>
       <c r="K11" s="9" t="n">
         <f aca="false">J11*(Assumptions!$B$3+G11+H11+I11)</f>
-        <v>388500</v>
+        <v>259000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2434,10 +2432,10 @@
         <v>6</v>
       </c>
       <c r="H12" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I12" s="20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J12" s="7" t="n">
         <f aca="false">D12*F12</f>
@@ -2445,7 +2443,7 @@
       </c>
       <c r="K12" s="9" t="n">
         <f aca="false">J12*(Assumptions!$B$3+G12+H12+I12)</f>
-        <v>18285</v>
+        <v>14310</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2465,24 +2463,24 @@
         <v>6</v>
       </c>
       <c r="F13" s="19" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="G13" s="20" t="n">
         <v>8</v>
       </c>
       <c r="H13" s="20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" s="20" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="J13" s="7" t="n">
         <f aca="false">D13*F13</f>
-        <v>1855</v>
+        <v>1060</v>
       </c>
       <c r="K13" s="9" t="n">
         <f aca="false">J13*(Assumptions!$B$3+G13+H13+I13)</f>
-        <v>68635</v>
+        <v>26500</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2502,24 +2500,24 @@
         <v>5</v>
       </c>
       <c r="F14" s="19" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G14" s="20" t="n">
         <v>6</v>
       </c>
       <c r="H14" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I14" s="20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J14" s="7" t="n">
         <f aca="false">D14*F14</f>
-        <v>2040</v>
+        <v>1020</v>
       </c>
       <c r="K14" s="9" t="n">
         <f aca="false">J14*(Assumptions!$B$3+G14+H14+I14)</f>
-        <v>46920</v>
+        <v>23460</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2539,24 +2537,24 @@
         <v>6</v>
       </c>
       <c r="F15" s="19" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="G15" s="20" t="n">
         <v>8</v>
       </c>
       <c r="H15" s="20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" s="20" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="J15" s="7" t="n">
         <f aca="false">D15*F15</f>
-        <v>2720</v>
+        <v>2040</v>
       </c>
       <c r="K15" s="9" t="n">
         <f aca="false">J15*(Assumptions!$B$3+G15+H15+I15)</f>
-        <v>100640</v>
+        <v>51000</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2565,11 +2563,11 @@
       </c>
       <c r="J16" s="21" t="n">
         <f aca="false">SUM(J8:J15)</f>
-        <v>39150</v>
+        <v>26875</v>
       </c>
       <c r="K16" s="10" t="n">
         <f aca="false">SUM(K8:K15)</f>
-        <v>1241340</v>
+        <v>756350</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2868,357 +2866,766 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="9" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="C3" s="16" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="B5" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E5" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G5" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H5" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="I3" s="5" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="I5" s="5" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="J5" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="B5" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" s="7" t="n">
-        <f aca="false">B5*(Assumptions!$D$8*Assumptions!$E$8+Assumptions!$D$12*Assumptions!$E$12)+C5*(Assumptions!$D$9*Assumptions!$E$9+Assumptions!$D$13*Assumptions!$E$13)+D5*(Assumptions!$D$10*Assumptions!$E$10+Assumptions!$D$14*Assumptions!$E$14)+E5*(Assumptions!$D$11*Assumptions!$E$11+Assumptions!$D$15*Assumptions!$E$15)</f>
-        <v>5581</v>
-      </c>
-      <c r="G5" s="20" t="n">
-        <v>15</v>
-      </c>
-      <c r="H5" s="9" t="n">
-        <f aca="false">F5*G5</f>
-        <v>83715</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="K5" s="5" t="s">
         <v>141</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="B6" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="F6" s="7" t="n">
-        <f aca="false">B6*(Assumptions!$D$8*Assumptions!$E$8+Assumptions!$D$12*Assumptions!$E$12)+C6*(Assumptions!$D$9*Assumptions!$E$9+Assumptions!$D$13*Assumptions!$E$13)+D6*(Assumptions!$D$10*Assumptions!$E$10+Assumptions!$D$14*Assumptions!$E$14)+E6*(Assumptions!$D$11*Assumptions!$E$11+Assumptions!$D$15*Assumptions!$E$15)</f>
-        <v>5061</v>
-      </c>
-      <c r="G6" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="H6" s="9" t="n">
-        <f aca="false">F6*G6</f>
-        <v>35427</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="K6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="B7" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="17" t="n">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="K7" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="7" t="n">
-        <f aca="false">B7*(Assumptions!$D$8*Assumptions!$E$8+Assumptions!$D$12*Assumptions!$E$12)+C7*(Assumptions!$D$9*Assumptions!$E$9+Assumptions!$D$13*Assumptions!$E$13)+D7*(Assumptions!$D$10*Assumptions!$E$10+Assumptions!$D$14*Assumptions!$E$14)+E7*(Assumptions!$D$11*Assumptions!$E$11+Assumptions!$D$15*Assumptions!$E$15)</f>
-        <v>2449</v>
-      </c>
-      <c r="G7" s="20" t="n">
-        <v>14</v>
-      </c>
-      <c r="H7" s="9" t="n">
-        <f aca="false">F7*G7</f>
-        <v>34286</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>145</v>
+      <c r="L7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="B8" s="17" t="n">
+      <c r="B8" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="K8" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" s="7" t="n">
-        <f aca="false">B8*(Assumptions!$D$8*Assumptions!$E$8+Assumptions!$D$12*Assumptions!$E$12)+C8*(Assumptions!$D$9*Assumptions!$E$9+Assumptions!$D$13*Assumptions!$E$13)+D8*(Assumptions!$D$10*Assumptions!$E$10+Assumptions!$D$14*Assumptions!$E$14)+E8*(Assumptions!$D$11*Assumptions!$E$11+Assumptions!$D$15*Assumptions!$E$15)</f>
-        <v>2710</v>
-      </c>
-      <c r="G8" s="20" t="n">
-        <v>15</v>
-      </c>
-      <c r="H8" s="9" t="n">
-        <f aca="false">F8*G8</f>
-        <v>40650</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>147</v>
+      <c r="L8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="B9" s="17" t="n">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="K9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="17" t="n">
+      <c r="L9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="M9" s="9" t="n">
         <v>0</v>
-      </c>
-      <c r="E9" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="7" t="n">
-        <f aca="false">B9*(Assumptions!$D$8*Assumptions!$E$8+Assumptions!$D$12*Assumptions!$E$12)+C9*(Assumptions!$D$9*Assumptions!$E$9+Assumptions!$D$13*Assumptions!$E$13)+D9*(Assumptions!$D$10*Assumptions!$E$10+Assumptions!$D$14*Assumptions!$E$14)+E9*(Assumptions!$D$11*Assumptions!$E$11+Assumptions!$D$15*Assumptions!$E$15)</f>
-        <v>624</v>
-      </c>
-      <c r="G9" s="20" t="n">
-        <v>22</v>
-      </c>
-      <c r="H9" s="9" t="n">
-        <f aca="false">F9*G9</f>
-        <v>13728</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" s="27" t="n">
+        <f aca="false">Assumptions!$D$8/3</f>
+        <v>34.6666666666667</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <f aca="false">Assumptions!$F$8</f>
+        <v>30</v>
+      </c>
+      <c r="F10" s="28" t="n">
+        <f aca="false">IF(C10=0,0,E10/C10)</f>
+        <v>6</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" s="27" t="n">
+        <f aca="false">Assumptions!$D$12/3</f>
+        <v>17.6666666666667</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <f aca="false">Assumptions!$F$12</f>
+        <v>15</v>
+      </c>
+      <c r="J10" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="7" t="n">
+        <f aca="false">C10*D10*G10</f>
+        <v>346.666666666667</v>
+      </c>
+      <c r="L10" s="7" t="n">
+        <f aca="false">C10*H10*J10</f>
+        <v>88.3333333333333</v>
+      </c>
+      <c r="M10" s="9" t="n">
+        <f aca="false">(K10+L10)*Labor!$C$3</f>
+        <v>6525</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D11" s="27" t="n">
+        <f aca="false">Assumptions!$D$9/3</f>
+        <v>34.6666666666667</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <f aca="false">Assumptions!$F$9</f>
+        <v>60</v>
+      </c>
+      <c r="F11" s="28" t="n">
+        <f aca="false">IF(C11=0,0,E11/C11)</f>
+        <v>10</v>
+      </c>
+      <c r="G11" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" s="27" t="n">
+        <f aca="false">Assumptions!$D$13/3</f>
+        <v>17.6666666666667</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <f aca="false">Assumptions!$F$13</f>
+        <v>20</v>
+      </c>
+      <c r="J11" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" s="7" t="n">
+        <f aca="false">C11*D11*G11</f>
+        <v>624</v>
+      </c>
+      <c r="L11" s="7" t="n">
+        <f aca="false">C11*H11*J11</f>
+        <v>212</v>
+      </c>
+      <c r="M11" s="9" t="n">
+        <f aca="false">(K11+L11)*Labor!$C$3</f>
+        <v>12540</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" s="27" t="n">
+        <f aca="false">Assumptions!$D$8/3</f>
+        <v>34.6666666666667</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <f aca="false">Assumptions!$F$8</f>
+        <v>30</v>
+      </c>
+      <c r="F12" s="28" t="n">
+        <f aca="false">IF(C12=0,0,E12/C12)</f>
+        <v>6</v>
+      </c>
+      <c r="G12" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" s="27" t="n">
+        <f aca="false">Assumptions!$D$12/3</f>
+        <v>17.6666666666667</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <f aca="false">Assumptions!$F$12</f>
+        <v>15</v>
+      </c>
+      <c r="J12" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="7" t="n">
+        <f aca="false">C12*D12*G12</f>
+        <v>346.666666666667</v>
+      </c>
+      <c r="L12" s="7" t="n">
+        <f aca="false">C12*H12*J12</f>
+        <v>88.3333333333333</v>
+      </c>
+      <c r="M12" s="9" t="n">
+        <f aca="false">(K12+L12)*Labor!$C$3</f>
+        <v>6525</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D13" s="27" t="n">
+        <f aca="false">Assumptions!$D$9/3</f>
+        <v>34.6666666666667</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <f aca="false">Assumptions!$F$9</f>
+        <v>60</v>
+      </c>
+      <c r="F13" s="28" t="n">
+        <f aca="false">IF(C13=0,0,E13/C13)</f>
+        <v>10</v>
+      </c>
+      <c r="G13" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" s="27" t="n">
+        <f aca="false">Assumptions!$D$13/3</f>
+        <v>17.6666666666667</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <f aca="false">Assumptions!$F$13</f>
+        <v>20</v>
+      </c>
+      <c r="J13" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" s="7" t="n">
+        <f aca="false">C13*D13*G13</f>
+        <v>624</v>
+      </c>
+      <c r="L13" s="7" t="n">
+        <f aca="false">C13*H13*J13</f>
+        <v>212</v>
+      </c>
+      <c r="M13" s="9" t="n">
+        <f aca="false">(K13+L13)*Labor!$C$3</f>
+        <v>12540</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D14" s="27" t="n">
+        <f aca="false">Assumptions!$D$8/3</f>
+        <v>34.6666666666667</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <f aca="false">Assumptions!$F$8</f>
+        <v>30</v>
+      </c>
+      <c r="F14" s="28" t="n">
+        <f aca="false">IF(C14=0,0,E14/C14)</f>
+        <v>6</v>
+      </c>
+      <c r="G14" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" s="27" t="n">
+        <f aca="false">Assumptions!$D$12/3</f>
+        <v>17.6666666666667</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <f aca="false">Assumptions!$F$12</f>
+        <v>15</v>
+      </c>
+      <c r="J14" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" s="7" t="n">
+        <f aca="false">C14*D14*G14</f>
+        <v>346.666666666667</v>
+      </c>
+      <c r="L14" s="7" t="n">
+        <f aca="false">C14*H14*J14</f>
+        <v>88.3333333333333</v>
+      </c>
+      <c r="M14" s="9" t="n">
+        <f aca="false">(K14+L14)*Labor!$C$3</f>
+        <v>6525</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D15" s="27" t="n">
+        <f aca="false">Assumptions!$D$9/3</f>
+        <v>34.6666666666667</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <f aca="false">Assumptions!$F$9</f>
+        <v>60</v>
+      </c>
+      <c r="F15" s="28" t="n">
+        <f aca="false">IF(C15=0,0,E15/C15)</f>
+        <v>10</v>
+      </c>
+      <c r="G15" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" s="27" t="n">
+        <f aca="false">Assumptions!$D$13/3</f>
+        <v>17.6666666666667</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <f aca="false">Assumptions!$F$13</f>
+        <v>20</v>
+      </c>
+      <c r="J15" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" s="7" t="n">
+        <f aca="false">C15*D15*G15</f>
+        <v>624</v>
+      </c>
+      <c r="L15" s="7" t="n">
+        <f aca="false">C15*H15*J15</f>
+        <v>212</v>
+      </c>
+      <c r="M15" s="9" t="n">
+        <f aca="false">(K15+L15)*Labor!$C$3</f>
+        <v>12540</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="B10" s="17" t="n">
+      <c r="B16" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" s="27" t="n">
+        <f aca="false">Assumptions!$D$10/2</f>
+        <v>35</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <f aca="false">Assumptions!$F$10</f>
+        <v>80</v>
+      </c>
+      <c r="F16" s="28" t="n">
+        <f aca="false">IF(C16=0,0,E16/C16)</f>
+        <v>16</v>
+      </c>
+      <c r="G16" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H16" s="27" t="n">
+        <f aca="false">Assumptions!$D$14/2</f>
+        <v>17</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <f aca="false">Assumptions!$F$14</f>
+        <v>30</v>
+      </c>
+      <c r="J16" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="7" t="n">
-        <f aca="false">B10*C10*(Assumptions!$D$8+Assumptions!$D$10+Assumptions!$D$12+Assumptions!$D$14)</f>
-        <v>522</v>
-      </c>
-      <c r="G10" s="20" t="n">
-        <v>15</v>
-      </c>
-      <c r="H10" s="9" t="n">
-        <f aca="false">F10*G10</f>
-        <v>7830</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="B11" s="17" t="n">
-        <v>20</v>
-      </c>
-      <c r="F11" s="7" t="n">
-        <f aca="false">B11*Assumptions!$B$32</f>
-        <v>1040</v>
-      </c>
-      <c r="G11" s="20" t="n">
-        <v>18</v>
-      </c>
-      <c r="H11" s="9" t="n">
-        <f aca="false">F11*G11</f>
-        <v>18720</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="F12" s="21" t="n">
-        <f aca="false">SUM(F5:F11)</f>
-        <v>17987</v>
-      </c>
-      <c r="H12" s="10" t="n">
-        <f aca="false">SUM(H5:H11)</f>
-        <v>234356</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="H13" s="9" t="n">
-        <f aca="false">Labor!$H$12*Assumptions!$B$33</f>
-        <v>23435.6</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="H14" s="12" t="n">
-        <f aca="false">Labor!$H$12*(1+Assumptions!$B$33)</f>
-        <v>257791.6</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>92</v>
+      <c r="K16" s="7" t="n">
+        <f aca="false">C16*D16*G16</f>
+        <v>525</v>
+      </c>
+      <c r="L16" s="7" t="n">
+        <f aca="false">C16*H16*J16</f>
+        <v>170</v>
+      </c>
+      <c r="M16" s="9" t="n">
+        <f aca="false">(K16+L16)*Labor!$C$3</f>
+        <v>10425</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="H17" s="18" t="n">
-        <v>70000</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>160</v>
+      <c r="A17" s="3"/>
+      <c r="B17" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D17" s="27" t="n">
+        <f aca="false">Assumptions!$D$11/2</f>
+        <v>35</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <f aca="false">Assumptions!$F$11</f>
+        <v>100</v>
+      </c>
+      <c r="F17" s="28" t="n">
+        <f aca="false">IF(C17=0,0,E17/C17)</f>
+        <v>16.6666666666667</v>
+      </c>
+      <c r="G17" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H17" s="27" t="n">
+        <f aca="false">Assumptions!$D$15/2</f>
+        <v>17</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <f aca="false">Assumptions!$F$15</f>
+        <v>60</v>
+      </c>
+      <c r="J17" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" s="7" t="n">
+        <f aca="false">C17*D17*G17</f>
+        <v>1050</v>
+      </c>
+      <c r="L17" s="7" t="n">
+        <f aca="false">C17*H17*J17</f>
+        <v>306</v>
+      </c>
+      <c r="M17" s="9" t="n">
+        <f aca="false">(K17+L17)*Labor!$C$3</f>
+        <v>20340</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="H18" s="18" t="n">
-        <v>50000</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>162</v>
+        <v>151</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" s="27" t="n">
+        <f aca="false">Assumptions!$D$10/2</f>
+        <v>35</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <f aca="false">Assumptions!$F$10</f>
+        <v>80</v>
+      </c>
+      <c r="F18" s="28" t="n">
+        <f aca="false">IF(C18=0,0,E18/C18)</f>
+        <v>16</v>
+      </c>
+      <c r="G18" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H18" s="27" t="n">
+        <f aca="false">Assumptions!$D$14/2</f>
+        <v>17</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <f aca="false">Assumptions!$F$14</f>
+        <v>30</v>
+      </c>
+      <c r="J18" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" s="7" t="n">
+        <f aca="false">C18*D18*G18</f>
+        <v>525</v>
+      </c>
+      <c r="L18" s="7" t="n">
+        <f aca="false">C18*H18*J18</f>
+        <v>170</v>
+      </c>
+      <c r="M18" s="9" t="n">
+        <f aca="false">(K18+L18)*Labor!$C$3</f>
+        <v>10425</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="H19" s="18" t="n">
-        <v>7000</v>
+      <c r="A19" s="3"/>
+      <c r="B19" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D19" s="27" t="n">
+        <f aca="false">Assumptions!$D$11/2</f>
+        <v>35</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <f aca="false">Assumptions!$F$11</f>
+        <v>100</v>
+      </c>
+      <c r="F19" s="28" t="n">
+        <f aca="false">IF(C19=0,0,E19/C19)</f>
+        <v>16.6666666666667</v>
+      </c>
+      <c r="G19" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H19" s="27" t="n">
+        <f aca="false">Assumptions!$D$15/2</f>
+        <v>17</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <f aca="false">Assumptions!$F$15</f>
+        <v>60</v>
+      </c>
+      <c r="J19" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K19" s="7" t="n">
+        <f aca="false">C19*D19*G19</f>
+        <v>1050</v>
+      </c>
+      <c r="L19" s="7" t="n">
+        <f aca="false">C19*H19*J19</f>
+        <v>306</v>
+      </c>
+      <c r="M19" s="9" t="n">
+        <f aca="false">(K19+L19)*Labor!$C$3</f>
+        <v>20340</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="H20" s="10" t="n">
-        <f aca="false">SUM(H17:H19)*(1+Assumptions!$B$34)</f>
-        <v>154940</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="H22" s="10" t="n">
-        <f aca="false">Labor!$H$14+Labor!$H$20</f>
-        <v>412731.6</v>
+        <v>89</v>
+      </c>
+      <c r="K20" s="21" t="n">
+        <f aca="false">SUM(K6:K19)</f>
+        <v>6062</v>
+      </c>
+      <c r="L20" s="21" t="n">
+        <f aca="false">SUM(L6:L19)</f>
+        <v>1853</v>
+      </c>
+      <c r="M20" s="10" t="n">
+        <f aca="false">SUM(M6:M19)</f>
+        <v>118725</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="5" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>166</v>
+        <v>154</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="M24" s="18" t="n">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="M25" s="18" t="n">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="M26" s="18" t="n">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="M27" s="9" t="n">
+        <f aca="false">SUM(M24:M26)*Assumptions!$B$34</f>
+        <v>27940</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="M28" s="10" t="n">
+        <f aca="false">SUM(M24:M27)</f>
+        <v>154940</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="M29" s="9" t="n">
+        <f aca="false">M20</f>
+        <v>118725</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="M30" s="9" t="n">
+        <f aca="false">M29*Assumptions!$B$33</f>
+        <v>11872.5</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="M31" s="10" t="n">
+        <f aca="false">M29*(1+Assumptions!$B$33)</f>
+        <v>130597.5</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="M32" s="10" t="n">
+        <f aca="false">Labor!$M$28+Labor!$M$31</f>
+        <v>285537.5</v>
       </c>
     </row>
   </sheetData>
@@ -3249,37 +3656,37 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="D3" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="E3" s="5" t="s">
         <v>171</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C4" s="24" t="n">
         <v>1800000</v>
@@ -3288,15 +3695,15 @@
         <v>1800000</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C5" s="24" t="n">
         <v>36000</v>
@@ -3305,15 +3712,15 @@
         <v>36000</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C6" s="24" t="n">
         <v>8000</v>
@@ -3322,15 +3729,15 @@
         <v>8000</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C7" s="24" t="n">
         <v>25000</v>
@@ -3339,15 +3746,15 @@
         <v>25000</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C8" s="24" t="n">
         <v>200000</v>
@@ -3356,15 +3763,15 @@
         <v>200000</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C9" s="24" t="n">
         <v>100000</v>
@@ -3373,15 +3780,15 @@
         <v>100000</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>186</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>188</v>
       </c>
       <c r="C10" s="24" t="n">
         <v>100000</v>
@@ -3390,15 +3797,15 @@
         <v>100000</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C11" s="24" t="n">
         <v>75000</v>
@@ -3407,15 +3814,15 @@
         <v>75000</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C12" s="24" t="n">
         <v>175000</v>
@@ -3424,15 +3831,15 @@
         <v>175000</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C13" s="24" t="n">
         <v>35000</v>
@@ -3441,15 +3848,15 @@
         <v>35000</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C14" s="24" t="n">
         <v>30000</v>
@@ -3458,15 +3865,15 @@
         <v>30000</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C15" s="24" t="n">
         <v>75000</v>
@@ -3475,15 +3882,15 @@
         <v>75000</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C16" s="24" t="n">
         <v>20000</v>
@@ -3492,15 +3899,15 @@
         <v>20000</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>198</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>200</v>
       </c>
       <c r="C17" s="24" t="n">
         <v>20000</v>
@@ -3509,15 +3916,15 @@
         <v>20000</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C18" s="24" t="n">
         <v>20000</v>
@@ -3526,15 +3933,15 @@
         <v>20000</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C19" s="24" t="n">
         <v>25000</v>
@@ -3543,12 +3950,12 @@
         <v>25000</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C20" s="10" t="n">
         <f aca="false">SUMIFS(C4:C19,$A$4:$A$19,"Acquisition")</f>
@@ -3561,7 +3968,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C21" s="12" t="n">
         <f aca="false">SUM(C4:C19)-C20</f>
@@ -3574,7 +3981,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C22" s="9" t="n">
         <f aca="false">C21*Assumptions!$B$28</f>
@@ -3587,7 +3994,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C23" s="10" t="n">
         <f aca="false">C20+C21+C22</f>
@@ -3624,156 +4031,156 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>55</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B4" s="8" t="n">
         <f aca="false">Assumptions!$B$29*(Assumptions!$B$30+Assumptions!$B$31)/100</f>
         <v>18293.4</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B5" s="18" t="n">
         <v>40000</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B6" s="18" t="n">
         <v>36000</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B7" s="18" t="n">
         <v>20000</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B8" s="18" t="n">
         <v>15000</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B9" s="18" t="n">
         <v>7200</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B10" s="18" t="n">
         <v>3000</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B11" s="18" t="n">
         <v>3500</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B12" s="18" t="n">
         <v>9000</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B13" s="18" t="n">
         <v>3600</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B14" s="18" t="n">
         <v>15000</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B15" s="18" t="n">
         <v>8000</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B16" s="10" t="n">
         <f aca="false">SUM(B4:B15)</f>
@@ -3805,12 +4212,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B3" s="8" t="n">
         <f aca="false">Capex!$C$23</f>
@@ -3819,7 +4226,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B4" s="15" t="n">
         <f aca="false">Assumptions!$B$35</f>
@@ -3828,7 +4235,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B5" s="9" t="n">
         <f aca="false">B3*B4</f>
@@ -3837,7 +4244,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B6" s="9" t="n">
         <f aca="false">B3-B5</f>
@@ -3848,14 +4255,14 @@
       <c r="A7" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B7" s="28" t="n">
+      <c r="B7" s="29" t="n">
         <f aca="false">Assumptions!$B$36</f>
         <v>0.0725</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B8" s="6" t="n">
         <f aca="false">Assumptions!$B$37</f>
@@ -3864,7 +4271,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B9" s="12" t="n">
         <f aca="false">-PMT(B7/12,B8*12,B5)*12</f>

--- a/806-Ramseur-PnL.xlsx
+++ b/806-Ramseur-PnL.xlsx
@@ -13,8 +13,6 @@
     <sheet name="Assumptions" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Labor" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Capex" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Opex" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Financing" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="175">
   <si>
     <t xml:space="preserve">806 E Ramseur Mini Golf + Bar — P&amp;L model</t>
   </si>
@@ -61,363 +59,273 @@
     <t xml:space="preserve">Sheets</t>
   </si>
   <si>
-    <t xml:space="preserve">P&amp;L — stabilized year split summer / winter / full year, plus a 5-year projection with ramp-up.</t>
+    <t xml:space="preserve">P&amp;L — revenue and gross margin, expenses (property interest, tax, insurance, utilities, labor, other), net profit and Simple ROI.</t>
   </si>
   <si>
     <t xml:space="preserve">Assumptions — schedule, players and spend by period, gross margins, cost and finance inputs.</t>
   </si>
   <si>
-    <t xml:space="preserve">Labor — hourly staff by day and daypart vs. players, salaried management, annual total. Capex — one-time costs. Opex — fixed annual costs. Financing — loan and equity.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Excludes depreciation, interest/principal split and income taxes. Planning estimates, not quotes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P&amp;L — stabilized year ($)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Summer = Apr-Nov (8 months), winter = Dec-Mar (4 months). Fixed costs, salaries, events and debt split by months; hourly labor by open hours.</t>
+    <t xml:space="preserve">Labor — hourly staff by day and daypart vs. players, salaried management, annual total. Capex — one-time costs (your amount vs default estimate).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Property service cost is interest only (amount financed x rate). Excludes principal, depreciation and income taxes. Planning estimates, not quotes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P&amp;L — annual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue and gross margin come from Assumptions (Revenue Estimates). Labor comes from the Labor sheet. Yellow cells are inputs; column C keeps the default estimate.</t>
   </si>
   <si>
     <t xml:space="preserve">Line</t>
   </si>
   <si>
+    <t xml:space="preserve">Your amount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Default estimate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source / note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total revenues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From Assumptions period table (Revenue Estimates tab)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total gross margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue by line x gross margin % on Assumptions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gross margin %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expenses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Property cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Property cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Amount financed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Interest rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Property service cost (financed x rate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interest only, no principal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Property tax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Durham County 57.92c + City 43.71c per $100 on $1.8M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Insurance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Utilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Labor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From Labor sheet (salaried + hourly, loaded)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Accounting software &amp; legal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Building and course maintenance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Trash &amp; maintenance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Misc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total expenses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net profit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simple ROI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equity contribution (property cost - amount financed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Initial capex excl. purchase price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capex sheet total less its purchase price line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total invested</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumptions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Golf price per round</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One price for all periods</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Private events per year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Birthdays, buyouts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average event package</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue split 8/12 summer, 4/12 winter on P&amp;L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Season</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daypart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days / yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hours / daypart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Players / day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Food $ / player</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ice cream $ / player</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bar $ / player</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rounds / yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue / yr</t>
+  </si>
+  <si>
     <t xml:space="preserve">Summer</t>
   </si>
   <si>
+    <t xml:space="preserve">Weekday (Wed-Fri)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Afternoon 12-5 pm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evening 5-11 pm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weekend (Sat-Sun)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Winter</t>
   </si>
   <si>
-    <t xml:space="preserve">Full year</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rounds played</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open hours</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revenue</t>
+    <t xml:space="preserve">Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day counts: calendar 2027, closed Mon-Tue. Players are per daypart per day.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gross margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note</t>
   </si>
   <si>
     <t xml:space="preserve">Golf</t>
   </si>
   <si>
+    <t xml:space="preserve">Course upkeep sits in fixed costs; Puttshack cites ~95% on mini golf</t>
+  </si>
+  <si>
     <t xml:space="preserve">Food</t>
   </si>
   <si>
+    <t xml:space="preserve">Food trucks keep their sales; 15% = our commission. Use ~65% if we run food ourselves</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ice cream</t>
   </si>
   <si>
+    <t xml:space="preserve">~30% product cost</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bar</t>
   </si>
   <si>
+    <t xml:space="preserve">~24% pour cost</t>
+  </si>
+  <si>
     <t xml:space="preserve">Private events</t>
   </si>
   <si>
-    <t xml:space="preserve">Total revenue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gross profit by line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Golf gross profit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Food gross profit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ice cream gross profit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bar gross profit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Private events gross profit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total gross profit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gross margin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operating costs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hourly labor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salaried labor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixed opex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Card processing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marketing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total operating costs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EBITDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EBITDA margin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Debt service</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cash flow after debt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Full-year checks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Labor % of revenue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revenue per round</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Debt service coverage (EBITDA / debt service)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cash-on-cash return on equity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5-year projection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Year 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Year 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Year 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Year 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Year 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Volume vs. stabilized</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gross profit</t>
+    <t xml:space="preserve">Food + drink in packages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost and finance input</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unit / note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capex contingency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% of non-acquisition capex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hourly payroll burden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FICA + unemployment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salaried burden incl. benefits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FICA + unemployment + health</t>
   </si>
   <si>
     <t xml:space="preserve">Labor</t>
   </si>
   <si>
-    <t xml:space="preserve">Card + marketing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cumulative cash flow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equity left to recover</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Excludes depreciation and income taxes. Labor held at full schedule from year 1.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assumptions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Golf price per round</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One price for all periods</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Private events per year</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Birthdays, buyouts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Average event package</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revenue split 8/12 summer, 4/12 winter on P&amp;L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Season</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Day type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daypart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days / yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hours / daypart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Players / day</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Food $ / player</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ice cream $ / player</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bar $ / player</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rounds / yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revenue / yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weekday (Wed-Fri)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Afternoon 12-5 pm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evening 5-11 pm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weekend (Sat-Sun)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Day counts: calendar 2027, closed Mon-Tue. Players are per daypart per day.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revenue line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Course upkeep sits in fixed costs; Puttshack cites ~95% on mini golf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Food trucks keep their sales; 15% = our commission. Use ~65% if we run food ourselves</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~30% product cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~24% pour cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Food + drink in packages</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cost and finance input</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unit / note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% of non-food sales (trucks process their own)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% of total sales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capex contingency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% of non-acquisition capex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assessed value for property tax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assumes assessed = purchase price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Durham County tax rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$ per $100; FY2026-27 adopted (dconc.gov, June 2026)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">City of Durham tax rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$ per $100; FY2025-26 proposed (durhamnc.gov); verify adopted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weeks per year</t>
-  </si>
-  <si>
-    <t xml:space="preserve">For maintenance hours</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hourly payroll burden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FICA + unemployment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salaried burden incl. benefits</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FICA + unemployment + health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Debt as % of total project</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SBA 504/7(a) can go higher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interest rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">per year</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amortization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">years</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cost inflation (years 2-5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Year 1 volume vs. stabilized</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramp-up to maturity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Year 2 volume vs. stabilized</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Year 3 volume vs. stabilized</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Year 4 volume vs. stabilized</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Year 5 volume vs. stabilized</t>
-  </si>
-  <si>
     <t xml:space="preserve">GM or Assistant GM is always on premises (salaried, below). Enter hourly staff per day and daypart in columns G and J. Players come from the Assumptions period table.</t>
   </si>
   <si>
@@ -535,12 +443,6 @@
     <t xml:space="preserve">Item</t>
   </si>
   <si>
-    <t xml:space="preserve">Your amount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Default estimate</t>
-  </si>
-  <si>
     <t xml:space="preserve">Basis</t>
   </si>
   <si>
@@ -647,94 +549,20 @@
   </si>
   <si>
     <t xml:space="preserve">Total project cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixed annual operating costs (year 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Property tax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assessed value assumed = $1.8M; county 57.92c + city 43.71c per $100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Insurance: GL, liquor liability, property, umbrella</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estimate; one NC bar operator reports under $20k for a location</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utilities (no HVAC; coolers, fans, lighting, water)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Building repairs + maintenance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estimate; 1948 Class C building</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Course + turf maintenance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POS, booking, software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABC permits + local licenses (renewals)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mixed beverages $1,000; malt $400; wine $400; local</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Music licensing (ASCAP/BMI/SESAC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trash, recycling, pest control</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alarm + camera monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accounting + legal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operating supplies (balls, putters, scorecards)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total fixed opex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Financing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Debt %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loan amount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equity required</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amortization (years)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Annual debt service</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="#,##0;\(#,##0\);\-"/>
-    <numFmt numFmtId="166" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
-    <numFmt numFmtId="167" formatCode="0.0%;\(0.0%\);\-"/>
+    <numFmt numFmtId="165" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
+    <numFmt numFmtId="166" formatCode="0.0%;\(0.0%\);\-"/>
+    <numFmt numFmtId="167" formatCode="0.00%"/>
     <numFmt numFmtId="168" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
-    <numFmt numFmtId="169" formatCode="0.00\x"/>
-    <numFmt numFmtId="170" formatCode="0.0000"/>
-    <numFmt numFmtId="171" formatCode="0.00%"/>
-    <numFmt numFmtId="172" formatCode="0.0"/>
+    <numFmt numFmtId="169" formatCode="#,##0;\(#,##0\);\-"/>
+    <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -789,14 +617,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF008000"/>
+      <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF008000"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -863,7 +691,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="27">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -888,7 +716,15 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -896,15 +732,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -912,11 +740,35 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -924,43 +776,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -968,19 +792,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1342,11 +1158,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="60"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1359,804 +1176,277 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+    <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="6" t="n">
-        <f aca="false">SUM(Assumptions!$J$8:$J$11)</f>
-        <v>21960</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <f aca="false">SUM(Assumptions!$J$12:$J$15)</f>
-        <v>4915</v>
-      </c>
-      <c r="D4" s="7" t="n">
-        <f aca="false">B4+C4</f>
-        <v>26875</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="6" t="n">
-        <f aca="false">SUMPRODUCT(Assumptions!$D$8:$D$11,Assumptions!$E$8:$E$11)</f>
-        <v>1914</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <f aca="false">SUMPRODUCT(Assumptions!$D$12:$D$15,Assumptions!$E$12:$E$15)</f>
-        <v>957</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <f aca="false">B5+C5</f>
-        <v>2871</v>
+      <c r="B6" s="6" t="n">
+        <f aca="false">SUM(Assumptions!$J$8:$J$15)*Assumptions!$B$3+SUMPRODUCT(Assumptions!$J$8:$J$15,Assumptions!$G$8:$G$15)+SUMPRODUCT(Assumptions!$J$8:$J$15,Assumptions!$H$8:$H$15)+SUMPRODUCT(Assumptions!$J$8:$J$15,Assumptions!$I$8:$I$15)+Assumptions!$B$4*Assumptions!$B$5</f>
+        <v>846350</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="B7" s="6" t="n">
+        <f aca="false">SUM(Assumptions!$J$8:$J$15)*Assumptions!$B$3*Assumptions!$B$19+SUMPRODUCT(Assumptions!$J$8:$J$15,Assumptions!$G$8:$G$15)*Assumptions!$B$20+SUMPRODUCT(Assumptions!$J$8:$J$15,Assumptions!$H$8:$H$15)*Assumptions!$B$21+SUMPRODUCT(Assumptions!$J$8:$J$15,Assumptions!$I$8:$I$15)*Assumptions!$B$22+Assumptions!$B$4*Assumptions!$B$5*Assumptions!$B$23</f>
+        <v>582416.5</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="8" t="n">
-        <f aca="false">SUM(Assumptions!$J$8:$J$11)*Assumptions!$B$3</f>
-        <v>263520</v>
-      </c>
-      <c r="C8" s="8" t="n">
-        <f aca="false">SUM(Assumptions!$J$12:$J$15)*Assumptions!$B$3</f>
-        <v>58980</v>
-      </c>
-      <c r="D8" s="9" t="n">
-        <f aca="false">B8+C8</f>
-        <v>322500</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="8" t="n">
-        <f aca="false">SUMPRODUCT(Assumptions!$J$8:$J$11,Assumptions!$G$8:$G$11)</f>
-        <v>158240</v>
-      </c>
-      <c r="C9" s="8" t="n">
-        <f aca="false">SUMPRODUCT(Assumptions!$J$12:$J$15,Assumptions!$G$12:$G$15)</f>
-        <v>35690</v>
-      </c>
-      <c r="D9" s="9" t="n">
-        <f aca="false">B9+C9</f>
-        <v>193930</v>
+        <v>26</v>
+      </c>
+      <c r="B8" s="7" t="n">
+        <f aca="false">IF($B$6=0,0,$B$7/$B$6)</f>
+        <v>0.688150883204348</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="8" t="n">
-        <f aca="false">SUMPRODUCT(Assumptions!$J$8:$J$11,Assumptions!$H$8:$H$11)</f>
-        <v>48120</v>
-      </c>
-      <c r="C10" s="8" t="n">
-        <f aca="false">SUMPRODUCT(Assumptions!$J$12:$J$15,Assumptions!$H$12:$H$15)</f>
-        <v>0</v>
-      </c>
-      <c r="D10" s="9" t="n">
-        <f aca="false">B10+C10</f>
-        <v>48120</v>
+      <c r="A10" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="8" t="n">
-        <f aca="false">SUMPRODUCT(Assumptions!$J$8:$J$11,Assumptions!$I$8:$I$11)</f>
-        <v>171200</v>
-      </c>
-      <c r="C11" s="8" t="n">
-        <f aca="false">SUMPRODUCT(Assumptions!$J$12:$J$15,Assumptions!$I$12:$I$15)</f>
-        <v>20600</v>
-      </c>
-      <c r="D11" s="9" t="n">
-        <f aca="false">B11+C11</f>
-        <v>191800</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B12" s="8" t="n">
-        <f aca="false">Assumptions!$B$4*Assumptions!$B$5*8/12</f>
-        <v>60000</v>
-      </c>
-      <c r="C12" s="8" t="n">
-        <f aca="false">Assumptions!$B$4*Assumptions!$B$5*4/12</f>
-        <v>30000</v>
-      </c>
-      <c r="D12" s="9" t="n">
-        <f aca="false">B12+C12</f>
-        <v>90000</v>
+        <v>1800000</v>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>1800000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="10" t="n">
-        <f aca="false">SUM(B8:B12)</f>
-        <v>701080</v>
-      </c>
-      <c r="C13" s="10" t="n">
-        <f aca="false">SUM(C8:C12)</f>
-        <v>145270</v>
-      </c>
-      <c r="D13" s="10" t="n">
-        <f aca="false">B13+C13</f>
-        <v>846350</v>
+      <c r="A13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="8" t="n">
+        <v>1260000</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>1260000</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="10" t="n">
+        <v>0.0725</v>
+      </c>
+      <c r="C14" s="11" t="n">
+        <v>0.0725</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
-        <v>30</v>
+      <c r="A15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="9" t="n">
+        <f aca="false">$B$13*$B$14</f>
+        <v>91350</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>91350</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" s="9" t="n">
-        <f aca="false">B8*Assumptions!$B$19</f>
-        <v>250344</v>
+        <v>34</v>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>18293</v>
       </c>
       <c r="C16" s="9" t="n">
-        <f aca="false">C8*Assumptions!$B$19</f>
-        <v>56031</v>
-      </c>
-      <c r="D16" s="9" t="n">
-        <f aca="false">B16+C16</f>
-        <v>306375</v>
+        <v>18293</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" s="9" t="n">
-        <f aca="false">B9*Assumptions!$B$20</f>
-        <v>23736</v>
+        <v>36</v>
+      </c>
+      <c r="B17" s="8" t="n">
+        <v>40000</v>
       </c>
       <c r="C17" s="9" t="n">
-        <f aca="false">C9*Assumptions!$B$20</f>
-        <v>5353.5</v>
-      </c>
-      <c r="D17" s="9" t="n">
-        <f aca="false">B17+C17</f>
-        <v>29089.5</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B18" s="9" t="n">
-        <f aca="false">B10*Assumptions!$B$21</f>
-        <v>33684</v>
+        <v>37</v>
+      </c>
+      <c r="B18" s="8" t="n">
+        <v>36000</v>
       </c>
       <c r="C18" s="9" t="n">
-        <f aca="false">C10*Assumptions!$B$21</f>
-        <v>0</v>
-      </c>
-      <c r="D18" s="9" t="n">
-        <f aca="false">B18+C18</f>
-        <v>33684</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B19" s="9" t="n">
-        <f aca="false">B11*Assumptions!$B$22</f>
-        <v>130112</v>
-      </c>
-      <c r="C19" s="9" t="n">
-        <f aca="false">C11*Assumptions!$B$22</f>
-        <v>15656</v>
-      </c>
-      <c r="D19" s="9" t="n">
-        <f aca="false">B19+C19</f>
-        <v>145768</v>
+        <v>38</v>
+      </c>
+      <c r="B19" s="12" t="n">
+        <f aca="false">Labor!$M$32</f>
+        <v>285537.5</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20" s="9" t="n">
-        <f aca="false">B12*Assumptions!$B$23</f>
-        <v>45000</v>
+        <v>40</v>
+      </c>
+      <c r="B20" s="8" t="n">
+        <v>15000</v>
       </c>
       <c r="C20" s="9" t="n">
-        <f aca="false">C12*Assumptions!$B$23</f>
-        <v>22500</v>
-      </c>
-      <c r="D20" s="9" t="n">
-        <f aca="false">B20+C20</f>
-        <v>67500</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B21" s="10" t="n">
-        <f aca="false">SUM(B16:B20)</f>
-        <v>482876</v>
-      </c>
-      <c r="C21" s="10" t="n">
-        <f aca="false">SUM(C16:C20)</f>
-        <v>99540.5</v>
-      </c>
-      <c r="D21" s="10" t="n">
-        <f aca="false">B21+C21</f>
-        <v>582416.5</v>
+      <c r="A21" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>30000</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="11" t="n">
-        <f aca="false">IF(B13=0,0,B21/B13)</f>
-        <v>0.688760198550807</v>
-      </c>
-      <c r="C22" s="11" t="n">
-        <f aca="false">IF(C13=0,0,C21/C13)</f>
-        <v>0.685210298065671</v>
-      </c>
-      <c r="D22" s="11" t="n">
-        <f aca="false">IF(D13=0,0,D21/D13)</f>
-        <v>0.688150883204348</v>
+        <v>42</v>
+      </c>
+      <c r="B22" s="8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>15000</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
+      </c>
+      <c r="B24" s="13" t="n">
+        <f aca="false">SUM(B15:B23)</f>
+        <v>546180.5</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B25" s="8" t="n">
-        <f aca="false">Labor!$K$20*Labor!$C$3*(1+Assumptions!$B$33)</f>
-        <v>100023</v>
-      </c>
-      <c r="C25" s="8" t="n">
-        <f aca="false">Labor!$L$20*Labor!$C$3*(1+Assumptions!$B$33)</f>
-        <v>30574.5</v>
-      </c>
-      <c r="D25" s="9" t="n">
-        <f aca="false">B25+C25</f>
-        <v>130597.5</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B26" s="8" t="n">
-        <f aca="false">Labor!$M$28*8/12</f>
-        <v>103293.333333333</v>
-      </c>
-      <c r="C26" s="8" t="n">
-        <f aca="false">Labor!$M$28*4/12</f>
-        <v>51646.6666666667</v>
-      </c>
-      <c r="D26" s="9" t="n">
-        <f aca="false">B26+C26</f>
-        <v>154940</v>
+      <c r="A25" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="13" t="n">
+        <f aca="false">$B$7-$B$24</f>
+        <v>36236</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B27" s="8" t="n">
-        <f aca="false">Opex!$B$16*8/12</f>
-        <v>119062.266666667</v>
-      </c>
-      <c r="C27" s="8" t="n">
-        <f aca="false">Opex!$B$16*4/12</f>
-        <v>59531.1333333333</v>
-      </c>
-      <c r="D27" s="9" t="n">
-        <f aca="false">B27+C27</f>
-        <v>178593.4</v>
+      <c r="A27" s="2" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B28" s="9" t="n">
-        <f aca="false">(B13-B9)*Assumptions!$B$26</f>
-        <v>14928.1</v>
-      </c>
-      <c r="C28" s="9" t="n">
-        <f aca="false">(C13-C9)*Assumptions!$B$26</f>
-        <v>3013.45</v>
-      </c>
-      <c r="D28" s="9" t="n">
-        <f aca="false">B28+C28</f>
-        <v>17941.55</v>
+        <f aca="false">$B$25</f>
+        <v>36236</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B29" s="9" t="n">
-        <f aca="false">B13*Assumptions!$B$27</f>
-        <v>28043.2</v>
-      </c>
-      <c r="C29" s="9" t="n">
-        <f aca="false">C13*Assumptions!$B$27</f>
-        <v>5810.8</v>
-      </c>
-      <c r="D29" s="9" t="n">
-        <f aca="false">B29+C29</f>
-        <v>33854</v>
+        <f aca="false">$B$12-$B$13</f>
+        <v>540000</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B30" s="10" t="n">
-        <f aca="false">SUM(B25:B29)</f>
-        <v>365349.9</v>
-      </c>
-      <c r="C30" s="10" t="n">
-        <f aca="false">SUM(C25:C29)</f>
-        <v>150576.55</v>
-      </c>
-      <c r="D30" s="10" t="n">
-        <f aca="false">B30+C30</f>
-        <v>515926.45</v>
+      <c r="A30" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B30" s="12" t="n">
+        <f aca="false">Capex!$C$23-Capex!$C$4</f>
+        <v>1034000</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B31" s="13" t="n">
+        <f aca="false">$B$29+$B$30</f>
+        <v>1574000</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B32" s="12" t="n">
-        <f aca="false">B21-B30</f>
-        <v>117526.1</v>
-      </c>
-      <c r="C32" s="12" t="n">
-        <f aca="false">C21-C30</f>
-        <v>-51036.05</v>
-      </c>
-      <c r="D32" s="12" t="n">
-        <f aca="false">B32+C32</f>
-        <v>66490.05</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B33" s="11" t="n">
-        <f aca="false">IF(B13=0,0,B32/B13)</f>
-        <v>0.167635790494665</v>
-      </c>
-      <c r="C33" s="11" t="n">
-        <f aca="false">IF(C13=0,0,C32/C13)</f>
-        <v>-0.351318579197357</v>
-      </c>
-      <c r="D33" s="11" t="n">
-        <f aca="false">IF(D13=0,0,D32/D13)</f>
-        <v>0.078560938146157</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B34" s="8" t="n">
-        <f aca="false">Financing!$B$9*8/12</f>
-        <v>114712.340559677</v>
-      </c>
-      <c r="C34" s="8" t="n">
-        <f aca="false">Financing!$B$9*4/12</f>
-        <v>57356.1702798383</v>
-      </c>
-      <c r="D34" s="9" t="n">
-        <f aca="false">B34+C34</f>
-        <v>172068.510839515</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B35" s="10" t="n">
-        <f aca="false">B32-B34</f>
-        <v>2813.75944032341</v>
-      </c>
-      <c r="C35" s="10" t="n">
-        <f aca="false">C32-C34</f>
-        <v>-108392.220279838</v>
-      </c>
-      <c r="D35" s="10" t="n">
-        <f aca="false">B35+C35</f>
-        <v>-105578.460839515</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D38" s="11" t="n">
-        <f aca="false">IF(D13=0,0,Labor!$M$32/D13)</f>
-        <v>0.337375199385597</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D39" s="13" t="n">
-        <f aca="false">IF(D4=0,0,D13/D4)</f>
-        <v>31.4920930232558</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D40" s="14" t="n">
-        <f aca="false">IF(D34=0,0,D32/D34)</f>
-        <v>0.386416141312538</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D41" s="11" t="n">
-        <f aca="false">IF(Financing!$B$6=0,0,D35/Financing!$B$6)</f>
-        <v>-0.124180734932386</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="F45" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B46" s="15" t="n">
-        <f aca="false">Assumptions!$B$39</f>
-        <v>0.75</v>
-      </c>
-      <c r="C46" s="15" t="n">
-        <f aca="false">Assumptions!$B$40</f>
-        <v>0.9</v>
-      </c>
-      <c r="D46" s="15" t="n">
-        <f aca="false">Assumptions!$B$41</f>
-        <v>1</v>
-      </c>
-      <c r="E46" s="15" t="n">
-        <f aca="false">Assumptions!$B$42</f>
-        <v>1.03</v>
-      </c>
-      <c r="F46" s="15" t="n">
-        <f aca="false">Assumptions!$B$43</f>
-        <v>1.06</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B47" s="12" t="n">
-        <f aca="false">$D$13*B46</f>
-        <v>634762.5</v>
-      </c>
-      <c r="C47" s="12" t="n">
-        <f aca="false">$D$13*C46</f>
-        <v>761715</v>
-      </c>
-      <c r="D47" s="12" t="n">
-        <f aca="false">$D$13*D46</f>
-        <v>846350</v>
-      </c>
-      <c r="E47" s="12" t="n">
-        <f aca="false">$D$13*E46</f>
-        <v>871740.5</v>
-      </c>
-      <c r="F47" s="12" t="n">
-        <f aca="false">$D$13*F46</f>
-        <v>897131</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B48" s="9" t="n">
-        <f aca="false">$D$21*B46</f>
-        <v>436812.375</v>
-      </c>
-      <c r="C48" s="9" t="n">
-        <f aca="false">$D$21*C46</f>
-        <v>524174.85</v>
-      </c>
-      <c r="D48" s="9" t="n">
-        <f aca="false">$D$21*D46</f>
-        <v>582416.5</v>
-      </c>
-      <c r="E48" s="9" t="n">
-        <f aca="false">$D$21*E46</f>
-        <v>599888.995</v>
-      </c>
-      <c r="F48" s="9" t="n">
-        <f aca="false">$D$21*F46</f>
-        <v>617361.49</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B49" s="8" t="n">
-        <f aca="false">Labor!$M$32*(1+Assumptions!$B$38)^0</f>
-        <v>285537.5</v>
-      </c>
-      <c r="C49" s="8" t="n">
-        <f aca="false">Labor!$M$32*(1+Assumptions!$B$38)^1</f>
-        <v>294103.625</v>
-      </c>
-      <c r="D49" s="8" t="n">
-        <f aca="false">Labor!$M$32*(1+Assumptions!$B$38)^2</f>
-        <v>302926.73375</v>
-      </c>
-      <c r="E49" s="8" t="n">
-        <f aca="false">Labor!$M$32*(1+Assumptions!$B$38)^3</f>
-        <v>312014.5357625</v>
-      </c>
-      <c r="F49" s="8" t="n">
-        <f aca="false">Labor!$M$32*(1+Assumptions!$B$38)^4</f>
-        <v>321374.971835375</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B50" s="8" t="n">
-        <f aca="false">Opex!$B$16*(1+Assumptions!$B$38)^0</f>
-        <v>178593.4</v>
-      </c>
-      <c r="C50" s="8" t="n">
-        <f aca="false">Opex!$B$16*(1+Assumptions!$B$38)^1</f>
-        <v>183951.202</v>
-      </c>
-      <c r="D50" s="8" t="n">
-        <f aca="false">Opex!$B$16*(1+Assumptions!$B$38)^2</f>
-        <v>189469.73806</v>
-      </c>
-      <c r="E50" s="8" t="n">
-        <f aca="false">Opex!$B$16*(1+Assumptions!$B$38)^3</f>
-        <v>195153.8302018</v>
-      </c>
-      <c r="F50" s="8" t="n">
-        <f aca="false">Opex!$B$16*(1+Assumptions!$B$38)^4</f>
-        <v>201008.445107854</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B51" s="9" t="n">
-        <f aca="false">(SUM($D$28:$D$29))*B46</f>
-        <v>38846.6625</v>
-      </c>
-      <c r="C51" s="9" t="n">
-        <f aca="false">(SUM($D$28:$D$29))*C46</f>
-        <v>46615.995</v>
-      </c>
-      <c r="D51" s="9" t="n">
-        <f aca="false">(SUM($D$28:$D$29))*D46</f>
-        <v>51795.55</v>
-      </c>
-      <c r="E51" s="9" t="n">
-        <f aca="false">(SUM($D$28:$D$29))*E46</f>
-        <v>53349.4165</v>
-      </c>
-      <c r="F51" s="9" t="n">
-        <f aca="false">(SUM($D$28:$D$29))*F46</f>
-        <v>54903.283</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B52" s="10" t="n">
-        <f aca="false">B48-B49-B50-B51</f>
-        <v>-66165.1875</v>
-      </c>
-      <c r="C52" s="10" t="n">
-        <f aca="false">C48-C49-C50-C51</f>
-        <v>-495.971999999958</v>
-      </c>
-      <c r="D52" s="10" t="n">
-        <f aca="false">D48-D49-D50-D51</f>
-        <v>38224.47819</v>
-      </c>
-      <c r="E52" s="10" t="n">
-        <f aca="false">E48-E49-E50-E51</f>
-        <v>39371.2125357</v>
-      </c>
-      <c r="F52" s="10" t="n">
-        <f aca="false">F48-F49-F50-F51</f>
-        <v>40074.7900567709</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B53" s="8" t="n">
-        <f aca="false">Financing!$B$9</f>
-        <v>172068.510839515</v>
-      </c>
-      <c r="C53" s="8" t="n">
-        <f aca="false">Financing!$B$9</f>
-        <v>172068.510839515</v>
-      </c>
-      <c r="D53" s="8" t="n">
-        <f aca="false">Financing!$B$9</f>
-        <v>172068.510839515</v>
-      </c>
-      <c r="E53" s="8" t="n">
-        <f aca="false">Financing!$B$9</f>
-        <v>172068.510839515</v>
-      </c>
-      <c r="F53" s="8" t="n">
-        <f aca="false">Financing!$B$9</f>
-        <v>172068.510839515</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B54" s="10" t="n">
-        <f aca="false">B52-B53</f>
-        <v>-238233.698339515</v>
-      </c>
-      <c r="C54" s="10" t="n">
-        <f aca="false">C52-C53</f>
-        <v>-172564.482839515</v>
-      </c>
-      <c r="D54" s="10" t="n">
-        <f aca="false">D52-D53</f>
-        <v>-133844.032649515</v>
-      </c>
-      <c r="E54" s="10" t="n">
-        <f aca="false">E52-E53</f>
-        <v>-132697.298303815</v>
-      </c>
-      <c r="F54" s="10" t="n">
-        <f aca="false">F52-F53</f>
-        <v>-131993.720782744</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B55" s="9" t="n">
-        <f aca="false">B54</f>
-        <v>-238233.698339515</v>
-      </c>
-      <c r="C55" s="9" t="n">
-        <f aca="false">B55+C54</f>
-        <v>-410798.18117903</v>
-      </c>
-      <c r="D55" s="9" t="n">
-        <f aca="false">C55+D54</f>
-        <v>-544642.213828545</v>
-      </c>
-      <c r="E55" s="9" t="n">
-        <f aca="false">D55+E54</f>
-        <v>-677339.512132359</v>
-      </c>
-      <c r="F55" s="9" t="n">
-        <f aca="false">E55+F54</f>
-        <v>-809333.232915103</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B56" s="9" t="n">
-        <f aca="false">Financing!$B$6-B55</f>
-        <v>1088433.69833952</v>
-      </c>
-      <c r="C56" s="9" t="n">
-        <f aca="false">Financing!$B$6-C55</f>
-        <v>1260998.18117903</v>
-      </c>
-      <c r="D56" s="9" t="n">
-        <f aca="false">Financing!$B$6-D55</f>
-        <v>1394842.21382854</v>
-      </c>
-      <c r="E56" s="9" t="n">
-        <f aca="false">Financing!$B$6-E55</f>
-        <v>1527539.51213236</v>
-      </c>
-      <c r="F56" s="9" t="n">
-        <f aca="false">Financing!$B$6-F55</f>
-        <v>1659533.2329151</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="3" t="s">
-        <v>66</v>
+      <c r="B32" s="14" t="n">
+        <f aca="false">IF($B$31=0,0,$B$25/$B$31)</f>
+        <v>0.0230216010165184</v>
       </c>
     </row>
   </sheetData>
@@ -2175,7 +1465,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -2190,106 +1480,106 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B3" s="16" t="n">
+        <v>52</v>
+      </c>
+      <c r="B3" s="15" t="n">
         <v>12</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B4" s="17" t="n">
+        <v>54</v>
+      </c>
+      <c r="B4" s="16" t="n">
         <v>60</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B5" s="18" t="n">
+        <v>56</v>
+      </c>
+      <c r="B5" s="17" t="n">
         <v>1500</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D8" s="17" t="n">
+        <v>71</v>
+      </c>
+      <c r="D8" s="16" t="n">
         <v>104</v>
       </c>
-      <c r="E8" s="17" t="n">
+      <c r="E8" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="F8" s="19" t="n">
+      <c r="F8" s="18" t="n">
         <v>30</v>
       </c>
-      <c r="G8" s="20" t="n">
+      <c r="G8" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="H8" s="20" t="n">
+      <c r="H8" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="I8" s="20" t="n">
+      <c r="I8" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="7" t="n">
+      <c r="J8" s="20" t="n">
         <f aca="false">D8*F8</f>
         <v>3120</v>
       </c>
@@ -2300,33 +1590,33 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D9" s="17" t="n">
+        <v>72</v>
+      </c>
+      <c r="D9" s="16" t="n">
         <v>104</v>
       </c>
-      <c r="E9" s="17" t="n">
+      <c r="E9" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="F9" s="19" t="n">
+      <c r="F9" s="18" t="n">
         <v>60</v>
       </c>
-      <c r="G9" s="20" t="n">
+      <c r="G9" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="H9" s="20" t="n">
+      <c r="H9" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="20" t="n">
+      <c r="I9" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="J9" s="7" t="n">
+      <c r="J9" s="20" t="n">
         <f aca="false">D9*F9</f>
         <v>6240</v>
       </c>
@@ -2337,33 +1627,33 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D10" s="17" t="n">
+        <v>71</v>
+      </c>
+      <c r="D10" s="16" t="n">
         <v>70</v>
       </c>
-      <c r="E10" s="17" t="n">
+      <c r="E10" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="F10" s="19" t="n">
+      <c r="F10" s="18" t="n">
         <v>80</v>
       </c>
-      <c r="G10" s="20" t="n">
+      <c r="G10" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="H10" s="20" t="n">
+      <c r="H10" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="I10" s="20" t="n">
+      <c r="I10" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="J10" s="7" t="n">
+      <c r="J10" s="20" t="n">
         <f aca="false">D10*F10</f>
         <v>5600</v>
       </c>
@@ -2374,33 +1664,33 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D11" s="17" t="n">
+        <v>72</v>
+      </c>
+      <c r="D11" s="16" t="n">
         <v>70</v>
       </c>
-      <c r="E11" s="17" t="n">
+      <c r="E11" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="F11" s="19" t="n">
+      <c r="F11" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="G11" s="20" t="n">
+      <c r="G11" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="H11" s="20" t="n">
+      <c r="H11" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="20" t="n">
+      <c r="I11" s="19" t="n">
         <v>16</v>
       </c>
-      <c r="J11" s="7" t="n">
+      <c r="J11" s="20" t="n">
         <f aca="false">D11*F11</f>
         <v>7000</v>
       </c>
@@ -2411,33 +1701,33 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>19</v>
+        <v>74</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D12" s="17" t="n">
+        <v>71</v>
+      </c>
+      <c r="D12" s="16" t="n">
         <v>53</v>
       </c>
-      <c r="E12" s="17" t="n">
+      <c r="E12" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="F12" s="19" t="n">
+      <c r="F12" s="18" t="n">
         <v>15</v>
       </c>
-      <c r="G12" s="20" t="n">
+      <c r="G12" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="H12" s="20" t="n">
+      <c r="H12" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="20" t="n">
+      <c r="I12" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="7" t="n">
+      <c r="J12" s="20" t="n">
         <f aca="false">D12*F12</f>
         <v>795</v>
       </c>
@@ -2448,33 +1738,33 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>19</v>
+        <v>74</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D13" s="17" t="n">
+        <v>72</v>
+      </c>
+      <c r="D13" s="16" t="n">
         <v>53</v>
       </c>
-      <c r="E13" s="17" t="n">
+      <c r="E13" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="F13" s="19" t="n">
+      <c r="F13" s="18" t="n">
         <v>20</v>
       </c>
-      <c r="G13" s="20" t="n">
+      <c r="G13" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="H13" s="20" t="n">
+      <c r="H13" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="20" t="n">
+      <c r="I13" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="J13" s="7" t="n">
+      <c r="J13" s="20" t="n">
         <f aca="false">D13*F13</f>
         <v>1060</v>
       </c>
@@ -2485,33 +1775,33 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>19</v>
+        <v>74</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D14" s="17" t="n">
+        <v>71</v>
+      </c>
+      <c r="D14" s="16" t="n">
         <v>34</v>
       </c>
-      <c r="E14" s="17" t="n">
+      <c r="E14" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="F14" s="19" t="n">
+      <c r="F14" s="18" t="n">
         <v>30</v>
       </c>
-      <c r="G14" s="20" t="n">
+      <c r="G14" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="H14" s="20" t="n">
+      <c r="H14" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="20" t="n">
+      <c r="I14" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="J14" s="7" t="n">
+      <c r="J14" s="20" t="n">
         <f aca="false">D14*F14</f>
         <v>1020</v>
       </c>
@@ -2522,33 +1812,33 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>19</v>
+        <v>74</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D15" s="17" t="n">
+        <v>72</v>
+      </c>
+      <c r="D15" s="16" t="n">
         <v>34</v>
       </c>
-      <c r="E15" s="17" t="n">
+      <c r="E15" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="F15" s="19" t="n">
+      <c r="F15" s="18" t="n">
         <v>60</v>
       </c>
-      <c r="G15" s="20" t="n">
+      <c r="G15" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="H15" s="20" t="n">
+      <c r="H15" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="20" t="n">
+      <c r="I15" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="J15" s="7" t="n">
+      <c r="J15" s="20" t="n">
         <f aca="false">D15*F15</f>
         <v>2040</v>
       </c>
@@ -2559,295 +1849,130 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="J16" s="21" t="n">
         <f aca="false">SUM(J8:J15)</f>
         <v>26875</v>
       </c>
-      <c r="K16" s="10" t="n">
+      <c r="K16" s="13" t="n">
         <f aca="false">SUM(K8:K15)</f>
         <v>756350</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="B19" s="22" t="n">
         <v>0.95</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="B20" s="22" t="n">
         <v>0.15</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>26</v>
+        <v>84</v>
       </c>
       <c r="B21" s="22" t="n">
         <v>0.7</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>27</v>
+        <v>86</v>
       </c>
       <c r="B22" s="22" t="n">
         <v>0.76</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="B23" s="22" t="n">
         <v>0.75</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="B26" s="23" t="n">
-        <v>0.0275</v>
+        <v>0.1</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="B27" s="23" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B28" s="23" t="n">
-        <v>0.1</v>
+        <v>0.22</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="B29" s="24" t="n">
-        <v>1800000</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="B30" s="25" t="n">
-        <v>0.5792</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="B31" s="25" t="n">
-        <v>0.4371</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="B32" s="17" t="n">
-        <v>52</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="B33" s="23" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B34" s="23" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B35" s="22" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="B36" s="26" t="n">
-        <v>0.0725</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="B37" s="17" t="n">
-        <v>25</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="B38" s="23" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B39" s="23" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="B40" s="23" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="B41" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="B42" s="23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="B43" s="23" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>125</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -2883,80 +2008,80 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C3" s="16" t="n">
+        <v>101</v>
+      </c>
+      <c r="C3" s="15" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>132</v>
+        <v>102</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>133</v>
+        <v>103</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>134</v>
+        <v>104</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>135</v>
+        <v>105</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>138</v>
+        <v>108</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>139</v>
+        <v>109</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>141</v>
+        <v>111</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>142</v>
+        <v>112</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C6" s="7" t="n">
+        <v>71</v>
+      </c>
+      <c r="C6" s="20" t="n">
         <v>5</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="K6" s="7" t="n">
+        <v>115</v>
+      </c>
+      <c r="K6" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="7" t="n">
+      <c r="L6" s="20" t="n">
         <v>0</v>
       </c>
       <c r="M6" s="9" t="n">
@@ -2966,18 +2091,18 @@
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C7" s="7" t="n">
+        <v>72</v>
+      </c>
+      <c r="C7" s="20" t="n">
         <v>6</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="K7" s="7" t="n">
+        <v>115</v>
+      </c>
+      <c r="K7" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="7" t="n">
+      <c r="L7" s="20" t="n">
         <v>0</v>
       </c>
       <c r="M7" s="9" t="n">
@@ -2986,21 +2111,21 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>146</v>
+        <v>116</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C8" s="7" t="n">
+        <v>71</v>
+      </c>
+      <c r="C8" s="20" t="n">
         <v>5</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="K8" s="7" t="n">
+        <v>115</v>
+      </c>
+      <c r="K8" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="7" t="n">
+      <c r="L8" s="20" t="n">
         <v>0</v>
       </c>
       <c r="M8" s="9" t="n">
@@ -3010,18 +2135,18 @@
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C9" s="7" t="n">
+        <v>72</v>
+      </c>
+      <c r="C9" s="20" t="n">
         <v>6</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="K9" s="7" t="n">
+        <v>115</v>
+      </c>
+      <c r="K9" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="L9" s="7" t="n">
+      <c r="L9" s="20" t="n">
         <v>0</v>
       </c>
       <c r="M9" s="9" t="n">
@@ -3030,45 +2155,45 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>147</v>
+        <v>117</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C10" s="7" t="n">
+        <v>71</v>
+      </c>
+      <c r="C10" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="D10" s="27" t="n">
+      <c r="D10" s="24" t="n">
         <f aca="false">Assumptions!$D$8/3</f>
         <v>34.6666666666667</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="25" t="n">
         <f aca="false">Assumptions!$F$8</f>
         <v>30</v>
       </c>
-      <c r="F10" s="28" t="n">
+      <c r="F10" s="26" t="n">
         <f aca="false">IF(C10=0,0,E10/C10)</f>
         <v>6</v>
       </c>
-      <c r="G10" s="19" t="n">
+      <c r="G10" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="H10" s="27" t="n">
+      <c r="H10" s="24" t="n">
         <f aca="false">Assumptions!$D$12/3</f>
         <v>17.6666666666667</v>
       </c>
-      <c r="I10" s="6" t="n">
+      <c r="I10" s="25" t="n">
         <f aca="false">Assumptions!$F$12</f>
         <v>15</v>
       </c>
-      <c r="J10" s="19" t="n">
+      <c r="J10" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="K10" s="7" t="n">
+      <c r="K10" s="20" t="n">
         <f aca="false">C10*D10*G10</f>
         <v>346.666666666667</v>
       </c>
-      <c r="L10" s="7" t="n">
+      <c r="L10" s="20" t="n">
         <f aca="false">C10*H10*J10</f>
         <v>88.3333333333333</v>
       </c>
@@ -3080,42 +2205,42 @@
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C11" s="7" t="n">
+        <v>72</v>
+      </c>
+      <c r="C11" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="D11" s="27" t="n">
+      <c r="D11" s="24" t="n">
         <f aca="false">Assumptions!$D$9/3</f>
         <v>34.6666666666667</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="25" t="n">
         <f aca="false">Assumptions!$F$9</f>
         <v>60</v>
       </c>
-      <c r="F11" s="28" t="n">
+      <c r="F11" s="26" t="n">
         <f aca="false">IF(C11=0,0,E11/C11)</f>
         <v>10</v>
       </c>
-      <c r="G11" s="19" t="n">
+      <c r="G11" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="H11" s="27" t="n">
+      <c r="H11" s="24" t="n">
         <f aca="false">Assumptions!$D$13/3</f>
         <v>17.6666666666667</v>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="I11" s="25" t="n">
         <f aca="false">Assumptions!$F$13</f>
         <v>20</v>
       </c>
-      <c r="J11" s="19" t="n">
+      <c r="J11" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="K11" s="7" t="n">
+      <c r="K11" s="20" t="n">
         <f aca="false">C11*D11*G11</f>
         <v>624</v>
       </c>
-      <c r="L11" s="7" t="n">
+      <c r="L11" s="20" t="n">
         <f aca="false">C11*H11*J11</f>
         <v>212</v>
       </c>
@@ -3126,45 +2251,45 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>148</v>
+        <v>118</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C12" s="7" t="n">
+        <v>71</v>
+      </c>
+      <c r="C12" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="D12" s="27" t="n">
+      <c r="D12" s="24" t="n">
         <f aca="false">Assumptions!$D$8/3</f>
         <v>34.6666666666667</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="E12" s="25" t="n">
         <f aca="false">Assumptions!$F$8</f>
         <v>30</v>
       </c>
-      <c r="F12" s="28" t="n">
+      <c r="F12" s="26" t="n">
         <f aca="false">IF(C12=0,0,E12/C12)</f>
         <v>6</v>
       </c>
-      <c r="G12" s="19" t="n">
+      <c r="G12" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="H12" s="27" t="n">
+      <c r="H12" s="24" t="n">
         <f aca="false">Assumptions!$D$12/3</f>
         <v>17.6666666666667</v>
       </c>
-      <c r="I12" s="6" t="n">
+      <c r="I12" s="25" t="n">
         <f aca="false">Assumptions!$F$12</f>
         <v>15</v>
       </c>
-      <c r="J12" s="19" t="n">
+      <c r="J12" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="K12" s="7" t="n">
+      <c r="K12" s="20" t="n">
         <f aca="false">C12*D12*G12</f>
         <v>346.666666666667</v>
       </c>
-      <c r="L12" s="7" t="n">
+      <c r="L12" s="20" t="n">
         <f aca="false">C12*H12*J12</f>
         <v>88.3333333333333</v>
       </c>
@@ -3176,42 +2301,42 @@
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C13" s="7" t="n">
+        <v>72</v>
+      </c>
+      <c r="C13" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="D13" s="27" t="n">
+      <c r="D13" s="24" t="n">
         <f aca="false">Assumptions!$D$9/3</f>
         <v>34.6666666666667</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="E13" s="25" t="n">
         <f aca="false">Assumptions!$F$9</f>
         <v>60</v>
       </c>
-      <c r="F13" s="28" t="n">
+      <c r="F13" s="26" t="n">
         <f aca="false">IF(C13=0,0,E13/C13)</f>
         <v>10</v>
       </c>
-      <c r="G13" s="19" t="n">
+      <c r="G13" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="H13" s="27" t="n">
+      <c r="H13" s="24" t="n">
         <f aca="false">Assumptions!$D$13/3</f>
         <v>17.6666666666667</v>
       </c>
-      <c r="I13" s="6" t="n">
+      <c r="I13" s="25" t="n">
         <f aca="false">Assumptions!$F$13</f>
         <v>20</v>
       </c>
-      <c r="J13" s="19" t="n">
+      <c r="J13" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="K13" s="7" t="n">
+      <c r="K13" s="20" t="n">
         <f aca="false">C13*D13*G13</f>
         <v>624</v>
       </c>
-      <c r="L13" s="7" t="n">
+      <c r="L13" s="20" t="n">
         <f aca="false">C13*H13*J13</f>
         <v>212</v>
       </c>
@@ -3222,45 +2347,45 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>149</v>
+        <v>119</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C14" s="7" t="n">
+        <v>71</v>
+      </c>
+      <c r="C14" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="D14" s="27" t="n">
+      <c r="D14" s="24" t="n">
         <f aca="false">Assumptions!$D$8/3</f>
         <v>34.6666666666667</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="E14" s="25" t="n">
         <f aca="false">Assumptions!$F$8</f>
         <v>30</v>
       </c>
-      <c r="F14" s="28" t="n">
+      <c r="F14" s="26" t="n">
         <f aca="false">IF(C14=0,0,E14/C14)</f>
         <v>6</v>
       </c>
-      <c r="G14" s="19" t="n">
+      <c r="G14" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="H14" s="27" t="n">
+      <c r="H14" s="24" t="n">
         <f aca="false">Assumptions!$D$12/3</f>
         <v>17.6666666666667</v>
       </c>
-      <c r="I14" s="6" t="n">
+      <c r="I14" s="25" t="n">
         <f aca="false">Assumptions!$F$12</f>
         <v>15</v>
       </c>
-      <c r="J14" s="19" t="n">
+      <c r="J14" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="K14" s="7" t="n">
+      <c r="K14" s="20" t="n">
         <f aca="false">C14*D14*G14</f>
         <v>346.666666666667</v>
       </c>
-      <c r="L14" s="7" t="n">
+      <c r="L14" s="20" t="n">
         <f aca="false">C14*H14*J14</f>
         <v>88.3333333333333</v>
       </c>
@@ -3272,42 +2397,42 @@
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C15" s="7" t="n">
+        <v>72</v>
+      </c>
+      <c r="C15" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="D15" s="27" t="n">
+      <c r="D15" s="24" t="n">
         <f aca="false">Assumptions!$D$9/3</f>
         <v>34.6666666666667</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="E15" s="25" t="n">
         <f aca="false">Assumptions!$F$9</f>
         <v>60</v>
       </c>
-      <c r="F15" s="28" t="n">
+      <c r="F15" s="26" t="n">
         <f aca="false">IF(C15=0,0,E15/C15)</f>
         <v>10</v>
       </c>
-      <c r="G15" s="19" t="n">
+      <c r="G15" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="H15" s="27" t="n">
+      <c r="H15" s="24" t="n">
         <f aca="false">Assumptions!$D$13/3</f>
         <v>17.6666666666667</v>
       </c>
-      <c r="I15" s="6" t="n">
+      <c r="I15" s="25" t="n">
         <f aca="false">Assumptions!$F$13</f>
         <v>20</v>
       </c>
-      <c r="J15" s="19" t="n">
+      <c r="J15" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="K15" s="7" t="n">
+      <c r="K15" s="20" t="n">
         <f aca="false">C15*D15*G15</f>
         <v>624</v>
       </c>
-      <c r="L15" s="7" t="n">
+      <c r="L15" s="20" t="n">
         <f aca="false">C15*H15*J15</f>
         <v>212</v>
       </c>
@@ -3318,45 +2443,45 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C16" s="7" t="n">
+        <v>71</v>
+      </c>
+      <c r="C16" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="D16" s="27" t="n">
+      <c r="D16" s="24" t="n">
         <f aca="false">Assumptions!$D$10/2</f>
         <v>35</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="E16" s="25" t="n">
         <f aca="false">Assumptions!$F$10</f>
         <v>80</v>
       </c>
-      <c r="F16" s="28" t="n">
+      <c r="F16" s="26" t="n">
         <f aca="false">IF(C16=0,0,E16/C16)</f>
         <v>16</v>
       </c>
-      <c r="G16" s="19" t="n">
+      <c r="G16" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="H16" s="27" t="n">
+      <c r="H16" s="24" t="n">
         <f aca="false">Assumptions!$D$14/2</f>
         <v>17</v>
       </c>
-      <c r="I16" s="6" t="n">
+      <c r="I16" s="25" t="n">
         <f aca="false">Assumptions!$F$14</f>
         <v>30</v>
       </c>
-      <c r="J16" s="19" t="n">
+      <c r="J16" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="K16" s="7" t="n">
+      <c r="K16" s="20" t="n">
         <f aca="false">C16*D16*G16</f>
         <v>525</v>
       </c>
-      <c r="L16" s="7" t="n">
+      <c r="L16" s="20" t="n">
         <f aca="false">C16*H16*J16</f>
         <v>170</v>
       </c>
@@ -3368,42 +2493,42 @@
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C17" s="7" t="n">
+        <v>72</v>
+      </c>
+      <c r="C17" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="D17" s="27" t="n">
+      <c r="D17" s="24" t="n">
         <f aca="false">Assumptions!$D$11/2</f>
         <v>35</v>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="E17" s="25" t="n">
         <f aca="false">Assumptions!$F$11</f>
         <v>100</v>
       </c>
-      <c r="F17" s="28" t="n">
+      <c r="F17" s="26" t="n">
         <f aca="false">IF(C17=0,0,E17/C17)</f>
         <v>16.6666666666667</v>
       </c>
-      <c r="G17" s="19" t="n">
+      <c r="G17" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="H17" s="27" t="n">
+      <c r="H17" s="24" t="n">
         <f aca="false">Assumptions!$D$15/2</f>
         <v>17</v>
       </c>
-      <c r="I17" s="6" t="n">
+      <c r="I17" s="25" t="n">
         <f aca="false">Assumptions!$F$15</f>
         <v>60</v>
       </c>
-      <c r="J17" s="19" t="n">
+      <c r="J17" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K17" s="7" t="n">
+      <c r="K17" s="20" t="n">
         <f aca="false">C17*D17*G17</f>
         <v>1050</v>
       </c>
-      <c r="L17" s="7" t="n">
+      <c r="L17" s="20" t="n">
         <f aca="false">C17*H17*J17</f>
         <v>306</v>
       </c>
@@ -3414,45 +2539,45 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C18" s="7" t="n">
+        <v>71</v>
+      </c>
+      <c r="C18" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="D18" s="27" t="n">
+      <c r="D18" s="24" t="n">
         <f aca="false">Assumptions!$D$10/2</f>
         <v>35</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="E18" s="25" t="n">
         <f aca="false">Assumptions!$F$10</f>
         <v>80</v>
       </c>
-      <c r="F18" s="28" t="n">
+      <c r="F18" s="26" t="n">
         <f aca="false">IF(C18=0,0,E18/C18)</f>
         <v>16</v>
       </c>
-      <c r="G18" s="19" t="n">
+      <c r="G18" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="H18" s="27" t="n">
+      <c r="H18" s="24" t="n">
         <f aca="false">Assumptions!$D$14/2</f>
         <v>17</v>
       </c>
-      <c r="I18" s="6" t="n">
+      <c r="I18" s="25" t="n">
         <f aca="false">Assumptions!$F$14</f>
         <v>30</v>
       </c>
-      <c r="J18" s="19" t="n">
+      <c r="J18" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="K18" s="7" t="n">
+      <c r="K18" s="20" t="n">
         <f aca="false">C18*D18*G18</f>
         <v>525</v>
       </c>
-      <c r="L18" s="7" t="n">
+      <c r="L18" s="20" t="n">
         <f aca="false">C18*H18*J18</f>
         <v>170</v>
       </c>
@@ -3464,42 +2589,42 @@
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C19" s="7" t="n">
+        <v>72</v>
+      </c>
+      <c r="C19" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="D19" s="27" t="n">
+      <c r="D19" s="24" t="n">
         <f aca="false">Assumptions!$D$11/2</f>
         <v>35</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="E19" s="25" t="n">
         <f aca="false">Assumptions!$F$11</f>
         <v>100</v>
       </c>
-      <c r="F19" s="28" t="n">
+      <c r="F19" s="26" t="n">
         <f aca="false">IF(C19=0,0,E19/C19)</f>
         <v>16.6666666666667</v>
       </c>
-      <c r="G19" s="19" t="n">
+      <c r="G19" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="H19" s="27" t="n">
+      <c r="H19" s="24" t="n">
         <f aca="false">Assumptions!$D$15/2</f>
         <v>17</v>
       </c>
-      <c r="I19" s="6" t="n">
+      <c r="I19" s="25" t="n">
         <f aca="false">Assumptions!$F$15</f>
         <v>60</v>
       </c>
-      <c r="J19" s="19" t="n">
+      <c r="J19" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K19" s="7" t="n">
+      <c r="K19" s="20" t="n">
         <f aca="false">C19*D19*G19</f>
         <v>1050</v>
       </c>
-      <c r="L19" s="7" t="n">
+      <c r="L19" s="20" t="n">
         <f aca="false">C19*H19*J19</f>
         <v>306</v>
       </c>
@@ -3510,7 +2635,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="K20" s="21" t="n">
         <f aca="false">SUM(K6:K19)</f>
@@ -3520,14 +2645,14 @@
         <f aca="false">SUM(L6:L19)</f>
         <v>1853</v>
       </c>
-      <c r="M20" s="10" t="n">
+      <c r="M20" s="13" t="n">
         <f aca="false">SUM(M6:M19)</f>
         <v>118725</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>152</v>
+        <v>122</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -3541,60 +2666,60 @@
       <c r="K23" s="5"/>
       <c r="L23" s="5"/>
       <c r="M23" s="5" t="s">
-        <v>153</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>154</v>
+        <v>124</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="M24" s="18" t="n">
+        <v>125</v>
+      </c>
+      <c r="M24" s="17" t="n">
         <v>70000</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>156</v>
+        <v>126</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="M25" s="18" t="n">
+        <v>127</v>
+      </c>
+      <c r="M25" s="17" t="n">
         <v>50000</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="M26" s="18" t="n">
+        <v>128</v>
+      </c>
+      <c r="M26" s="17" t="n">
         <v>7000</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>159</v>
+        <v>129</v>
       </c>
       <c r="M27" s="9" t="n">
-        <f aca="false">SUM(M24:M26)*Assumptions!$B$34</f>
+        <f aca="false">SUM(M24:M26)*Assumptions!$B$28</f>
         <v>27940</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="M28" s="10" t="n">
+        <v>130</v>
+      </c>
+      <c r="M28" s="13" t="n">
         <f aca="false">SUM(M24:M27)</f>
         <v>154940</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="M29" s="9" t="n">
         <f aca="false">M20</f>
@@ -3603,27 +2728,27 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>162</v>
+        <v>132</v>
       </c>
       <c r="M30" s="9" t="n">
-        <f aca="false">M29*Assumptions!$B$33</f>
+        <f aca="false">M29*Assumptions!$B$27</f>
         <v>11872.5</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="M31" s="10" t="n">
-        <f aca="false">M29*(1+Assumptions!$B$33)</f>
+        <v>133</v>
+      </c>
+      <c r="M31" s="13" t="n">
+        <f aca="false">M29*(1+Assumptions!$B$27)</f>
         <v>130597.5</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="M32" s="10" t="n">
+        <v>134</v>
+      </c>
+      <c r="M32" s="13" t="n">
         <f aca="false">Labor!$M$28+Labor!$M$31</f>
         <v>285537.5</v>
       </c>
@@ -3656,626 +2781,353 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>165</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>169</v>
+        <v>18</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>170</v>
+        <v>19</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>171</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C4" s="24" t="n">
+        <v>141</v>
+      </c>
+      <c r="C4" s="8" t="n">
         <v>1800000</v>
       </c>
-      <c r="D4" s="18" t="n">
+      <c r="D4" s="17" t="n">
         <v>1800000</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>174</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="C5" s="24" t="n">
+        <v>143</v>
+      </c>
+      <c r="C5" s="8" t="n">
         <v>36000</v>
       </c>
-      <c r="D5" s="18" t="n">
+      <c r="D5" s="17" t="n">
         <v>36000</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>176</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C6" s="24" t="n">
+        <v>145</v>
+      </c>
+      <c r="C6" s="8" t="n">
         <v>8000</v>
       </c>
-      <c r="D6" s="18" t="n">
+      <c r="D6" s="17" t="n">
         <v>8000</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>179</v>
+        <v>147</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C7" s="24" t="n">
+        <v>148</v>
+      </c>
+      <c r="C7" s="8" t="n">
         <v>25000</v>
       </c>
-      <c r="D7" s="18" t="n">
+      <c r="D7" s="17" t="n">
         <v>25000</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="C8" s="24" t="n">
+        <v>150</v>
+      </c>
+      <c r="C8" s="8" t="n">
         <v>200000</v>
       </c>
-      <c r="D8" s="18" t="n">
+      <c r="D8" s="17" t="n">
         <v>200000</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>183</v>
+        <v>151</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>184</v>
+        <v>152</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="C9" s="24" t="n">
+        <v>153</v>
+      </c>
+      <c r="C9" s="8" t="n">
         <v>100000</v>
       </c>
-      <c r="D9" s="18" t="n">
+      <c r="D9" s="17" t="n">
         <v>100000</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>184</v>
+        <v>152</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="C10" s="24" t="n">
+        <v>154</v>
+      </c>
+      <c r="C10" s="8" t="n">
         <v>100000</v>
       </c>
-      <c r="D10" s="18" t="n">
+      <c r="D10" s="17" t="n">
         <v>100000</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>184</v>
+        <v>152</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="C11" s="24" t="n">
+        <v>155</v>
+      </c>
+      <c r="C11" s="8" t="n">
         <v>75000</v>
       </c>
-      <c r="D11" s="18" t="n">
+      <c r="D11" s="17" t="n">
         <v>75000</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>188</v>
+        <v>156</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="C12" s="24" t="n">
+        <v>157</v>
+      </c>
+      <c r="C12" s="8" t="n">
         <v>175000</v>
       </c>
-      <c r="D12" s="18" t="n">
+      <c r="D12" s="17" t="n">
         <v>175000</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>190</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>188</v>
+        <v>156</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="C13" s="24" t="n">
+        <v>159</v>
+      </c>
+      <c r="C13" s="8" t="n">
         <v>35000</v>
       </c>
-      <c r="D13" s="18" t="n">
+      <c r="D13" s="17" t="n">
         <v>35000</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>190</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>188</v>
+        <v>156</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C14" s="24" t="n">
+        <v>160</v>
+      </c>
+      <c r="C14" s="8" t="n">
         <v>30000</v>
       </c>
-      <c r="D14" s="18" t="n">
+      <c r="D14" s="17" t="n">
         <v>30000</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>190</v>
+        <v>158</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>193</v>
+        <v>161</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="C15" s="24" t="n">
+        <v>162</v>
+      </c>
+      <c r="C15" s="8" t="n">
         <v>75000</v>
       </c>
-      <c r="D15" s="18" t="n">
+      <c r="D15" s="17" t="n">
         <v>75000</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>195</v>
+        <v>163</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>196</v>
+        <v>164</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="C16" s="24" t="n">
+        <v>165</v>
+      </c>
+      <c r="C16" s="8" t="n">
         <v>20000</v>
       </c>
-      <c r="D16" s="18" t="n">
+      <c r="D16" s="17" t="n">
         <v>20000</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>196</v>
+        <v>164</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="C17" s="24" t="n">
+        <v>166</v>
+      </c>
+      <c r="C17" s="8" t="n">
         <v>20000</v>
       </c>
-      <c r="D17" s="18" t="n">
+      <c r="D17" s="17" t="n">
         <v>20000</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>199</v>
+        <v>167</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="C18" s="24" t="n">
+        <v>168</v>
+      </c>
+      <c r="C18" s="8" t="n">
         <v>20000</v>
       </c>
-      <c r="D18" s="18" t="n">
+      <c r="D18" s="17" t="n">
         <v>20000</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>201</v>
+        <v>169</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="C19" s="24" t="n">
+        <v>170</v>
+      </c>
+      <c r="C19" s="8" t="n">
         <v>25000</v>
       </c>
-      <c r="D19" s="18" t="n">
+      <c r="D19" s="17" t="n">
         <v>25000</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C20" s="10" t="n">
+        <v>171</v>
+      </c>
+      <c r="C20" s="13" t="n">
         <f aca="false">SUMIFS(C4:C19,$A$4:$A$19,"Acquisition")</f>
         <v>1844000</v>
       </c>
-      <c r="D20" s="10" t="n">
+      <c r="D20" s="13" t="n">
         <f aca="false">SUMIFS(D4:D19,$A$4:$A$19,"Acquisition")</f>
         <v>1844000</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="C21" s="12" t="n">
+        <v>172</v>
+      </c>
+      <c r="C21" s="6" t="n">
         <f aca="false">SUM(C4:C19)-C20</f>
         <v>900000</v>
       </c>
-      <c r="D21" s="12" t="n">
+      <c r="D21" s="6" t="n">
         <f aca="false">SUM(D4:D19)-D20</f>
         <v>900000</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="C22" s="9" t="n">
-        <f aca="false">C21*Assumptions!$B$28</f>
+        <f aca="false">C21*Assumptions!$B$26</f>
         <v>90000</v>
       </c>
       <c r="D22" s="9" t="n">
-        <f aca="false">D21*Assumptions!$B$28</f>
+        <f aca="false">D21*Assumptions!$B$26</f>
         <v>90000</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="C23" s="10" t="n">
+        <v>174</v>
+      </c>
+      <c r="C23" s="13" t="n">
         <f aca="false">C20+C21+C22</f>
         <v>2834000</v>
       </c>
-      <c r="D23" s="10" t="n">
+      <c r="D23" s="13" t="n">
         <f aca="false">D20+D21+D22</f>
         <v>2834000</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="70"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="B4" s="8" t="n">
-        <f aca="false">Assumptions!$B$29*(Assumptions!$B$30+Assumptions!$B$31)/100</f>
-        <v>18293.4</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="B5" s="18" t="n">
-        <v>40000</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="B6" s="18" t="n">
-        <v>36000</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="B7" s="18" t="n">
-        <v>20000</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="B8" s="18" t="n">
-        <v>15000</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="B9" s="18" t="n">
-        <v>7200</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="B10" s="18" t="n">
-        <v>3000</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B11" s="18" t="n">
-        <v>3500</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B12" s="18" t="n">
-        <v>9000</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="B13" s="18" t="n">
-        <v>3600</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="B14" s="18" t="n">
-        <v>15000</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="B15" s="18" t="n">
-        <v>8000</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="B16" s="10" t="n">
-        <f aca="false">SUM(B4:B15)</f>
-        <v>178593.4</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="B3" s="8" t="n">
-        <f aca="false">Capex!$C$23</f>
-        <v>2834000</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="B4" s="15" t="n">
-        <f aca="false">Assumptions!$B$35</f>
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="B5" s="9" t="n">
-        <f aca="false">B3*B4</f>
-        <v>1983800</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="B6" s="9" t="n">
-        <f aca="false">B3-B5</f>
-        <v>850200</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="B7" s="29" t="n">
-        <f aca="false">Assumptions!$B$36</f>
-        <v>0.0725</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="B8" s="6" t="n">
-        <f aca="false">Assumptions!$B$37</f>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="B9" s="12" t="n">
-        <f aca="false">-PMT(B7/12,B8*12,B5)*12</f>
-        <v>172068.510839515</v>
       </c>
     </row>
   </sheetData>

--- a/806-Ramseur-PnL.xlsx
+++ b/806-Ramseur-PnL.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="171">
   <si>
     <t xml:space="preserve">806 E Ramseur Mini Golf + Bar — P&amp;L model</t>
   </si>
@@ -35,7 +35,7 @@
     <t xml:space="preserve">1. Edit inputs on the Assumptions sheet. Blue text = input. Yellow fill = key lever.</t>
   </si>
   <si>
-    <t xml:space="preserve">2. The period table (Assumptions!D8:I15) matches the Revenue Estimates web page. 'Copy period table for Excel' on that page pastes into D8.</t>
+    <t xml:space="preserve">2. The period table (Assumptions!D8:I35) matches the Revenue Estimates web page. 'Copy period table for Excel' on that page pastes into D8.</t>
   </si>
   <si>
     <t xml:space="preserve">3. Set gross margin per revenue line in Assumptions!B19:B23.</t>
@@ -197,13 +197,13 @@
     <t xml:space="preserve">Average event package</t>
   </si>
   <si>
-    <t xml:space="preserve">Revenue split 8/12 summer, 4/12 winter on P&amp;L</t>
+    <t xml:space="preserve">Dollars per event</t>
   </si>
   <si>
     <t xml:space="preserve">Season</t>
   </si>
   <si>
-    <t xml:space="preserve">Day type</t>
+    <t xml:space="preserve">Day</t>
   </si>
   <si>
     <t xml:space="preserve">Daypart</t>
@@ -236,7 +236,7 @@
     <t xml:space="preserve">Summer</t>
   </si>
   <si>
-    <t xml:space="preserve">Weekday (Wed-Fri)</t>
+    <t xml:space="preserve">Monday</t>
   </si>
   <si>
     <t xml:space="preserve">Afternoon 12-5 pm</t>
@@ -245,7 +245,22 @@
     <t xml:space="preserve">Evening 5-11 pm</t>
   </si>
   <si>
-    <t xml:space="preserve">Weekend (Sat-Sun)</t>
+    <t xml:space="preserve">Tuesday</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wednesday</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thursday</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Friday</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saturday</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunday</t>
   </si>
   <si>
     <t xml:space="preserve">Winter</t>
@@ -254,7 +269,7 @@
     <t xml:space="preserve">Total</t>
   </si>
   <si>
-    <t xml:space="preserve">Day counts: calendar 2027, closed Mon-Tue. Players are per daypart per day.</t>
+    <t xml:space="preserve">Days = count of that weekday in each season, calendar 2027. Mon-Tue default to 0 players (closed). Players are per daypart per day.</t>
   </si>
   <si>
     <t xml:space="preserve">Revenue line</t>
@@ -332,9 +347,6 @@
     <t xml:space="preserve">Hourly wage, all hourly staff</t>
   </si>
   <si>
-    <t xml:space="preserve">Day</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hours</t>
   </si>
   <si>
@@ -366,30 +378,6 @@
   </si>
   <si>
     <t xml:space="preserve">Annual wages</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monday</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Closed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tuesday</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wednesday</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thursday</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Friday</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saturday</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunday</t>
   </si>
   <si>
     <t xml:space="preserve">Annual labor</t>
@@ -691,7 +679,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -785,10 +773,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1200,8 +1184,8 @@
         <v>22</v>
       </c>
       <c r="B6" s="6" t="n">
-        <f aca="false">SUM(Assumptions!$J$8:$J$15)*Assumptions!$B$3+SUMPRODUCT(Assumptions!$J$8:$J$15,Assumptions!$G$8:$G$15)+SUMPRODUCT(Assumptions!$J$8:$J$15,Assumptions!$H$8:$H$15)+SUMPRODUCT(Assumptions!$J$8:$J$15,Assumptions!$I$8:$I$15)+Assumptions!$B$4*Assumptions!$B$5</f>
-        <v>846350</v>
+        <f aca="false">SUM(Assumptions!$J$8:$J$35)*Assumptions!$B$3+SUMPRODUCT(Assumptions!$J$8:$J$35,Assumptions!$G$8:$G$35)+SUMPRODUCT(Assumptions!$J$8:$J$35,Assumptions!$H$8:$H$35)+SUMPRODUCT(Assumptions!$J$8:$J$35,Assumptions!$I$8:$I$35)+Assumptions!$B$4*Assumptions!$B$5</f>
+        <v>766350</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>23</v>
@@ -1212,8 +1196,8 @@
         <v>24</v>
       </c>
       <c r="B7" s="6" t="n">
-        <f aca="false">SUM(Assumptions!$J$8:$J$15)*Assumptions!$B$3*Assumptions!$B$19+SUMPRODUCT(Assumptions!$J$8:$J$15,Assumptions!$G$8:$G$15)*Assumptions!$B$20+SUMPRODUCT(Assumptions!$J$8:$J$15,Assumptions!$H$8:$H$15)*Assumptions!$B$21+SUMPRODUCT(Assumptions!$J$8:$J$15,Assumptions!$I$8:$I$15)*Assumptions!$B$22+Assumptions!$B$4*Assumptions!$B$5*Assumptions!$B$23</f>
-        <v>582416.5</v>
+        <f aca="false">SUM(Assumptions!$J$8:$J$35)*Assumptions!$B$3*Assumptions!$B$40+SUMPRODUCT(Assumptions!$J$8:$J$35,Assumptions!$G$8:$G$35)*Assumptions!$B$41+SUMPRODUCT(Assumptions!$J$8:$J$35,Assumptions!$H$8:$H$35)*Assumptions!$B$42+SUMPRODUCT(Assumptions!$J$8:$J$35,Assumptions!$I$8:$I$35)*Assumptions!$B$43+Assumptions!$B$4*Assumptions!$B$5*Assumptions!$B$44</f>
+        <v>522416.5</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>25</v>
@@ -1225,7 +1209,7 @@
       </c>
       <c r="B8" s="7" t="n">
         <f aca="false">IF($B$6=0,0,$B$7/$B$6)</f>
-        <v>0.688150883204348</v>
+        <v>0.681694395511189</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1393,7 +1377,7 @@
       </c>
       <c r="B25" s="13" t="n">
         <f aca="false">$B$7-$B$24</f>
-        <v>36236</v>
+        <v>-23764</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1407,7 +1391,7 @@
       </c>
       <c r="B28" s="9" t="n">
         <f aca="false">$B$25</f>
-        <v>36236</v>
+        <v>-23764</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1425,7 +1409,7 @@
       </c>
       <c r="B30" s="12" t="n">
         <f aca="false">Capex!$C$23-Capex!$C$4</f>
-        <v>1034000</v>
+        <v>940500</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>49</v>
@@ -1437,7 +1421,7 @@
       </c>
       <c r="B31" s="13" t="n">
         <f aca="false">$B$29+$B$30</f>
-        <v>1574000</v>
+        <v>1480500</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1446,7 +1430,7 @@
       </c>
       <c r="B32" s="14" t="n">
         <f aca="false">IF($B$31=0,0,$B$25/$B$31)</f>
-        <v>0.0230216010165184</v>
+        <v>-0.0160513340087808</v>
       </c>
     </row>
   </sheetData>
@@ -1465,7 +1449,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1499,7 +1483,7 @@
         <v>54</v>
       </c>
       <c r="B4" s="16" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>55</v>
@@ -1510,7 +1494,7 @@
         <v>56</v>
       </c>
       <c r="B5" s="17" t="n">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>57</v>
@@ -1562,13 +1546,13 @@
         <v>71</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>104</v>
+        <v>35</v>
       </c>
       <c r="E8" s="16" t="n">
         <v>5</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G8" s="19" t="n">
         <v>6</v>
@@ -1581,11 +1565,11 @@
       </c>
       <c r="J8" s="20" t="n">
         <f aca="false">D8*F8</f>
-        <v>3120</v>
+        <v>0</v>
       </c>
       <c r="K8" s="9" t="n">
         <f aca="false">J8*(Assumptions!$B$3+G8+H8+I8)</f>
-        <v>68640</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1599,13 +1583,13 @@
         <v>72</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>104</v>
+        <v>35</v>
       </c>
       <c r="E9" s="16" t="n">
         <v>6</v>
       </c>
       <c r="F9" s="18" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="G9" s="19" t="n">
         <v>8</v>
@@ -1618,11 +1602,11 @@
       </c>
       <c r="J9" s="20" t="n">
         <f aca="false">D9*F9</f>
-        <v>6240</v>
+        <v>0</v>
       </c>
       <c r="K9" s="9" t="n">
         <f aca="false">J9*(Assumptions!$B$3+G9+H9+I9)</f>
-        <v>162240</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1636,13 +1620,13 @@
         <v>71</v>
       </c>
       <c r="D10" s="16" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="E10" s="16" t="n">
         <v>5</v>
       </c>
       <c r="F10" s="18" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="G10" s="19" t="n">
         <v>6</v>
@@ -1651,15 +1635,15 @@
         <v>4</v>
       </c>
       <c r="I10" s="19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J10" s="20" t="n">
         <f aca="false">D10*F10</f>
-        <v>5600</v>
+        <v>0</v>
       </c>
       <c r="K10" s="9" t="n">
         <f aca="false">J10*(Assumptions!$B$3+G10+H10+I10)</f>
-        <v>151200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1673,13 +1657,13 @@
         <v>72</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="E11" s="16" t="n">
         <v>6</v>
       </c>
       <c r="F11" s="18" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G11" s="19" t="n">
         <v>8</v>
@@ -1688,103 +1672,103 @@
         <v>1</v>
       </c>
       <c r="I11" s="19" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="J11" s="20" t="n">
         <f aca="false">D11*F11</f>
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="K11" s="9" t="n">
         <f aca="false">J11*(Assumptions!$B$3+G11+H11+I11)</f>
-        <v>259000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>70</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>71</v>
       </c>
       <c r="D12" s="16" t="n">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="E12" s="16" t="n">
         <v>5</v>
       </c>
       <c r="F12" s="18" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G12" s="19" t="n">
         <v>6</v>
       </c>
       <c r="H12" s="19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I12" s="19" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="20" t="n">
         <f aca="false">D12*F12</f>
-        <v>795</v>
+        <v>1020</v>
       </c>
       <c r="K12" s="9" t="n">
         <f aca="false">J12*(Assumptions!$B$3+G12+H12+I12)</f>
-        <v>14310</v>
+        <v>22440</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>70</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>72</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="E13" s="16" t="n">
         <v>6</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="G13" s="19" t="n">
         <v>8</v>
       </c>
       <c r="H13" s="19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" s="19" t="n">
         <v>5</v>
       </c>
       <c r="J13" s="20" t="n">
         <f aca="false">D13*F13</f>
-        <v>1060</v>
+        <v>2040</v>
       </c>
       <c r="K13" s="9" t="n">
         <f aca="false">J13*(Assumptions!$B$3+G13+H13+I13)</f>
-        <v>26500</v>
+        <v>53040</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>71</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E14" s="16" t="n">
         <v>5</v>
@@ -1796,32 +1780,32 @@
         <v>6</v>
       </c>
       <c r="H14" s="19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I14" s="19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J14" s="20" t="n">
         <f aca="false">D14*F14</f>
-        <v>1020</v>
+        <v>1050</v>
       </c>
       <c r="K14" s="9" t="n">
         <f aca="false">J14*(Assumptions!$B$3+G14+H14+I14)</f>
-        <v>23460</v>
+        <v>23100</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>72</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E15" s="16" t="n">
         <v>6</v>
@@ -1833,146 +1817,886 @@
         <v>8</v>
       </c>
       <c r="H15" s="19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="19" t="n">
         <v>5</v>
       </c>
       <c r="J15" s="20" t="n">
         <f aca="false">D15*F15</f>
-        <v>2040</v>
+        <v>2100</v>
       </c>
       <c r="K15" s="9" t="n">
         <f aca="false">J15*(Assumptions!$B$3+G15+H15+I15)</f>
-        <v>51000</v>
+        <v>54600</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="J16" s="21" t="n">
-        <f aca="false">SUM(J8:J15)</f>
-        <v>26875</v>
-      </c>
-      <c r="K16" s="13" t="n">
-        <f aca="false">SUM(K8:K15)</f>
-        <v>756350</v>
+      <c r="A16" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D16" s="16" t="n">
+        <v>35</v>
+      </c>
+      <c r="E16" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" s="18" t="n">
+        <v>30</v>
+      </c>
+      <c r="G16" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H16" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="20" t="n">
+        <f aca="false">D16*F16</f>
+        <v>1050</v>
+      </c>
+      <c r="K16" s="9" t="n">
+        <f aca="false">J16*(Assumptions!$B$3+G16+H16+I16)</f>
+        <v>23100</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>76</v>
       </c>
+      <c r="C17" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D17" s="16" t="n">
+        <v>35</v>
+      </c>
+      <c r="E17" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="F17" s="18" t="n">
+        <v>60</v>
+      </c>
+      <c r="G17" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="H17" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="J17" s="20" t="n">
+        <f aca="false">D17*F17</f>
+        <v>2100</v>
+      </c>
+      <c r="K17" s="9" t="n">
+        <f aca="false">J17*(Assumptions!$B$3+G17+H17+I17)</f>
+        <v>54600</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>79</v>
+      <c r="C18" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" s="16" t="n">
+        <v>35</v>
+      </c>
+      <c r="E18" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F18" s="18" t="n">
+        <v>80</v>
+      </c>
+      <c r="G18" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H18" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I18" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="J18" s="20" t="n">
+        <f aca="false">D18*F18</f>
+        <v>2800</v>
+      </c>
+      <c r="K18" s="9" t="n">
+        <f aca="false">J18*(Assumptions!$B$3+G18+H18+I18)</f>
+        <v>75600</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B19" s="22" t="n">
-        <v>0.95</v>
+        <v>69</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>77</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>81</v>
+        <v>72</v>
+      </c>
+      <c r="D19" s="16" t="n">
+        <v>35</v>
+      </c>
+      <c r="E19" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="F19" s="18" t="n">
+        <v>100</v>
+      </c>
+      <c r="G19" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="H19" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="J19" s="20" t="n">
+        <f aca="false">D19*F19</f>
+        <v>3500</v>
+      </c>
+      <c r="K19" s="9" t="n">
+        <f aca="false">J19*(Assumptions!$B$3+G19+H19+I19)</f>
+        <v>129500</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B20" s="22" t="n">
-        <v>0.15</v>
+        <v>69</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>78</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>83</v>
+        <v>71</v>
+      </c>
+      <c r="D20" s="16" t="n">
+        <v>35</v>
+      </c>
+      <c r="E20" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" s="18" t="n">
+        <v>80</v>
+      </c>
+      <c r="G20" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H20" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I20" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="J20" s="20" t="n">
+        <f aca="false">D20*F20</f>
+        <v>2800</v>
+      </c>
+      <c r="K20" s="9" t="n">
+        <f aca="false">J20*(Assumptions!$B$3+G20+H20+I20)</f>
+        <v>75600</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B21" s="22" t="n">
-        <v>0.7</v>
+        <v>69</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>78</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>85</v>
+        <v>72</v>
+      </c>
+      <c r="D21" s="16" t="n">
+        <v>35</v>
+      </c>
+      <c r="E21" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="F21" s="18" t="n">
+        <v>100</v>
+      </c>
+      <c r="G21" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="H21" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="J21" s="20" t="n">
+        <f aca="false">D21*F21</f>
+        <v>3500</v>
+      </c>
+      <c r="K21" s="9" t="n">
+        <f aca="false">J21*(Assumptions!$B$3+G21+H21+I21)</f>
+        <v>129500</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B22" s="22" t="n">
-        <v>0.76</v>
+        <v>79</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>87</v>
+        <v>71</v>
+      </c>
+      <c r="D22" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="E22" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F22" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H22" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="20" t="n">
+        <f aca="false">D22*F22</f>
+        <v>0</v>
+      </c>
+      <c r="K22" s="9" t="n">
+        <f aca="false">J22*(Assumptions!$B$3+G22+H22+I22)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B23" s="22" t="n">
-        <v>0.75</v>
+        <v>79</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>89</v>
+        <v>72</v>
+      </c>
+      <c r="D23" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="E23" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="F23" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="H23" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="J23" s="20" t="n">
+        <f aca="false">D23*F23</f>
+        <v>0</v>
+      </c>
+      <c r="K23" s="9" t="n">
+        <f aca="false">J23*(Assumptions!$B$3+G23+H23+I23)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D24" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="E24" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F24" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H24" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="20" t="n">
+        <f aca="false">D24*F24</f>
+        <v>0</v>
+      </c>
+      <c r="K24" s="9" t="n">
+        <f aca="false">J24*(Assumptions!$B$3+G24+H24+I24)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>92</v>
+      <c r="A25" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D25" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="E25" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="F25" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="H25" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="J25" s="20" t="n">
+        <f aca="false">D25*F25</f>
+        <v>0</v>
+      </c>
+      <c r="K25" s="9" t="n">
+        <f aca="false">J25*(Assumptions!$B$3+G25+H25+I25)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="B26" s="23" t="n">
-        <v>0.1</v>
+        <v>79</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>74</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>94</v>
+        <v>71</v>
+      </c>
+      <c r="D26" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="E26" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" s="18" t="n">
+        <v>15</v>
+      </c>
+      <c r="G26" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H26" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="20" t="n">
+        <f aca="false">D26*F26</f>
+        <v>270</v>
+      </c>
+      <c r="K26" s="9" t="n">
+        <f aca="false">J26*(Assumptions!$B$3+G26+H26+I26)</f>
+        <v>4860</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B27" s="23" t="n">
-        <v>0.1</v>
+        <v>79</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>74</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>96</v>
+        <v>72</v>
+      </c>
+      <c r="D27" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="E27" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="F27" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="G27" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="H27" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="J27" s="20" t="n">
+        <f aca="false">D27*F27</f>
+        <v>360</v>
+      </c>
+      <c r="K27" s="9" t="n">
+        <f aca="false">J27*(Assumptions!$B$3+G27+H27+I27)</f>
+        <v>9000</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D28" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="E28" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" s="18" t="n">
+        <v>15</v>
+      </c>
+      <c r="G28" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H28" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="20" t="n">
+        <f aca="false">D28*F28</f>
+        <v>255</v>
+      </c>
+      <c r="K28" s="9" t="n">
+        <f aca="false">J28*(Assumptions!$B$3+G28+H28+I28)</f>
+        <v>4590</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D29" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="E29" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="F29" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="G29" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="H29" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="J29" s="20" t="n">
+        <f aca="false">D29*F29</f>
+        <v>340</v>
+      </c>
+      <c r="K29" s="9" t="n">
+        <f aca="false">J29*(Assumptions!$B$3+G29+H29+I29)</f>
+        <v>8500</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D30" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="E30" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F30" s="18" t="n">
+        <v>15</v>
+      </c>
+      <c r="G30" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H30" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="20" t="n">
+        <f aca="false">D30*F30</f>
+        <v>270</v>
+      </c>
+      <c r="K30" s="9" t="n">
+        <f aca="false">J30*(Assumptions!$B$3+G30+H30+I30)</f>
+        <v>4860</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D31" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="E31" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="F31" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="G31" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="H31" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="J31" s="20" t="n">
+        <f aca="false">D31*F31</f>
+        <v>360</v>
+      </c>
+      <c r="K31" s="9" t="n">
+        <f aca="false">J31*(Assumptions!$B$3+G31+H31+I31)</f>
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D32" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="E32" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F32" s="18" t="n">
+        <v>30</v>
+      </c>
+      <c r="G32" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H32" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="J32" s="20" t="n">
+        <f aca="false">D32*F32</f>
+        <v>510</v>
+      </c>
+      <c r="K32" s="9" t="n">
+        <f aca="false">J32*(Assumptions!$B$3+G32+H32+I32)</f>
+        <v>11730</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D33" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="E33" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="F33" s="18" t="n">
+        <v>60</v>
+      </c>
+      <c r="G33" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="H33" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="J33" s="20" t="n">
+        <f aca="false">D33*F33</f>
+        <v>1020</v>
+      </c>
+      <c r="K33" s="9" t="n">
+        <f aca="false">J33*(Assumptions!$B$3+G33+H33+I33)</f>
+        <v>25500</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D34" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="E34" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F34" s="18" t="n">
+        <v>30</v>
+      </c>
+      <c r="G34" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H34" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="J34" s="20" t="n">
+        <f aca="false">D34*F34</f>
+        <v>510</v>
+      </c>
+      <c r="K34" s="9" t="n">
+        <f aca="false">J34*(Assumptions!$B$3+G34+H34+I34)</f>
+        <v>11730</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D35" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="E35" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="F35" s="18" t="n">
+        <v>60</v>
+      </c>
+      <c r="G35" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="H35" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="J35" s="20" t="n">
+        <f aca="false">D35*F35</f>
+        <v>1020</v>
+      </c>
+      <c r="K35" s="9" t="n">
+        <f aca="false">J35*(Assumptions!$B$3+G35+H35+I35)</f>
+        <v>25500</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="J36" s="21" t="n">
+        <f aca="false">SUM(J8:J35)</f>
+        <v>26875</v>
+      </c>
+      <c r="K36" s="13" t="n">
+        <f aca="false">SUM(K8:K35)</f>
+        <v>756350</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B40" s="22" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B41" s="22" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B42" s="22" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B43" s="22" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B44" s="22" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C46" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="B28" s="23" t="n">
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B47" s="23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B48" s="23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B49" s="23" t="n">
         <v>0.22</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>98</v>
+      <c r="C49" s="3" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -2008,17 +2732,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C3" s="15" t="n">
         <v>15</v>
@@ -2026,48 +2750,48 @@
     </row>
     <row r="5" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>60</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>71</v>
@@ -2075,16 +2799,42 @@
       <c r="C6" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>115</v>
+      <c r="D6" s="24" t="n">
+        <f aca="false">Assumptions!$D$8</f>
+        <v>35</v>
+      </c>
+      <c r="E6" s="24" t="n">
+        <f aca="false">Assumptions!$F$8</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="25" t="n">
+        <f aca="false">IF(C6=0,0,E6/C6)</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="24" t="n">
+        <f aca="false">Assumptions!$D$22</f>
+        <v>17</v>
+      </c>
+      <c r="I6" s="24" t="n">
+        <f aca="false">Assumptions!$F$22</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="K6" s="20" t="n">
+        <f aca="false">C6*D6*G6</f>
         <v>0</v>
       </c>
       <c r="L6" s="20" t="n">
+        <f aca="false">C6*H6*J6</f>
         <v>0</v>
       </c>
       <c r="M6" s="9" t="n">
+        <f aca="false">(K6+L6)*Labor!$C$3</f>
         <v>0</v>
       </c>
     </row>
@@ -2096,22 +2846,48 @@
       <c r="C7" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>115</v>
+      <c r="D7" s="24" t="n">
+        <f aca="false">Assumptions!$D$9</f>
+        <v>35</v>
+      </c>
+      <c r="E7" s="24" t="n">
+        <f aca="false">Assumptions!$F$9</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="25" t="n">
+        <f aca="false">IF(C7=0,0,E7/C7)</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="24" t="n">
+        <f aca="false">Assumptions!$D$23</f>
+        <v>17</v>
+      </c>
+      <c r="I7" s="24" t="n">
+        <f aca="false">Assumptions!$F$23</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="K7" s="20" t="n">
+        <f aca="false">C7*D7*G7</f>
         <v>0</v>
       </c>
       <c r="L7" s="20" t="n">
+        <f aca="false">C7*H7*J7</f>
         <v>0</v>
       </c>
       <c r="M7" s="9" t="n">
+        <f aca="false">(K7+L7)*Labor!$C$3</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>116</v>
+        <v>73</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>71</v>
@@ -2119,16 +2895,42 @@
       <c r="C8" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>115</v>
+      <c r="D8" s="24" t="n">
+        <f aca="false">Assumptions!$D$10</f>
+        <v>35</v>
+      </c>
+      <c r="E8" s="24" t="n">
+        <f aca="false">Assumptions!$F$10</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="25" t="n">
+        <f aca="false">IF(C8=0,0,E8/C8)</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="24" t="n">
+        <f aca="false">Assumptions!$D$24</f>
+        <v>17</v>
+      </c>
+      <c r="I8" s="24" t="n">
+        <f aca="false">Assumptions!$F$24</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="K8" s="20" t="n">
+        <f aca="false">C8*D8*G8</f>
         <v>0</v>
       </c>
       <c r="L8" s="20" t="n">
+        <f aca="false">C8*H8*J8</f>
         <v>0</v>
       </c>
       <c r="M8" s="9" t="n">
+        <f aca="false">(K8+L8)*Labor!$C$3</f>
         <v>0</v>
       </c>
     </row>
@@ -2140,22 +2942,48 @@
       <c r="C9" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>115</v>
+      <c r="D9" s="24" t="n">
+        <f aca="false">Assumptions!$D$11</f>
+        <v>35</v>
+      </c>
+      <c r="E9" s="24" t="n">
+        <f aca="false">Assumptions!$F$11</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="25" t="n">
+        <f aca="false">IF(C9=0,0,E9/C9)</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="24" t="n">
+        <f aca="false">Assumptions!$D$25</f>
+        <v>17</v>
+      </c>
+      <c r="I9" s="24" t="n">
+        <f aca="false">Assumptions!$F$25</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="K9" s="20" t="n">
+        <f aca="false">C9*D9*G9</f>
         <v>0</v>
       </c>
       <c r="L9" s="20" t="n">
+        <f aca="false">C9*H9*J9</f>
         <v>0</v>
       </c>
       <c r="M9" s="9" t="n">
+        <f aca="false">(K9+L9)*Labor!$C$3</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>117</v>
+        <v>74</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>71</v>
@@ -2164,14 +2992,14 @@
         <v>5</v>
       </c>
       <c r="D10" s="24" t="n">
-        <f aca="false">Assumptions!$D$8/3</f>
-        <v>34.6666666666667</v>
-      </c>
-      <c r="E10" s="25" t="n">
-        <f aca="false">Assumptions!$F$8</f>
+        <f aca="false">Assumptions!$D$12</f>
+        <v>34</v>
+      </c>
+      <c r="E10" s="24" t="n">
+        <f aca="false">Assumptions!$F$12</f>
         <v>30</v>
       </c>
-      <c r="F10" s="26" t="n">
+      <c r="F10" s="25" t="n">
         <f aca="false">IF(C10=0,0,E10/C10)</f>
         <v>6</v>
       </c>
@@ -2179,11 +3007,11 @@
         <v>2</v>
       </c>
       <c r="H10" s="24" t="n">
-        <f aca="false">Assumptions!$D$12/3</f>
-        <v>17.6666666666667</v>
-      </c>
-      <c r="I10" s="25" t="n">
-        <f aca="false">Assumptions!$F$12</f>
+        <f aca="false">Assumptions!$D$26</f>
+        <v>18</v>
+      </c>
+      <c r="I10" s="24" t="n">
+        <f aca="false">Assumptions!$F$26</f>
         <v>15</v>
       </c>
       <c r="J10" s="18" t="n">
@@ -2191,15 +3019,15 @@
       </c>
       <c r="K10" s="20" t="n">
         <f aca="false">C10*D10*G10</f>
-        <v>346.666666666667</v>
+        <v>340</v>
       </c>
       <c r="L10" s="20" t="n">
         <f aca="false">C10*H10*J10</f>
-        <v>88.3333333333333</v>
+        <v>90</v>
       </c>
       <c r="M10" s="9" t="n">
         <f aca="false">(K10+L10)*Labor!$C$3</f>
-        <v>6525</v>
+        <v>6450</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2211,14 +3039,14 @@
         <v>6</v>
       </c>
       <c r="D11" s="24" t="n">
-        <f aca="false">Assumptions!$D$9/3</f>
-        <v>34.6666666666667</v>
-      </c>
-      <c r="E11" s="25" t="n">
-        <f aca="false">Assumptions!$F$9</f>
+        <f aca="false">Assumptions!$D$13</f>
+        <v>34</v>
+      </c>
+      <c r="E11" s="24" t="n">
+        <f aca="false">Assumptions!$F$13</f>
         <v>60</v>
       </c>
-      <c r="F11" s="26" t="n">
+      <c r="F11" s="25" t="n">
         <f aca="false">IF(C11=0,0,E11/C11)</f>
         <v>10</v>
       </c>
@@ -2226,11 +3054,11 @@
         <v>3</v>
       </c>
       <c r="H11" s="24" t="n">
-        <f aca="false">Assumptions!$D$13/3</f>
-        <v>17.6666666666667</v>
-      </c>
-      <c r="I11" s="25" t="n">
-        <f aca="false">Assumptions!$F$13</f>
+        <f aca="false">Assumptions!$D$27</f>
+        <v>18</v>
+      </c>
+      <c r="I11" s="24" t="n">
+        <f aca="false">Assumptions!$F$27</f>
         <v>20</v>
       </c>
       <c r="J11" s="18" t="n">
@@ -2238,20 +3066,20 @@
       </c>
       <c r="K11" s="20" t="n">
         <f aca="false">C11*D11*G11</f>
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="L11" s="20" t="n">
         <f aca="false">C11*H11*J11</f>
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="M11" s="9" t="n">
         <f aca="false">(K11+L11)*Labor!$C$3</f>
-        <v>12540</v>
+        <v>12420</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>118</v>
+        <v>75</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>71</v>
@@ -2260,14 +3088,14 @@
         <v>5</v>
       </c>
       <c r="D12" s="24" t="n">
-        <f aca="false">Assumptions!$D$8/3</f>
-        <v>34.6666666666667</v>
-      </c>
-      <c r="E12" s="25" t="n">
-        <f aca="false">Assumptions!$F$8</f>
+        <f aca="false">Assumptions!$D$14</f>
+        <v>35</v>
+      </c>
+      <c r="E12" s="24" t="n">
+        <f aca="false">Assumptions!$F$14</f>
         <v>30</v>
       </c>
-      <c r="F12" s="26" t="n">
+      <c r="F12" s="25" t="n">
         <f aca="false">IF(C12=0,0,E12/C12)</f>
         <v>6</v>
       </c>
@@ -2275,11 +3103,11 @@
         <v>2</v>
       </c>
       <c r="H12" s="24" t="n">
-        <f aca="false">Assumptions!$D$12/3</f>
-        <v>17.6666666666667</v>
-      </c>
-      <c r="I12" s="25" t="n">
-        <f aca="false">Assumptions!$F$12</f>
+        <f aca="false">Assumptions!$D$28</f>
+        <v>17</v>
+      </c>
+      <c r="I12" s="24" t="n">
+        <f aca="false">Assumptions!$F$28</f>
         <v>15</v>
       </c>
       <c r="J12" s="18" t="n">
@@ -2287,11 +3115,11 @@
       </c>
       <c r="K12" s="20" t="n">
         <f aca="false">C12*D12*G12</f>
-        <v>346.666666666667</v>
+        <v>350</v>
       </c>
       <c r="L12" s="20" t="n">
         <f aca="false">C12*H12*J12</f>
-        <v>88.3333333333333</v>
+        <v>85</v>
       </c>
       <c r="M12" s="9" t="n">
         <f aca="false">(K12+L12)*Labor!$C$3</f>
@@ -2307,14 +3135,14 @@
         <v>6</v>
       </c>
       <c r="D13" s="24" t="n">
-        <f aca="false">Assumptions!$D$9/3</f>
-        <v>34.6666666666667</v>
-      </c>
-      <c r="E13" s="25" t="n">
-        <f aca="false">Assumptions!$F$9</f>
+        <f aca="false">Assumptions!$D$15</f>
+        <v>35</v>
+      </c>
+      <c r="E13" s="24" t="n">
+        <f aca="false">Assumptions!$F$15</f>
         <v>60</v>
       </c>
-      <c r="F13" s="26" t="n">
+      <c r="F13" s="25" t="n">
         <f aca="false">IF(C13=0,0,E13/C13)</f>
         <v>10</v>
       </c>
@@ -2322,11 +3150,11 @@
         <v>3</v>
       </c>
       <c r="H13" s="24" t="n">
-        <f aca="false">Assumptions!$D$13/3</f>
-        <v>17.6666666666667</v>
-      </c>
-      <c r="I13" s="25" t="n">
-        <f aca="false">Assumptions!$F$13</f>
+        <f aca="false">Assumptions!$D$29</f>
+        <v>17</v>
+      </c>
+      <c r="I13" s="24" t="n">
+        <f aca="false">Assumptions!$F$29</f>
         <v>20</v>
       </c>
       <c r="J13" s="18" t="n">
@@ -2334,20 +3162,20 @@
       </c>
       <c r="K13" s="20" t="n">
         <f aca="false">C13*D13*G13</f>
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="L13" s="20" t="n">
         <f aca="false">C13*H13*J13</f>
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="M13" s="9" t="n">
         <f aca="false">(K13+L13)*Labor!$C$3</f>
-        <v>12540</v>
+        <v>12510</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>119</v>
+        <v>76</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>71</v>
@@ -2356,14 +3184,14 @@
         <v>5</v>
       </c>
       <c r="D14" s="24" t="n">
-        <f aca="false">Assumptions!$D$8/3</f>
-        <v>34.6666666666667</v>
-      </c>
-      <c r="E14" s="25" t="n">
-        <f aca="false">Assumptions!$F$8</f>
+        <f aca="false">Assumptions!$D$16</f>
+        <v>35</v>
+      </c>
+      <c r="E14" s="24" t="n">
+        <f aca="false">Assumptions!$F$16</f>
         <v>30</v>
       </c>
-      <c r="F14" s="26" t="n">
+      <c r="F14" s="25" t="n">
         <f aca="false">IF(C14=0,0,E14/C14)</f>
         <v>6</v>
       </c>
@@ -2371,11 +3199,11 @@
         <v>2</v>
       </c>
       <c r="H14" s="24" t="n">
-        <f aca="false">Assumptions!$D$12/3</f>
-        <v>17.6666666666667</v>
-      </c>
-      <c r="I14" s="25" t="n">
-        <f aca="false">Assumptions!$F$12</f>
+        <f aca="false">Assumptions!$D$30</f>
+        <v>18</v>
+      </c>
+      <c r="I14" s="24" t="n">
+        <f aca="false">Assumptions!$F$30</f>
         <v>15</v>
       </c>
       <c r="J14" s="18" t="n">
@@ -2383,15 +3211,15 @@
       </c>
       <c r="K14" s="20" t="n">
         <f aca="false">C14*D14*G14</f>
-        <v>346.666666666667</v>
+        <v>350</v>
       </c>
       <c r="L14" s="20" t="n">
         <f aca="false">C14*H14*J14</f>
-        <v>88.3333333333333</v>
+        <v>90</v>
       </c>
       <c r="M14" s="9" t="n">
         <f aca="false">(K14+L14)*Labor!$C$3</f>
-        <v>6525</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2403,14 +3231,14 @@
         <v>6</v>
       </c>
       <c r="D15" s="24" t="n">
-        <f aca="false">Assumptions!$D$9/3</f>
-        <v>34.6666666666667</v>
-      </c>
-      <c r="E15" s="25" t="n">
-        <f aca="false">Assumptions!$F$9</f>
+        <f aca="false">Assumptions!$D$17</f>
+        <v>35</v>
+      </c>
+      <c r="E15" s="24" t="n">
+        <f aca="false">Assumptions!$F$17</f>
         <v>60</v>
       </c>
-      <c r="F15" s="26" t="n">
+      <c r="F15" s="25" t="n">
         <f aca="false">IF(C15=0,0,E15/C15)</f>
         <v>10</v>
       </c>
@@ -2418,11 +3246,11 @@
         <v>3</v>
       </c>
       <c r="H15" s="24" t="n">
-        <f aca="false">Assumptions!$D$13/3</f>
-        <v>17.6666666666667</v>
-      </c>
-      <c r="I15" s="25" t="n">
-        <f aca="false">Assumptions!$F$13</f>
+        <f aca="false">Assumptions!$D$31</f>
+        <v>18</v>
+      </c>
+      <c r="I15" s="24" t="n">
+        <f aca="false">Assumptions!$F$31</f>
         <v>20</v>
       </c>
       <c r="J15" s="18" t="n">
@@ -2430,20 +3258,20 @@
       </c>
       <c r="K15" s="20" t="n">
         <f aca="false">C15*D15*G15</f>
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="L15" s="20" t="n">
         <f aca="false">C15*H15*J15</f>
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="M15" s="9" t="n">
         <f aca="false">(K15+L15)*Labor!$C$3</f>
-        <v>12540</v>
+        <v>12690</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>120</v>
+        <v>77</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>71</v>
@@ -2452,14 +3280,14 @@
         <v>5</v>
       </c>
       <c r="D16" s="24" t="n">
-        <f aca="false">Assumptions!$D$10/2</f>
+        <f aca="false">Assumptions!$D$18</f>
         <v>35</v>
       </c>
-      <c r="E16" s="25" t="n">
-        <f aca="false">Assumptions!$F$10</f>
+      <c r="E16" s="24" t="n">
+        <f aca="false">Assumptions!$F$18</f>
         <v>80</v>
       </c>
-      <c r="F16" s="26" t="n">
+      <c r="F16" s="25" t="n">
         <f aca="false">IF(C16=0,0,E16/C16)</f>
         <v>16</v>
       </c>
@@ -2467,11 +3295,11 @@
         <v>3</v>
       </c>
       <c r="H16" s="24" t="n">
-        <f aca="false">Assumptions!$D$14/2</f>
+        <f aca="false">Assumptions!$D$32</f>
         <v>17</v>
       </c>
-      <c r="I16" s="25" t="n">
-        <f aca="false">Assumptions!$F$14</f>
+      <c r="I16" s="24" t="n">
+        <f aca="false">Assumptions!$F$32</f>
         <v>30</v>
       </c>
       <c r="J16" s="18" t="n">
@@ -2499,14 +3327,14 @@
         <v>6</v>
       </c>
       <c r="D17" s="24" t="n">
-        <f aca="false">Assumptions!$D$11/2</f>
+        <f aca="false">Assumptions!$D$19</f>
         <v>35</v>
       </c>
-      <c r="E17" s="25" t="n">
-        <f aca="false">Assumptions!$F$11</f>
+      <c r="E17" s="24" t="n">
+        <f aca="false">Assumptions!$F$19</f>
         <v>100</v>
       </c>
-      <c r="F17" s="26" t="n">
+      <c r="F17" s="25" t="n">
         <f aca="false">IF(C17=0,0,E17/C17)</f>
         <v>16.6666666666667</v>
       </c>
@@ -2514,11 +3342,11 @@
         <v>5</v>
       </c>
       <c r="H17" s="24" t="n">
-        <f aca="false">Assumptions!$D$15/2</f>
+        <f aca="false">Assumptions!$D$33</f>
         <v>17</v>
       </c>
-      <c r="I17" s="25" t="n">
-        <f aca="false">Assumptions!$F$15</f>
+      <c r="I17" s="24" t="n">
+        <f aca="false">Assumptions!$F$33</f>
         <v>60</v>
       </c>
       <c r="J17" s="18" t="n">
@@ -2539,7 +3367,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>71</v>
@@ -2548,14 +3376,14 @@
         <v>5</v>
       </c>
       <c r="D18" s="24" t="n">
-        <f aca="false">Assumptions!$D$10/2</f>
+        <f aca="false">Assumptions!$D$20</f>
         <v>35</v>
       </c>
-      <c r="E18" s="25" t="n">
-        <f aca="false">Assumptions!$F$10</f>
+      <c r="E18" s="24" t="n">
+        <f aca="false">Assumptions!$F$20</f>
         <v>80</v>
       </c>
-      <c r="F18" s="26" t="n">
+      <c r="F18" s="25" t="n">
         <f aca="false">IF(C18=0,0,E18/C18)</f>
         <v>16</v>
       </c>
@@ -2563,11 +3391,11 @@
         <v>3</v>
       </c>
       <c r="H18" s="24" t="n">
-        <f aca="false">Assumptions!$D$14/2</f>
+        <f aca="false">Assumptions!$D$34</f>
         <v>17</v>
       </c>
-      <c r="I18" s="25" t="n">
-        <f aca="false">Assumptions!$F$14</f>
+      <c r="I18" s="24" t="n">
+        <f aca="false">Assumptions!$F$34</f>
         <v>30</v>
       </c>
       <c r="J18" s="18" t="n">
@@ -2595,14 +3423,14 @@
         <v>6</v>
       </c>
       <c r="D19" s="24" t="n">
-        <f aca="false">Assumptions!$D$11/2</f>
+        <f aca="false">Assumptions!$D$21</f>
         <v>35</v>
       </c>
-      <c r="E19" s="25" t="n">
-        <f aca="false">Assumptions!$F$11</f>
+      <c r="E19" s="24" t="n">
+        <f aca="false">Assumptions!$F$21</f>
         <v>100</v>
       </c>
-      <c r="F19" s="26" t="n">
+      <c r="F19" s="25" t="n">
         <f aca="false">IF(C19=0,0,E19/C19)</f>
         <v>16.6666666666667</v>
       </c>
@@ -2610,11 +3438,11 @@
         <v>5</v>
       </c>
       <c r="H19" s="24" t="n">
-        <f aca="false">Assumptions!$D$15/2</f>
+        <f aca="false">Assumptions!$D$35</f>
         <v>17</v>
       </c>
-      <c r="I19" s="25" t="n">
-        <f aca="false">Assumptions!$F$15</f>
+      <c r="I19" s="24" t="n">
+        <f aca="false">Assumptions!$F$35</f>
         <v>60</v>
       </c>
       <c r="J19" s="18" t="n">
@@ -2635,7 +3463,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="K20" s="21" t="n">
         <f aca="false">SUM(K6:K19)</f>
@@ -2652,7 +3480,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -2666,15 +3494,15 @@
       <c r="K23" s="5"/>
       <c r="L23" s="5"/>
       <c r="M23" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="M24" s="17" t="n">
         <v>70000</v>
@@ -2682,10 +3510,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="M25" s="17" t="n">
         <v>50000</v>
@@ -2693,7 +3521,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="M26" s="17" t="n">
         <v>7000</v>
@@ -2701,16 +3529,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="M27" s="9" t="n">
-        <f aca="false">SUM(M24:M26)*Assumptions!$B$28</f>
+        <f aca="false">SUM(M24:M26)*Assumptions!$B$49</f>
         <v>27940</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="M28" s="13" t="n">
         <f aca="false">SUM(M24:M27)</f>
@@ -2719,7 +3547,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="M29" s="9" t="n">
         <f aca="false">M20</f>
@@ -2728,25 +3556,25 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="M30" s="9" t="n">
-        <f aca="false">M29*Assumptions!$B$27</f>
+        <f aca="false">M29*Assumptions!$B$48</f>
         <v>11872.5</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="M31" s="13" t="n">
-        <f aca="false">M29*(1+Assumptions!$B$27)</f>
+        <f aca="false">M29*(1+Assumptions!$B$48)</f>
         <v>130597.5</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="M32" s="13" t="n">
         <f aca="false">Labor!$M$28+Labor!$M$31</f>
@@ -2781,20 +3609,20 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>18</v>
@@ -2803,15 +3631,15 @@
         <v>19</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C4" s="8" t="n">
         <v>1800000</v>
@@ -2820,15 +3648,15 @@
         <v>1800000</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C5" s="8" t="n">
         <v>36000</v>
@@ -2837,15 +3665,15 @@
         <v>36000</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C6" s="8" t="n">
         <v>8000</v>
@@ -2854,15 +3682,15 @@
         <v>8000</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C7" s="8" t="n">
         <v>25000</v>
@@ -2871,32 +3699,32 @@
         <v>25000</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="D8" s="17" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C9" s="8" t="n">
         <v>100000</v>
@@ -2905,15 +3733,15 @@
         <v>100000</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>100000</v>
@@ -2922,15 +3750,15 @@
         <v>100000</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C11" s="8" t="n">
         <v>75000</v>
@@ -2939,15 +3767,15 @@
         <v>75000</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C12" s="8" t="n">
         <v>175000</v>
@@ -2956,15 +3784,15 @@
         <v>175000</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C13" s="8" t="n">
         <v>35000</v>
@@ -2973,32 +3801,32 @@
         <v>35000</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>160</v>
-      </c>
       <c r="C14" s="8" t="n">
-        <v>30000</v>
+        <v>15000</v>
       </c>
       <c r="D14" s="17" t="n">
-        <v>30000</v>
+        <v>15000</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C15" s="8" t="n">
         <v>75000</v>
@@ -3007,15 +3835,15 @@
         <v>75000</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C16" s="8" t="n">
         <v>20000</v>
@@ -3024,49 +3852,49 @@
         <v>20000</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C17" s="8" t="n">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="D17" s="17" t="n">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C18" s="8" t="n">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="D18" s="17" t="n">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C19" s="8" t="n">
         <v>25000</v>
@@ -3075,12 +3903,12 @@
         <v>25000</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C20" s="13" t="n">
         <f aca="false">SUMIFS(C4:C19,$A$4:$A$19,"Acquisition")</f>
@@ -3093,41 +3921,41 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="2" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C21" s="6" t="n">
         <f aca="false">SUM(C4:C19)-C20</f>
-        <v>900000</v>
+        <v>815000</v>
       </c>
       <c r="D21" s="6" t="n">
         <f aca="false">SUM(D4:D19)-D20</f>
-        <v>900000</v>
+        <v>815000</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C22" s="9" t="n">
-        <f aca="false">C21*Assumptions!$B$26</f>
-        <v>90000</v>
+        <f aca="false">C21*Assumptions!$B$47</f>
+        <v>81500</v>
       </c>
       <c r="D22" s="9" t="n">
-        <f aca="false">D21*Assumptions!$B$26</f>
-        <v>90000</v>
+        <f aca="false">D21*Assumptions!$B$47</f>
+        <v>81500</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="2" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C23" s="13" t="n">
         <f aca="false">C20+C21+C22</f>
-        <v>2834000</v>
+        <v>2740500</v>
       </c>
       <c r="D23" s="13" t="n">
         <f aca="false">D20+D21+D22</f>
-        <v>2834000</v>
+        <v>2740500</v>
       </c>
     </row>
   </sheetData>

--- a/806-Ramseur-PnL.xlsx
+++ b/806-Ramseur-PnL.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="167">
   <si>
     <t xml:space="preserve">806 E Ramseur Mini Golf + Bar — P&amp;L model</t>
   </si>
@@ -89,6 +89,27 @@
     <t xml:space="preserve">Source / note</t>
   </si>
   <si>
+    <t xml:space="preserve">Property cost and financing (separate calculation)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Property cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Amount financed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Interest rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Equity contribution (property cost - amount financed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Property service cost (financed x rate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interest only, no principal</t>
+  </si>
+  <si>
     <t xml:space="preserve">Revenue</t>
   </si>
   <si>
@@ -110,22 +131,10 @@
     <t xml:space="preserve">Expenses</t>
   </si>
   <si>
-    <t xml:space="preserve">Property cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Property cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Amount financed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Interest rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Property service cost (financed x rate)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interest only, no principal</t>
+    <t xml:space="preserve">  Property service cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From property calculation above</t>
   </si>
   <si>
     <t xml:space="preserve">  Property tax</t>
@@ -167,13 +176,13 @@
     <t xml:space="preserve">Simple ROI</t>
   </si>
   <si>
-    <t xml:space="preserve">Equity contribution (property cost - amount financed)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Initial capex excl. purchase price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capex sheet total less its purchase price line</t>
+    <t xml:space="preserve">Equity contribution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Initial capex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capex sheet total</t>
   </si>
   <si>
     <t xml:space="preserve">Total invested</t>
@@ -419,7 +428,7 @@
     <t xml:space="preserve">Annual total labor</t>
   </si>
   <si>
-    <t xml:space="preserve">Initial capex</t>
+    <t xml:space="preserve">Initial capex (excludes the property purchase; see P&amp;L)</t>
   </si>
   <si>
     <t xml:space="preserve">Enter your amount in column C. Column D keeps the default estimate for reference.</t>
@@ -434,33 +443,15 @@
     <t xml:space="preserve">Basis</t>
   </si>
   <si>
-    <t xml:space="preserve">Acquisition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Purchase price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owner target; broker asking $2.2M ($176/SF)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Closing costs (~2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legal, title, recording, lender fees</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Due diligence: Phase I ESA, survey, inspection, zoning letter</t>
+    <t xml:space="preserve">Soft costs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Architecture, engineering, permit fees</t>
   </si>
   <si>
     <t xml:space="preserve">Owner estimate</t>
   </si>
   <si>
-    <t xml:space="preserve">Soft costs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Architecture, engineering, permit fees</t>
-  </si>
-  <si>
     <t xml:space="preserve">Building</t>
   </si>
   <si>
@@ -527,16 +518,13 @@
     <t xml:space="preserve">Pre-opening: hiring, training, launch marketing, ABC permits</t>
   </si>
   <si>
-    <t xml:space="preserve">Subtotal: acquisition</t>
-  </si>
-  <si>
     <t xml:space="preserve">Subtotal: build-out and opening</t>
   </si>
   <si>
     <t xml:space="preserve">Contingency (% on Assumptions)</t>
   </si>
   <si>
-    <t xml:space="preserve">Total project cost</t>
+    <t xml:space="preserve">Total initial capex</t>
   </si>
 </sst>
 </file>
@@ -546,8 +534,8 @@
   <numFmts count="7">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
-    <numFmt numFmtId="166" formatCode="0.0%;\(0.0%\);\-"/>
-    <numFmt numFmtId="167" formatCode="0.00%"/>
+    <numFmt numFmtId="166" formatCode="0.00%"/>
+    <numFmt numFmtId="167" formatCode="0.0%;\(0.0%\);\-"/>
     <numFmt numFmtId="168" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
     <numFmt numFmtId="169" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="170" formatCode="0.0"/>
@@ -704,14 +692,6 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -720,7 +700,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -736,7 +724,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -768,11 +756,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1142,7 +1130,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
@@ -1180,257 +1168,278 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B6" s="6" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>1800000</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>1260000</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>1260000</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>0.0725</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>0.0725</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="7" t="n">
+        <f aca="false">$B$6-$B$7</f>
+        <v>540000</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="10" t="n">
+        <f aca="false">$B$7*$B$8</f>
+        <v>91350</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>91350</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="10" t="n">
         <f aca="false">SUM(Assumptions!$J$8:$J$35)*Assumptions!$B$3+SUMPRODUCT(Assumptions!$J$8:$J$35,Assumptions!$G$8:$G$35)+SUMPRODUCT(Assumptions!$J$8:$J$35,Assumptions!$H$8:$H$35)+SUMPRODUCT(Assumptions!$J$8:$J$35,Assumptions!$I$8:$I$35)+Assumptions!$B$4*Assumptions!$B$5</f>
         <v>766350</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="6" t="n">
+      <c r="D13" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="10" t="n">
         <f aca="false">SUM(Assumptions!$J$8:$J$35)*Assumptions!$B$3*Assumptions!$B$40+SUMPRODUCT(Assumptions!$J$8:$J$35,Assumptions!$G$8:$G$35)*Assumptions!$B$41+SUMPRODUCT(Assumptions!$J$8:$J$35,Assumptions!$H$8:$H$35)*Assumptions!$B$42+SUMPRODUCT(Assumptions!$J$8:$J$35,Assumptions!$I$8:$I$35)*Assumptions!$B$43+Assumptions!$B$4*Assumptions!$B$5*Assumptions!$B$44</f>
         <v>522416.5</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="7" t="n">
-        <f aca="false">IF($B$6=0,0,$B$7/$B$6)</f>
-        <v>0.681694395511189</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="8" t="n">
-        <v>1800000</v>
-      </c>
-      <c r="C12" s="9" t="n">
-        <v>1800000</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" s="8" t="n">
-        <v>1260000</v>
-      </c>
-      <c r="C13" s="9" t="n">
-        <v>1260000</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="10" t="n">
-        <v>0.0725</v>
-      </c>
-      <c r="C14" s="11" t="n">
-        <v>0.0725</v>
+      <c r="D14" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="9" t="n">
-        <f aca="false">$B$13*$B$14</f>
-        <v>91350</v>
-      </c>
-      <c r="C15" s="9" t="n">
-        <v>91350</v>
-      </c>
-      <c r="D15" s="3" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="s">
+      <c r="B15" s="11" t="n">
+        <f aca="false">IF($B$13=0,0,$B$14/$B$13)</f>
+        <v>0.681694395511189</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="B16" s="8" t="n">
-        <v>18293</v>
-      </c>
-      <c r="C16" s="9" t="n">
-        <v>18293</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17" s="8" t="n">
-        <v>40000</v>
-      </c>
-      <c r="C17" s="9" t="n">
-        <v>40000</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="8" t="n">
-        <v>36000</v>
-      </c>
-      <c r="C18" s="9" t="n">
-        <v>36000</v>
+        <v>35</v>
+      </c>
+      <c r="B18" s="7" t="n">
+        <f aca="false">$B$10</f>
+        <v>91350</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>18293</v>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>18293</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="B19" s="12" t="n">
-        <f aca="false">Labor!$M$32</f>
-        <v>285537.5</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20" s="8" t="n">
-        <v>15000</v>
-      </c>
-      <c r="C20" s="9" t="n">
-        <v>15000</v>
+        <v>39</v>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>40000</v>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>40000</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21" s="8" t="n">
-        <v>30000</v>
-      </c>
-      <c r="C21" s="9" t="n">
-        <v>30000</v>
+        <v>40</v>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>36000</v>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>36000</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="12" t="n">
+        <f aca="false">Labor!$M$32</f>
+        <v>256646</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="B22" s="8" t="n">
-        <v>15000</v>
-      </c>
-      <c r="C22" s="9" t="n">
-        <v>15000</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B23" s="8" t="n">
+      <c r="B23" s="6" t="n">
         <v>15000</v>
       </c>
-      <c r="C23" s="9" t="n">
+      <c r="C23" s="7" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="13" t="n">
-        <f aca="false">SUM(B15:B23)</f>
-        <v>546180.5</v>
+      <c r="B24" s="6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>30000</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B25" s="13" t="n">
-        <f aca="false">$B$7-$B$24</f>
-        <v>-23764</v>
+      <c r="B25" s="6" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>15000</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="B27" s="13" t="n">
+        <f aca="false">SUM(B18:B26)</f>
+        <v>517289</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B28" s="9" t="n">
-        <f aca="false">$B$25</f>
-        <v>-23764</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B29" s="9" t="n">
-        <f aca="false">$B$12-$B$13</f>
+      <c r="A28" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" s="13" t="n">
+        <f aca="false">$B$14-$B$27</f>
+        <v>5127.5</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B31" s="7" t="n">
+        <f aca="false">$B$28</f>
+        <v>5127.5</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B32" s="7" t="n">
+        <f aca="false">$B$9</f>
         <v>540000</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B30" s="12" t="n">
-        <f aca="false">Capex!$C$23-Capex!$C$4</f>
-        <v>940500</v>
-      </c>
-      <c r="D30" s="3" t="s">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B33" s="12" t="n">
+        <f aca="false">Capex!$C$19</f>
+        <v>896500</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B34" s="13" t="n">
+        <f aca="false">$B$9+$B$33</f>
+        <v>1436500</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="2" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B31" s="13" t="n">
-        <f aca="false">$B$29+$B$30</f>
-        <v>1480500</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B32" s="14" t="n">
-        <f aca="false">IF($B$31=0,0,$B$25/$B$31)</f>
-        <v>-0.0160513340087808</v>
+      <c r="B35" s="14" t="n">
+        <f aca="false">IF($B$34=0,0,$B$28/$B$34)</f>
+        <v>0.00356943961016359</v>
       </c>
     </row>
   </sheetData>
@@ -1464,86 +1473,86 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B3" s="15" t="n">
         <v>12</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B4" s="16" t="n">
         <v>20</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B5" s="17" t="n">
         <v>500</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D8" s="16" t="n">
         <v>35</v>
@@ -1567,20 +1576,20 @@
         <f aca="false">D8*F8</f>
         <v>0</v>
       </c>
-      <c r="K8" s="9" t="n">
+      <c r="K8" s="7" t="n">
         <f aca="false">J8*(Assumptions!$B$3+G8+H8+I8)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D9" s="16" t="n">
         <v>35</v>
@@ -1604,20 +1613,20 @@
         <f aca="false">D9*F9</f>
         <v>0</v>
       </c>
-      <c r="K9" s="9" t="n">
+      <c r="K9" s="7" t="n">
         <f aca="false">J9*(Assumptions!$B$3+G9+H9+I9)</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D10" s="16" t="n">
         <v>35</v>
@@ -1641,20 +1650,20 @@
         <f aca="false">D10*F10</f>
         <v>0</v>
       </c>
-      <c r="K10" s="9" t="n">
+      <c r="K10" s="7" t="n">
         <f aca="false">J10*(Assumptions!$B$3+G10+H10+I10)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D11" s="16" t="n">
         <v>35</v>
@@ -1678,20 +1687,20 @@
         <f aca="false">D11*F11</f>
         <v>0</v>
       </c>
-      <c r="K11" s="9" t="n">
+      <c r="K11" s="7" t="n">
         <f aca="false">J11*(Assumptions!$B$3+G11+H11+I11)</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>71</v>
       </c>
       <c r="D12" s="16" t="n">
         <v>34</v>
@@ -1715,20 +1724,20 @@
         <f aca="false">D12*F12</f>
         <v>1020</v>
       </c>
-      <c r="K12" s="9" t="n">
+      <c r="K12" s="7" t="n">
         <f aca="false">J12*(Assumptions!$B$3+G12+H12+I12)</f>
         <v>22440</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D13" s="16" t="n">
         <v>34</v>
@@ -1752,20 +1761,20 @@
         <f aca="false">D13*F13</f>
         <v>2040</v>
       </c>
-      <c r="K13" s="9" t="n">
+      <c r="K13" s="7" t="n">
         <f aca="false">J13*(Assumptions!$B$3+G13+H13+I13)</f>
         <v>53040</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D14" s="16" t="n">
         <v>35</v>
@@ -1789,20 +1798,20 @@
         <f aca="false">D14*F14</f>
         <v>1050</v>
       </c>
-      <c r="K14" s="9" t="n">
+      <c r="K14" s="7" t="n">
         <f aca="false">J14*(Assumptions!$B$3+G14+H14+I14)</f>
         <v>23100</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="D15" s="16" t="n">
         <v>35</v>
@@ -1826,20 +1835,20 @@
         <f aca="false">D15*F15</f>
         <v>2100</v>
       </c>
-      <c r="K15" s="9" t="n">
+      <c r="K15" s="7" t="n">
         <f aca="false">J15*(Assumptions!$B$3+G15+H15+I15)</f>
         <v>54600</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D16" s="16" t="n">
         <v>35</v>
@@ -1863,20 +1872,20 @@
         <f aca="false">D16*F16</f>
         <v>1050</v>
       </c>
-      <c r="K16" s="9" t="n">
+      <c r="K16" s="7" t="n">
         <f aca="false">J16*(Assumptions!$B$3+G16+H16+I16)</f>
         <v>23100</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D17" s="16" t="n">
         <v>35</v>
@@ -1900,20 +1909,20 @@
         <f aca="false">D17*F17</f>
         <v>2100</v>
       </c>
-      <c r="K17" s="9" t="n">
+      <c r="K17" s="7" t="n">
         <f aca="false">J17*(Assumptions!$B$3+G17+H17+I17)</f>
         <v>54600</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D18" s="16" t="n">
         <v>35</v>
@@ -1937,20 +1946,20 @@
         <f aca="false">D18*F18</f>
         <v>2800</v>
       </c>
-      <c r="K18" s="9" t="n">
+      <c r="K18" s="7" t="n">
         <f aca="false">J18*(Assumptions!$B$3+G18+H18+I18)</f>
         <v>75600</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D19" s="16" t="n">
         <v>35</v>
@@ -1974,20 +1983,20 @@
         <f aca="false">D19*F19</f>
         <v>3500</v>
       </c>
-      <c r="K19" s="9" t="n">
+      <c r="K19" s="7" t="n">
         <f aca="false">J19*(Assumptions!$B$3+G19+H19+I19)</f>
         <v>129500</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D20" s="16" t="n">
         <v>35</v>
@@ -2011,20 +2020,20 @@
         <f aca="false">D20*F20</f>
         <v>2800</v>
       </c>
-      <c r="K20" s="9" t="n">
+      <c r="K20" s="7" t="n">
         <f aca="false">J20*(Assumptions!$B$3+G20+H20+I20)</f>
         <v>75600</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D21" s="16" t="n">
         <v>35</v>
@@ -2048,20 +2057,20 @@
         <f aca="false">D21*F21</f>
         <v>3500</v>
       </c>
-      <c r="K21" s="9" t="n">
+      <c r="K21" s="7" t="n">
         <f aca="false">J21*(Assumptions!$B$3+G21+H21+I21)</f>
         <v>129500</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D22" s="16" t="n">
         <v>17</v>
@@ -2085,20 +2094,20 @@
         <f aca="false">D22*F22</f>
         <v>0</v>
       </c>
-      <c r="K22" s="9" t="n">
+      <c r="K22" s="7" t="n">
         <f aca="false">J22*(Assumptions!$B$3+G22+H22+I22)</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D23" s="16" t="n">
         <v>17</v>
@@ -2122,20 +2131,20 @@
         <f aca="false">D23*F23</f>
         <v>0</v>
       </c>
-      <c r="K23" s="9" t="n">
+      <c r="K23" s="7" t="n">
         <f aca="false">J23*(Assumptions!$B$3+G23+H23+I23)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D24" s="16" t="n">
         <v>17</v>
@@ -2159,20 +2168,20 @@
         <f aca="false">D24*F24</f>
         <v>0</v>
       </c>
-      <c r="K24" s="9" t="n">
+      <c r="K24" s="7" t="n">
         <f aca="false">J24*(Assumptions!$B$3+G24+H24+I24)</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D25" s="16" t="n">
         <v>17</v>
@@ -2196,20 +2205,20 @@
         <f aca="false">D25*F25</f>
         <v>0</v>
       </c>
-      <c r="K25" s="9" t="n">
+      <c r="K25" s="7" t="n">
         <f aca="false">J25*(Assumptions!$B$3+G25+H25+I25)</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>71</v>
       </c>
       <c r="D26" s="16" t="n">
         <v>18</v>
@@ -2233,20 +2242,20 @@
         <f aca="false">D26*F26</f>
         <v>270</v>
       </c>
-      <c r="K26" s="9" t="n">
+      <c r="K26" s="7" t="n">
         <f aca="false">J26*(Assumptions!$B$3+G26+H26+I26)</f>
         <v>4860</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D27" s="16" t="n">
         <v>18</v>
@@ -2270,20 +2279,20 @@
         <f aca="false">D27*F27</f>
         <v>360</v>
       </c>
-      <c r="K27" s="9" t="n">
+      <c r="K27" s="7" t="n">
         <f aca="false">J27*(Assumptions!$B$3+G27+H27+I27)</f>
         <v>9000</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D28" s="16" t="n">
         <v>17</v>
@@ -2307,20 +2316,20 @@
         <f aca="false">D28*F28</f>
         <v>255</v>
       </c>
-      <c r="K28" s="9" t="n">
+      <c r="K28" s="7" t="n">
         <f aca="false">J28*(Assumptions!$B$3+G28+H28+I28)</f>
         <v>4590</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="D29" s="16" t="n">
         <v>17</v>
@@ -2344,20 +2353,20 @@
         <f aca="false">D29*F29</f>
         <v>340</v>
       </c>
-      <c r="K29" s="9" t="n">
+      <c r="K29" s="7" t="n">
         <f aca="false">J29*(Assumptions!$B$3+G29+H29+I29)</f>
         <v>8500</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="C30" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D30" s="16" t="n">
         <v>18</v>
@@ -2381,20 +2390,20 @@
         <f aca="false">D30*F30</f>
         <v>270</v>
       </c>
-      <c r="K30" s="9" t="n">
+      <c r="K30" s="7" t="n">
         <f aca="false">J30*(Assumptions!$B$3+G30+H30+I30)</f>
         <v>4860</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="C31" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D31" s="16" t="n">
         <v>18</v>
@@ -2418,20 +2427,20 @@
         <f aca="false">D31*F31</f>
         <v>360</v>
       </c>
-      <c r="K31" s="9" t="n">
+      <c r="K31" s="7" t="n">
         <f aca="false">J31*(Assumptions!$B$3+G31+H31+I31)</f>
         <v>9000</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D32" s="16" t="n">
         <v>17</v>
@@ -2455,20 +2464,20 @@
         <f aca="false">D32*F32</f>
         <v>510</v>
       </c>
-      <c r="K32" s="9" t="n">
+      <c r="K32" s="7" t="n">
         <f aca="false">J32*(Assumptions!$B$3+G32+H32+I32)</f>
         <v>11730</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D33" s="16" t="n">
         <v>17</v>
@@ -2492,20 +2501,20 @@
         <f aca="false">D33*F33</f>
         <v>1020</v>
       </c>
-      <c r="K33" s="9" t="n">
+      <c r="K33" s="7" t="n">
         <f aca="false">J33*(Assumptions!$B$3+G33+H33+I33)</f>
         <v>25500</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D34" s="16" t="n">
         <v>17</v>
@@ -2529,20 +2538,20 @@
         <f aca="false">D34*F34</f>
         <v>510</v>
       </c>
-      <c r="K34" s="9" t="n">
+      <c r="K34" s="7" t="n">
         <f aca="false">J34*(Assumptions!$B$3+G34+H34+I34)</f>
         <v>11730</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D35" s="16" t="n">
         <v>17</v>
@@ -2566,14 +2575,14 @@
         <f aca="false">D35*F35</f>
         <v>1020</v>
       </c>
-      <c r="K35" s="9" t="n">
+      <c r="K35" s="7" t="n">
         <f aca="false">J35*(Assumptions!$B$3+G35+H35+I35)</f>
         <v>25500</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="J36" s="21" t="n">
         <f aca="false">SUM(J8:J35)</f>
@@ -2586,117 +2595,117 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B40" s="22" t="n">
         <v>0.95</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B41" s="22" t="n">
         <v>0.15</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B42" s="22" t="n">
         <v>0.7</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B43" s="22" t="n">
         <v>0.76</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B44" s="22" t="n">
         <v>0.75</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B47" s="23" t="n">
         <v>0.1</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B48" s="23" t="n">
         <v>0.1</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B49" s="23" t="n">
         <v>0.22</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -2732,17 +2741,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C3" s="15" t="n">
         <v>15</v>
@@ -2750,51 +2759,51 @@
     </row>
     <row r="5" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C6" s="20" t="n">
         <v>5</v>
@@ -2833,7 +2842,7 @@
         <f aca="false">C6*H6*J6</f>
         <v>0</v>
       </c>
-      <c r="M6" s="9" t="n">
+      <c r="M6" s="7" t="n">
         <f aca="false">(K6+L6)*Labor!$C$3</f>
         <v>0</v>
       </c>
@@ -2841,7 +2850,7 @@
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C7" s="20" t="n">
         <v>6</v>
@@ -2880,17 +2889,17 @@
         <f aca="false">C7*H7*J7</f>
         <v>0</v>
       </c>
-      <c r="M7" s="9" t="n">
+      <c r="M7" s="7" t="n">
         <f aca="false">(K7+L7)*Labor!$C$3</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C8" s="20" t="n">
         <v>5</v>
@@ -2929,7 +2938,7 @@
         <f aca="false">C8*H8*J8</f>
         <v>0</v>
       </c>
-      <c r="M8" s="9" t="n">
+      <c r="M8" s="7" t="n">
         <f aca="false">(K8+L8)*Labor!$C$3</f>
         <v>0</v>
       </c>
@@ -2937,7 +2946,7 @@
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C9" s="20" t="n">
         <v>6</v>
@@ -2976,17 +2985,17 @@
         <f aca="false">C9*H9*J9</f>
         <v>0</v>
       </c>
-      <c r="M9" s="9" t="n">
+      <c r="M9" s="7" t="n">
         <f aca="false">(K9+L9)*Labor!$C$3</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>71</v>
       </c>
       <c r="C10" s="20" t="n">
         <v>5</v>
@@ -3004,7 +3013,7 @@
         <v>6</v>
       </c>
       <c r="G10" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10" s="24" t="n">
         <f aca="false">Assumptions!$D$26</f>
@@ -3019,21 +3028,21 @@
       </c>
       <c r="K10" s="20" t="n">
         <f aca="false">C10*D10*G10</f>
-        <v>340</v>
+        <v>170</v>
       </c>
       <c r="L10" s="20" t="n">
         <f aca="false">C10*H10*J10</f>
         <v>90</v>
       </c>
-      <c r="M10" s="9" t="n">
+      <c r="M10" s="7" t="n">
         <f aca="false">(K10+L10)*Labor!$C$3</f>
-        <v>6450</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C11" s="20" t="n">
         <v>6</v>
@@ -3051,7 +3060,7 @@
         <v>10</v>
       </c>
       <c r="G11" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H11" s="24" t="n">
         <f aca="false">Assumptions!$D$27</f>
@@ -3062,27 +3071,27 @@
         <v>20</v>
       </c>
       <c r="J11" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K11" s="20" t="n">
         <f aca="false">C11*D11*G11</f>
-        <v>612</v>
+        <v>408</v>
       </c>
       <c r="L11" s="20" t="n">
         <f aca="false">C11*H11*J11</f>
-        <v>216</v>
-      </c>
-      <c r="M11" s="9" t="n">
+        <v>108</v>
+      </c>
+      <c r="M11" s="7" t="n">
         <f aca="false">(K11+L11)*Labor!$C$3</f>
-        <v>12420</v>
+        <v>7740</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C12" s="20" t="n">
         <v>5</v>
@@ -3100,7 +3109,7 @@
         <v>6</v>
       </c>
       <c r="G12" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12" s="24" t="n">
         <f aca="false">Assumptions!$D$28</f>
@@ -3115,21 +3124,21 @@
       </c>
       <c r="K12" s="20" t="n">
         <f aca="false">C12*D12*G12</f>
-        <v>350</v>
+        <v>175</v>
       </c>
       <c r="L12" s="20" t="n">
         <f aca="false">C12*H12*J12</f>
         <v>85</v>
       </c>
-      <c r="M12" s="9" t="n">
+      <c r="M12" s="7" t="n">
         <f aca="false">(K12+L12)*Labor!$C$3</f>
-        <v>6525</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C13" s="20" t="n">
         <v>6</v>
@@ -3147,7 +3156,7 @@
         <v>10</v>
       </c>
       <c r="G13" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H13" s="24" t="n">
         <f aca="false">Assumptions!$D$29</f>
@@ -3158,27 +3167,27 @@
         <v>20</v>
       </c>
       <c r="J13" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K13" s="20" t="n">
         <f aca="false">C13*D13*G13</f>
-        <v>630</v>
+        <v>420</v>
       </c>
       <c r="L13" s="20" t="n">
         <f aca="false">C13*H13*J13</f>
-        <v>204</v>
-      </c>
-      <c r="M13" s="9" t="n">
+        <v>102</v>
+      </c>
+      <c r="M13" s="7" t="n">
         <f aca="false">(K13+L13)*Labor!$C$3</f>
-        <v>12510</v>
+        <v>7830</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C14" s="20" t="n">
         <v>5</v>
@@ -3217,7 +3226,7 @@
         <f aca="false">C14*H14*J14</f>
         <v>90</v>
       </c>
-      <c r="M14" s="9" t="n">
+      <c r="M14" s="7" t="n">
         <f aca="false">(K14+L14)*Labor!$C$3</f>
         <v>6600</v>
       </c>
@@ -3225,7 +3234,7 @@
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C15" s="20" t="n">
         <v>6</v>
@@ -3264,17 +3273,17 @@
         <f aca="false">C15*H15*J15</f>
         <v>216</v>
       </c>
-      <c r="M15" s="9" t="n">
+      <c r="M15" s="7" t="n">
         <f aca="false">(K15+L15)*Labor!$C$3</f>
         <v>12690</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C16" s="20" t="n">
         <v>5</v>
@@ -3313,7 +3322,7 @@
         <f aca="false">C16*H16*J16</f>
         <v>170</v>
       </c>
-      <c r="M16" s="9" t="n">
+      <c r="M16" s="7" t="n">
         <f aca="false">(K16+L16)*Labor!$C$3</f>
         <v>10425</v>
       </c>
@@ -3321,7 +3330,7 @@
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C17" s="20" t="n">
         <v>6</v>
@@ -3339,7 +3348,7 @@
         <v>16.6666666666667</v>
       </c>
       <c r="G17" s="18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H17" s="24" t="n">
         <f aca="false">Assumptions!$D$33</f>
@@ -3350,27 +3359,27 @@
         <v>60</v>
       </c>
       <c r="J17" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K17" s="20" t="n">
         <f aca="false">C17*D17*G17</f>
-        <v>1050</v>
+        <v>840</v>
       </c>
       <c r="L17" s="20" t="n">
         <f aca="false">C17*H17*J17</f>
-        <v>306</v>
-      </c>
-      <c r="M17" s="9" t="n">
+        <v>204</v>
+      </c>
+      <c r="M17" s="7" t="n">
         <f aca="false">(K17+L17)*Labor!$C$3</f>
-        <v>20340</v>
+        <v>15660</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C18" s="20" t="n">
         <v>5</v>
@@ -3388,7 +3397,7 @@
         <v>16</v>
       </c>
       <c r="G18" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H18" s="24" t="n">
         <f aca="false">Assumptions!$D$34</f>
@@ -3399,25 +3408,25 @@
         <v>30</v>
       </c>
       <c r="J18" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K18" s="20" t="n">
         <f aca="false">C18*D18*G18</f>
-        <v>525</v>
+        <v>350</v>
       </c>
       <c r="L18" s="20" t="n">
         <f aca="false">C18*H18*J18</f>
-        <v>170</v>
-      </c>
-      <c r="M18" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="M18" s="7" t="n">
         <f aca="false">(K18+L18)*Labor!$C$3</f>
-        <v>10425</v>
+        <v>6525</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C19" s="20" t="n">
         <v>6</v>
@@ -3435,7 +3444,7 @@
         <v>16.6666666666667</v>
       </c>
       <c r="G19" s="18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H19" s="24" t="n">
         <f aca="false">Assumptions!$D$35</f>
@@ -3450,37 +3459,37 @@
       </c>
       <c r="K19" s="20" t="n">
         <f aca="false">C19*D19*G19</f>
-        <v>1050</v>
+        <v>840</v>
       </c>
       <c r="L19" s="20" t="n">
         <f aca="false">C19*H19*J19</f>
         <v>306</v>
       </c>
-      <c r="M19" s="9" t="n">
+      <c r="M19" s="7" t="n">
         <f aca="false">(K19+L19)*Labor!$C$3</f>
-        <v>20340</v>
+        <v>17190</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K20" s="21" t="n">
         <f aca="false">SUM(K6:K19)</f>
-        <v>6062</v>
+        <v>4708</v>
       </c>
       <c r="L20" s="21" t="n">
         <f aca="false">SUM(L6:L19)</f>
-        <v>1853</v>
+        <v>1456</v>
       </c>
       <c r="M20" s="13" t="n">
         <f aca="false">SUM(M6:M19)</f>
-        <v>118725</v>
+        <v>92460</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -3494,15 +3503,15 @@
       <c r="K23" s="5"/>
       <c r="L23" s="5"/>
       <c r="M23" s="5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M24" s="17" t="n">
         <v>70000</v>
@@ -3510,10 +3519,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="M25" s="17" t="n">
         <v>50000</v>
@@ -3521,7 +3530,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="M26" s="17" t="n">
         <v>7000</v>
@@ -3529,16 +3538,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="M27" s="9" t="n">
+        <v>128</v>
+      </c>
+      <c r="M27" s="7" t="n">
         <f aca="false">SUM(M24:M26)*Assumptions!$B$49</f>
         <v>27940</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="M28" s="13" t="n">
         <f aca="false">SUM(M24:M27)</f>
@@ -3547,38 +3556,38 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="M29" s="9" t="n">
+        <v>130</v>
+      </c>
+      <c r="M29" s="7" t="n">
         <f aca="false">M20</f>
-        <v>118725</v>
+        <v>92460</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="M30" s="9" t="n">
+        <v>131</v>
+      </c>
+      <c r="M30" s="7" t="n">
         <f aca="false">M29*Assumptions!$B$48</f>
-        <v>11872.5</v>
+        <v>9246</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="M31" s="13" t="n">
         <f aca="false">M29*(1+Assumptions!$B$48)</f>
-        <v>130597.5</v>
+        <v>101706</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="M32" s="13" t="n">
         <f aca="false">Labor!$M$28+Labor!$M$31</f>
-        <v>285537.5</v>
+        <v>256646</v>
       </c>
     </row>
   </sheetData>
@@ -3597,7 +3606,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
@@ -3609,20 +3618,20 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>18</v>
@@ -3631,75 +3640,75 @@
         <v>19</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="C4" s="8" t="n">
-        <v>1800000</v>
+        <v>140</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>25000</v>
       </c>
       <c r="D4" s="17" t="n">
-        <v>1800000</v>
+        <v>25000</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="C5" s="8" t="n">
-        <v>36000</v>
+        <v>143</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>150000</v>
       </c>
       <c r="D5" s="17" t="n">
-        <v>36000</v>
+        <v>150000</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>141</v>
-      </c>
-      <c r="C6" s="8" t="n">
-        <v>8000</v>
-      </c>
-      <c r="D6" s="17" t="n">
-        <v>8000</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="C7" s="8" t="n">
-        <v>25000</v>
+        <v>147</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>100000</v>
       </c>
       <c r="D7" s="17" t="n">
-        <v>25000</v>
+        <v>100000</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3707,255 +3716,191 @@
         <v>145</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>150000</v>
+        <v>148</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>75000</v>
       </c>
       <c r="D8" s="17" t="n">
-        <v>150000</v>
+        <v>75000</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="C9" s="8" t="n">
-        <v>100000</v>
+        <v>150</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>175000</v>
       </c>
       <c r="D9" s="17" t="n">
-        <v>100000</v>
+        <v>175000</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C10" s="8" t="n">
-        <v>100000</v>
+        <v>152</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>35000</v>
       </c>
       <c r="D10" s="17" t="n">
-        <v>100000</v>
+        <v>35000</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="C11" s="8" t="n">
-        <v>75000</v>
+        <v>153</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>15000</v>
       </c>
       <c r="D11" s="17" t="n">
-        <v>75000</v>
+        <v>15000</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="C12" s="8" t="n">
-        <v>175000</v>
+        <v>155</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>75000</v>
       </c>
       <c r="D12" s="17" t="n">
-        <v>175000</v>
+        <v>75000</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C13" s="8" t="n">
-        <v>35000</v>
+        <v>158</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>20000</v>
       </c>
       <c r="D13" s="17" t="n">
-        <v>35000</v>
+        <v>20000</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="C14" s="8" t="n">
-        <v>15000</v>
+        <v>159</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>10000</v>
       </c>
       <c r="D14" s="17" t="n">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C15" s="8" t="n">
-        <v>75000</v>
+        <v>161</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>10000</v>
       </c>
       <c r="D15" s="17" t="n">
-        <v>75000</v>
+        <v>10000</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="C16" s="8" t="n">
-        <v>20000</v>
+        <v>163</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>25000</v>
       </c>
       <c r="D16" s="17" t="n">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="C17" s="8" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D17" s="17" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>142</v>
+      <c r="B17" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C17" s="13" t="n">
+        <f aca="false">SUM(C4:C16)</f>
+        <v>815000</v>
+      </c>
+      <c r="D17" s="13" t="n">
+        <f aca="false">SUM(D4:D16)</f>
+        <v>815000</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
-        <v>163</v>
-      </c>
       <c r="B18" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C18" s="8" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D18" s="17" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>142</v>
+        <v>165</v>
+      </c>
+      <c r="C18" s="7" t="n">
+        <f aca="false">C17*Assumptions!$B$47</f>
+        <v>81500</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <f aca="false">D17*Assumptions!$B$47</f>
+        <v>81500</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="C19" s="8" t="n">
-        <v>25000</v>
-      </c>
-      <c r="D19" s="17" t="n">
-        <v>25000</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C20" s="13" t="n">
-        <f aca="false">SUMIFS(C4:C19,$A$4:$A$19,"Acquisition")</f>
-        <v>1844000</v>
-      </c>
-      <c r="D20" s="13" t="n">
-        <f aca="false">SUMIFS(D4:D19,$A$4:$A$19,"Acquisition")</f>
-        <v>1844000</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="C21" s="6" t="n">
-        <f aca="false">SUM(C4:C19)-C20</f>
-        <v>815000</v>
-      </c>
-      <c r="D21" s="6" t="n">
-        <f aca="false">SUM(D4:D19)-D20</f>
-        <v>815000</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="C22" s="9" t="n">
-        <f aca="false">C21*Assumptions!$B$47</f>
-        <v>81500</v>
-      </c>
-      <c r="D22" s="9" t="n">
-        <f aca="false">D21*Assumptions!$B$47</f>
-        <v>81500</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C23" s="13" t="n">
-        <f aca="false">C20+C21+C22</f>
-        <v>2740500</v>
-      </c>
-      <c r="D23" s="13" t="n">
-        <f aca="false">D20+D21+D22</f>
-        <v>2740500</v>
+      <c r="C19" s="13" t="n">
+        <f aca="false">C17+C18</f>
+        <v>896500</v>
+      </c>
+      <c r="D19" s="13" t="n">
+        <f aca="false">D17+D18</f>
+        <v>896500</v>
       </c>
     </row>
   </sheetData>

--- a/806-Ramseur-PnL.xlsx
+++ b/806-Ramseur-PnL.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="172">
   <si>
     <t xml:space="preserve">806 E Ramseur Mini Golf + Bar — P&amp;L model</t>
   </si>
@@ -89,10 +89,25 @@
     <t xml:space="preserve">Source / note</t>
   </si>
   <si>
-    <t xml:space="preserve">Property cost and financing (separate calculation)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Property cost</t>
+    <t xml:space="preserve">Property acquisition and financing (separate calculation)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Purchase price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Closing costs (~2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legal, title, recording, lender fees</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Due diligence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase I ESA, survey, inspection, zoning letter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Total property acquisition</t>
   </si>
   <si>
     <t xml:space="preserve">  Amount financed</t>
@@ -101,7 +116,7 @@
     <t xml:space="preserve">  Interest rate</t>
   </si>
   <si>
-    <t xml:space="preserve">  Equity contribution (property cost - amount financed)</t>
+    <t xml:space="preserve">  Equity contribution (total acquisition - amount financed)</t>
   </si>
   <si>
     <t xml:space="preserve">  Property service cost (financed x rate)</t>
@@ -700,15 +715,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="166" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1130,7 +1145,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
@@ -1183,186 +1198,193 @@
         <v>23</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>1260000</v>
+        <v>36000</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>1260000</v>
+        <v>36000</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="8" t="n">
+        <f aca="false">$B$6+$B$7+$B$8</f>
+        <v>1844000</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>1844000</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>1260000</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>1260000</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="9" t="n">
         <v>0.0725</v>
       </c>
-      <c r="C8" s="9" t="n">
+      <c r="C11" s="10" t="n">
         <v>0.0725</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="7" t="n">
-        <f aca="false">$B$6-$B$7</f>
-        <v>540000</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="10" t="n">
-        <f aca="false">$B$7*$B$8</f>
-        <v>91350</v>
-      </c>
-      <c r="C10" s="7" t="n">
-        <v>91350</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
-        <v>28</v>
+      <c r="A12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="7" t="n">
+        <f aca="false">$B$9-$B$10</f>
+        <v>584000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="B13" s="8" t="n">
+        <f aca="false">$B$10*$B$11</f>
+        <v>91350</v>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>91350</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="8" t="n">
         <f aca="false">SUM(Assumptions!$J$8:$J$35)*Assumptions!$B$3+SUMPRODUCT(Assumptions!$J$8:$J$35,Assumptions!$G$8:$G$35)+SUMPRODUCT(Assumptions!$J$8:$J$35,Assumptions!$H$8:$H$35)+SUMPRODUCT(Assumptions!$J$8:$J$35,Assumptions!$I$8:$I$35)+Assumptions!$B$4*Assumptions!$B$5</f>
         <v>766350</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="10" t="n">
+      <c r="D16" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" s="8" t="n">
         <f aca="false">SUM(Assumptions!$J$8:$J$35)*Assumptions!$B$3*Assumptions!$B$40+SUMPRODUCT(Assumptions!$J$8:$J$35,Assumptions!$G$8:$G$35)*Assumptions!$B$41+SUMPRODUCT(Assumptions!$J$8:$J$35,Assumptions!$H$8:$H$35)*Assumptions!$B$42+SUMPRODUCT(Assumptions!$J$8:$J$35,Assumptions!$I$8:$I$35)*Assumptions!$B$43+Assumptions!$B$4*Assumptions!$B$5*Assumptions!$B$44</f>
         <v>522416.5</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15" s="11" t="n">
-        <f aca="false">IF($B$13=0,0,$B$14/$B$13)</f>
-        <v>0.681694395511189</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
-        <v>34</v>
+      <c r="D17" s="3" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" s="7" t="n">
-        <f aca="false">$B$10</f>
-        <v>91350</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="6" t="n">
-        <v>18293</v>
-      </c>
-      <c r="C19" s="7" t="n">
-        <v>18293</v>
-      </c>
-      <c r="D19" s="3" t="s">
         <v>38</v>
       </c>
+      <c r="B18" s="11" t="n">
+        <f aca="false">IF($B$16=0,0,$B$17/$B$16)</f>
+        <v>0.681694395511189</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="B20" s="6" t="n">
-        <v>40000</v>
-      </c>
-      <c r="C20" s="7" t="n">
-        <v>40000</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="6" t="n">
-        <v>36000</v>
-      </c>
-      <c r="C21" s="7" t="n">
-        <v>36000</v>
+      <c r="B21" s="7" t="n">
+        <f aca="false">$B$13</f>
+        <v>91350</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>18293</v>
+      </c>
+      <c r="C22" s="7" t="n">
+        <v>18293</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>40000</v>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>36000</v>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>36000</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" s="12" t="n">
         <f aca="false">Labor!$M$32</f>
         <v>256646</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B23" s="6" t="n">
-        <v>15000</v>
-      </c>
-      <c r="C23" s="7" t="n">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B24" s="6" t="n">
-        <v>30000</v>
-      </c>
-      <c r="C24" s="7" t="n">
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B25" s="6" t="n">
-        <v>15000</v>
-      </c>
-      <c r="C25" s="7" t="n">
-        <v>15000</v>
+      <c r="D25" s="3" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B26" s="6" t="n">
         <v>15000</v>
@@ -1372,74 +1394,107 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B27" s="13" t="n">
-        <f aca="false">SUM(B18:B26)</f>
-        <v>517289</v>
+      <c r="A27" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>30000</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B28" s="13" t="n">
-        <f aca="false">$B$14-$B$27</f>
-        <v>5127.5</v>
+      <c r="A28" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C29" s="7" t="n">
+        <v>15000</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
+      </c>
+      <c r="B30" s="13" t="n">
+        <f aca="false">SUM(B21:B29)</f>
+        <v>517289</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B31" s="7" t="n">
-        <f aca="false">$B$28</f>
+      <c r="A31" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B31" s="13" t="n">
+        <f aca="false">$B$17-$B$30</f>
         <v>5127.5</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B32" s="7" t="n">
-        <f aca="false">$B$9</f>
-        <v>540000</v>
-      </c>
-    </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B33" s="12" t="n">
+      <c r="A33" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B34" s="7" t="n">
+        <f aca="false">$B$31</f>
+        <v>5127.5</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B35" s="7" t="n">
+        <f aca="false">$B$12</f>
+        <v>584000</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B36" s="12" t="n">
         <f aca="false">Capex!$C$19</f>
         <v>896500</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B34" s="13" t="n">
-        <f aca="false">$B$9+$B$33</f>
-        <v>1436500</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B35" s="14" t="n">
-        <f aca="false">IF($B$34=0,0,$B$28/$B$34)</f>
-        <v>0.00356943961016359</v>
+      <c r="D36" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B37" s="13" t="n">
+        <f aca="false">$B$12+$B$36</f>
+        <v>1480500</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B38" s="14" t="n">
+        <f aca="false">IF($B$37=0,0,$B$31/$B$37)</f>
+        <v>0.00346335697399527</v>
       </c>
     </row>
   </sheetData>
@@ -1473,86 +1528,86 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B3" s="15" t="n">
         <v>12</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B4" s="16" t="n">
         <v>20</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B5" s="17" t="n">
         <v>500</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D8" s="16" t="n">
         <v>35</v>
@@ -1583,13 +1638,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D9" s="16" t="n">
         <v>35</v>
@@ -1620,13 +1675,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D10" s="16" t="n">
         <v>35</v>
@@ -1657,13 +1712,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D11" s="16" t="n">
         <v>35</v>
@@ -1694,13 +1749,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D12" s="16" t="n">
         <v>34</v>
@@ -1731,13 +1786,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D13" s="16" t="n">
         <v>34</v>
@@ -1768,13 +1823,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D14" s="16" t="n">
         <v>35</v>
@@ -1805,13 +1860,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D15" s="16" t="n">
         <v>35</v>
@@ -1842,13 +1897,13 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>74</v>
       </c>
       <c r="D16" s="16" t="n">
         <v>35</v>
@@ -1879,13 +1934,13 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D17" s="16" t="n">
         <v>35</v>
@@ -1916,13 +1971,13 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D18" s="16" t="n">
         <v>35</v>
@@ -1953,13 +2008,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="D19" s="16" t="n">
         <v>35</v>
@@ -1990,13 +2045,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D20" s="16" t="n">
         <v>35</v>
@@ -2027,13 +2082,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D21" s="16" t="n">
         <v>35</v>
@@ -2064,13 +2119,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D22" s="16" t="n">
         <v>17</v>
@@ -2101,13 +2156,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D23" s="16" t="n">
         <v>17</v>
@@ -2138,13 +2193,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D24" s="16" t="n">
         <v>17</v>
@@ -2175,13 +2230,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D25" s="16" t="n">
         <v>17</v>
@@ -2212,13 +2267,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="C26" s="3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D26" s="16" t="n">
         <v>18</v>
@@ -2249,13 +2304,13 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="C27" s="3" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D27" s="16" t="n">
         <v>18</v>
@@ -2286,13 +2341,13 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D28" s="16" t="n">
         <v>17</v>
@@ -2323,13 +2378,13 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D29" s="16" t="n">
         <v>17</v>
@@ -2360,13 +2415,13 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B30" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>74</v>
       </c>
       <c r="D30" s="16" t="n">
         <v>18</v>
@@ -2397,13 +2452,13 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D31" s="16" t="n">
         <v>18</v>
@@ -2434,13 +2489,13 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D32" s="16" t="n">
         <v>17</v>
@@ -2471,13 +2526,13 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B33" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="D33" s="16" t="n">
         <v>17</v>
@@ -2508,13 +2563,13 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D34" s="16" t="n">
         <v>17</v>
@@ -2545,13 +2600,13 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D35" s="16" t="n">
         <v>17</v>
@@ -2582,7 +2637,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="J36" s="21" t="n">
         <f aca="false">SUM(J8:J35)</f>
@@ -2595,117 +2650,117 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B40" s="22" t="n">
         <v>0.95</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B41" s="22" t="n">
         <v>0.15</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B42" s="22" t="n">
         <v>0.7</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B43" s="22" t="n">
         <v>0.76</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B44" s="22" t="n">
         <v>0.75</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="B47" s="23" t="n">
         <v>0.1</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B48" s="23" t="n">
         <v>0.1</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B49" s="23" t="n">
         <v>0.22</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -2741,17 +2796,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C3" s="15" t="n">
         <v>15</v>
@@ -2759,51 +2814,51 @@
     </row>
     <row r="5" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C6" s="20" t="n">
         <v>5</v>
@@ -2850,7 +2905,7 @@
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C7" s="20" t="n">
         <v>6</v>
@@ -2896,10 +2951,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C8" s="20" t="n">
         <v>5</v>
@@ -2946,7 +3001,7 @@
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C9" s="20" t="n">
         <v>6</v>
@@ -2992,10 +3047,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C10" s="20" t="n">
         <v>5</v>
@@ -3042,7 +3097,7 @@
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C11" s="20" t="n">
         <v>6</v>
@@ -3088,10 +3143,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C12" s="20" t="n">
         <v>5</v>
@@ -3138,7 +3193,7 @@
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C13" s="20" t="n">
         <v>6</v>
@@ -3184,10 +3239,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>74</v>
       </c>
       <c r="C14" s="20" t="n">
         <v>5</v>
@@ -3234,7 +3289,7 @@
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C15" s="20" t="n">
         <v>6</v>
@@ -3280,10 +3335,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C16" s="20" t="n">
         <v>5</v>
@@ -3330,7 +3385,7 @@
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C17" s="20" t="n">
         <v>6</v>
@@ -3376,10 +3431,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C18" s="20" t="n">
         <v>5</v>
@@ -3426,7 +3481,7 @@
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C19" s="20" t="n">
         <v>6</v>
@@ -3472,7 +3527,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="K20" s="21" t="n">
         <f aca="false">SUM(K6:K19)</f>
@@ -3489,7 +3544,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -3503,15 +3558,15 @@
       <c r="K23" s="5"/>
       <c r="L23" s="5"/>
       <c r="M23" s="5" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="M24" s="17" t="n">
         <v>70000</v>
@@ -3519,10 +3574,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="M25" s="17" t="n">
         <v>50000</v>
@@ -3530,7 +3585,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="M26" s="17" t="n">
         <v>7000</v>
@@ -3538,7 +3593,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="M27" s="7" t="n">
         <f aca="false">SUM(M24:M26)*Assumptions!$B$49</f>
@@ -3547,7 +3602,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="M28" s="13" t="n">
         <f aca="false">SUM(M24:M27)</f>
@@ -3556,7 +3611,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="M29" s="7" t="n">
         <f aca="false">M20</f>
@@ -3565,7 +3620,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="M30" s="7" t="n">
         <f aca="false">M29*Assumptions!$B$48</f>
@@ -3574,7 +3629,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="M31" s="13" t="n">
         <f aca="false">M29*(1+Assumptions!$B$48)</f>
@@ -3583,7 +3638,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="M32" s="13" t="n">
         <f aca="false">Labor!$M$28+Labor!$M$31</f>
@@ -3618,20 +3673,20 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>18</v>
@@ -3640,15 +3695,15 @@
         <v>19</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>25000</v>
@@ -3657,15 +3712,15 @@
         <v>25000</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>150000</v>
@@ -3674,15 +3729,15 @@
         <v>150000</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>100000</v>
@@ -3691,15 +3746,15 @@
         <v>100000</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>100000</v>
@@ -3708,15 +3763,15 @@
         <v>100000</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>75000</v>
@@ -3725,15 +3780,15 @@
         <v>75000</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>175000</v>
@@ -3742,15 +3797,15 @@
         <v>175000</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>35000</v>
@@ -3759,15 +3814,15 @@
         <v>35000</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>15000</v>
@@ -3776,15 +3831,15 @@
         <v>15000</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>75000</v>
@@ -3793,15 +3848,15 @@
         <v>75000</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>20000</v>
@@ -3810,15 +3865,15 @@
         <v>20000</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>10000</v>
@@ -3827,15 +3882,15 @@
         <v>10000</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>10000</v>
@@ -3844,15 +3899,15 @@
         <v>10000</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>25000</v>
@@ -3861,12 +3916,12 @@
         <v>25000</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="2" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="C17" s="13" t="n">
         <f aca="false">SUM(C4:C16)</f>
@@ -3879,7 +3934,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="3" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="C18" s="7" t="n">
         <f aca="false">C17*Assumptions!$B$47</f>
@@ -3892,7 +3947,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="2" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C19" s="13" t="n">
         <f aca="false">C17+C18</f>
